--- a/TS3_mapping.xlsx
+++ b/TS3_mapping.xlsx
@@ -1565,9 +1565,10 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Spectrum-6 in Flash Recovery Mode. 
+          <t xml:space="preserve">Spectrum-6 in Flash Recovery Mode. 
 Suspect ASIC issue.
-Tried master PDB then pass. Replacing with new PDB to retest.</t>
+Tried master PDB then pass. Replacing with new PDB to retest.
+29-SEP: Passed with new PDB - &gt; retets on PDB station </t>
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
@@ -2729,8 +2730,9 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Spectrum-6 in Flash Recovery Mode. 
-Suspect ASIC issue.</t>
+          <t xml:space="preserve">Spectrum-6 in Flash Recovery Mode. 
+Suspect ASIC issue.
+NV : share details </t>
         </is>
       </c>
       <c r="Q41" t="inlineStr"/>

--- a/TS3_mapping.xlsx
+++ b/TS3_mapping.xlsx
@@ -948,7 +948,11 @@
           <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,2,4,4,0,13,134.85,12.89,8.41,6.6,-2.34,nan],[prb:nan,2,4,4,1,13,134.85,12.79,8.51,6.6,-2.89,nan],[prb:nan,2,4,4,2,13,134.85,12.86,8.44,6.6,-2.45,nan],[prb:nan,2,4,4,3,13,134.85,12.98,8.32,6.73,0.15,nan]</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>High speed fail; ELS2 OE4 Lane0~3 no BER</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
@@ -1748,7 +1752,11 @@
           <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,12,6,24,8,95,119.32,12.89,7.88,6.6,-20.09,nan],[prp:-20.09,12,6,24,8,95,119.32,12.89,7.88,6.6,-20.09,nan],[prb:nan,12,6,24,9,95,119.32,12.89,7.88,6.46,-19.75,nan],[prp:-19.75,12,6,24,9,95,119.32,12.89,7.88,6.46,-19.75,nan],[prb:nan,12,6,24,10,95,119.32,12.82,7.95,6.46,-22.68,nan],[prp:-22.68,12,6,24,10,95,119.32,12.82,7.95,6.46,-22.68,nan],[prb:nan,12,6,24,11,95,119.32,12.73,8.04,6.46,-22.68,nan],[prp:-22.68,12,6,24,11,95,119.32,12.73,8.04,6.46,-22.68,nan],[prb:nan,14,5,28,4,110,139.47,12.7,8.74,6.73,-2.79,nan],[prb:nan,14,5,28,5,110,139.47,12.61,8.83,6.73,-2.33,nan],[prb:nan,14,5,28,6,110,139.47,12.67,8.77,6.73,-2.66,nan],[prb:nan,14,5,28,7,110,139.47,12.76,8.68,6.73,-18.57,nan],[prp:-18.57,14,5,28,7,110,139.47,12.76,8.68,6.73,-18.57,nan],[prb:nan,5,1,9,4,34,144.37,13.18,8.41,6.86,-21.87,nan],[prp:-21.87,5,1,9,4,34,144.37,13.18,8.41,6.86,-21.87,nan],[prb:nan,5,1,9,5,34,144.37,13.01,8.58,6.73,-21.87,nan],[prp:-21.87,5,1,9,5,34,144.37,13.01,8.58,6.73,-21.87,nan],[prb:nan,5,1,9,6,34,144.37,13.15,8.44,6.73,-22.68,nan],[prp:-22.68,5,1,9,6,34,144.37,13.15,8.44,6.73,-22.68,nan],[prb:nan,5,1,9,7,34,144.37,13.23,8.36,6.99,-22.08,nan],[prp:-22.08,5,1,9,7,34,144.37,13.23,8.36,6.99,-22.08,nan],[prp:-5.2,2,1,3,6,10,129.27,12.76,8.35,6.6,-5.2,8e-10]</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>found FBK broken - FXV to understand what happened and send RC report</t>
+        </is>
+      </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>

--- a/TS3_mapping.xlsx
+++ b/TS3_mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z64"/>
+  <dimension ref="A1:Z66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -581,12 +581,14 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>63865158390003</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>63865158390003</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -609,9 +611,21 @@
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
@@ -656,7 +670,7 @@
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>FXV</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -666,7 +680,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>On-going</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -676,40 +690,14 @@
       <c r="Z3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" t="n">
-        <v>63865158140001</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>63865158090003</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>63865158370001</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -726,15 +714,27 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-19.75,2,0,3,0,9,124.66,12.73,8.23,6.46,-19.75,nan],[prb:nan,2,0,3,0,9,124.66,12.73,8.23,6.46,-19.75,nan],[prp:-19.75,2,0,3,1,9,124.66,12.67,8.29,6.46,-19.75,nan],[prb:nan,2,0,3,1,9,124.66,12.67,8.29,6.46,-19.75,nan],[prp:-18.7,2,0,3,2,9,124.66,12.86,8.1,6.73,-18.7,nan],[prb:nan,2,0,3,2,9,124.66,12.86,8.1,6.73,-18.7,nan],[prp:-19.07,2,0,3,3,9,124.66,12.76,8.2,6.6,-19.07,nan],[prb:nan,2,0,3,3,9,124.66,12.76,8.2,6.6,-19.07,nan]</t>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,11,4,22,0,85,144.08,12.86,8.73,6.6,-2.43,nan],[prb:nan,11,4,22,1,85,144.08,12.89,8.7,6.73,-2.99,nan],[prb:nan,11,4,22,2,85,144.08,12.82,8.77,6.6,-20.97,nan],[prp:-20.97,11,4,22,2,85,144.08,12.82,8.77,6.6,-20.97,nan],[prb:nan,11,4,22,3,85,144.08,12.86,8.73,6.73,-2.91,nan],[prb:nan,11,6,22,8,87,149.92,12.82,8.94,6.6,-18.15,nan],[prp:-18.15,11,6,22,8,87,149.92,12.82,8.94,6.6,-18.15,nan],[prb:nan,11,6,22,9,87,149.92,12.92,8.84,6.86,-2.39,nan],[prb:nan,11,6,22,10,87,149.92,12.82,8.94,6.6,-2.62,nan],[prb:nan,11,6,22,11,87,149.92,12.73,9.03,6.6,-2.4,nan],[prb:nan,11,7,22,12,88,148.62,12.86,8.86,6.73,-2.3,nan],[prb:nan,11,7,22,13,88,148.62,13.04,8.68,6.99,-2.47,nan],[prb:nan,11,7,22,14,88,148.62,12.89,8.83,6.6,-2.9,nan],[prb:nan,11,7,22,15,88,148.62,12.76,8.96,6.73,-22.68,nan],[prp:-22.68,11,7,22,15,88,148.62,12.76,8.96,6.73,-22.68,nan],[prb:nan,12,3,23,12,92,133.72,12.76,8.5,6.6,-21.61,nan],[prp:-21.61,12,3,23,12,92,133.72,12.76,8.5,6.6,-21.61,nan],[prb:nan,12,3,23,13,92,133.72,12.61,8.65,6.46,-2.37,nan],[prb:nan,12,3,23,14,92,133.72,12.86,8.4,6.6,-2.4,nan],[prb:nan,12,3,23,15,92,133.72,12.76,8.5,6.46,-2.63,nan],[prb:nan,12,6,24,8,95,140.62,12.82,8.66,6.6,-2.2,nan],[prb:nan,12,6,24,9,95,140.62,12.86,8.62,6.6,-21.19,nan],[prp:-21.19,12,6,24,9,95,140.62,12.86,8.62,6.6,-21.19,nan],[prb:nan,12,6,24,10,95,140.62,12.73,8.75,6.46,-18.04,nan],[prp:-18.04,12,6,24,10,95,140.62,12.73,8.75,6.46,-18.04,nan],[prb:nan,12,6,24,11,95,140.62,12.64,8.84,6.32,-18.36,nan],[prp:-18.36,12,6,24,11,95,140.62,12.64,8.84,6.32,-18.36,nan],[prb:nan,12,7,24,12,96,138.35,12.82,8.59,6.6,-20.6,nan],[prp:-20.6,12,7,24,12,96,138.35,12.82,8.59,6.6,-20.6,nan],[prb:nan,12,7,24,13,96,138.35,13.01,8.4,6.73,-20.76,nan],[prp:-20.76,12,7,24,13,96,138.35,13.01,8.4,6.73,-20.76,nan],[prb:nan,12,7,24,14,96,138.35,12.92,8.49,6.46,-21.61,nan],[prp:-21.61,12,7,24,14,96,138.35,12.92,8.49,6.46,-21.61,nan],[prb:nan,12,7,24,15,96,138.35,12.82,8.59,6.6,-21.61,nan],[prp:-21.61,12,7,24,15,96,138.35,12.82,8.59,6.6,-21.61,nan],[prb:nan,15,3,29,12,116,145.1,12.95,8.67,6.86,-21.87,nan],[prp:-21.87,15,3,29,12,116,145.1,12.95,8.67,6.86,-21.87,nan],[prb:nan,15,3,29,13,116,145.1,13.04,8.58,6.86,-21.87,nan],[prp:-21.87,15,3,29,13,116,145.1,13.04,8.58,6.86,-21.87,nan],[prb:nan,15,3,29,14,116,145.1,12.95,8.67,6.73,-22.08,nan],[prp:-22.08,15,3,29,14,116,145.1,12.95,8.67,6.73,-22.08,nan],[prb:nan,15,3,29,15,116,145.1,12.76,8.86,6.73,-22.08,nan],[prp:-22.08,15,3,29,15,116,145.1,12.76,8.86,6.73,-22.08,nan]</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>On-going</t>
+        </is>
+      </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
@@ -748,10 +748,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>63865158140004</v>
+        <v>63865158140001</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -759,24 +759,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>63865158090008</v>
+        <v>63865158090003</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>63865158370005+'[TS3_Yield_Report_20260929_094412.xlsx]Fail Units'!$F$13</t>
-        </is>
+      <c r="G5" t="n">
+        <v>63865158370001</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -792,7 +794,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,4,6,8,8,31,159.81,13.07,8.97,6.73,-2.69,nan],[prp:-22.68,4,6,8,9,31,159.81,13.04,9,6.86,-22.68,nan],[prb:nan,4,6,8,9,31,159.81,13.04,9,6.86,-22.68,nan],[prp:-19.21,4,6,8,10,31,159.81,13.15,8.89,6.99,-19.21,nan],[prb:nan,4,6,8,10,31,159.81,13.15,8.89,6.99,-19.21,nan],[prp:-19.47,4,6,8,11,31,159.81,12.95,9.09,6.73,-19.47,nan],[prb:nan,4,6,8,11,31,159.81,12.95,9.09,6.73,-19.47,nan],[prp:-18.7,4,7,8,12,32,180.92,13.4,9.17,7.11,-18.7,nan],[prb:nan,4,7,8,12,32,180.92,13.4,9.17,7.11,-18.7,nan],[prp:-18.93,4,7,8,13,32,180.92,13.32,9.25,7.11,-18.93,nan],[prb:nan,4,7,8,13,32,180.92,13.32,9.25,7.11,-18.93,nan],[prp:-22.37,4,7,8,14,32,180.92,13.4,9.17,7.23,-22.37,nan],[prb:nan,4,7,8,14,32,180.92,13.4,9.17,7.23,-22.37,nan],[prp:-22.37,4,7,8,15,32,180.92,13.12,9.45,6.86,-22.37,nan],[prb:nan,4,7,8,15,32,180.92,13.12,9.45,6.86,-22.37,nan],[prp:-19.32,4,3,7,12,28,164.29,13.15,9.01,6.73,-19.32,nan],[prb:nan,4,3,7,12,28,164.29,13.15,9.01,6.73,-19.32,nan],[prb:nan,4,3,7,13,28,164.29,13.09,9.07,6.6,-2.67,nan],[prb:nan,4,3,7,14,28,164.29,13.04,9.12,6.73,-2.48,nan],[prb:nan,4,3,7,15,28,164.29,12.98,9.18,6.73,-2.16,nan],[prp:-20.76,3,6,6,8,23,130.09,12.79,8.35,6.6,-20.76,nan],[prb:nan,3,6,6,8,23,130.09,12.79,8.35,6.6,-20.76,nan],[prb:nan,3,6,6,9,23,130.09,12.95,8.19,6.6,-2.6,nan],[prb:nan,3,6,6,10,23,130.09,12.82,8.32,6.46,-1.81,nan],[prb:nan,3,6,6,11,23,130.09,12.82,8.32,6.6,-2.1,nan],[prb:nan,3,7,6,12,24,144.49,12.98,8.62,6.73,-2.24,nan],[prb:nan,3,7,6,13,24,144.49,13.12,8.48,6.86,-2.84,nan],[prb:nan,3,7,6,14,24,144.49,13.07,8.53,6.73,-2.41,nan],[prp:-18.04,3,7,6,15,24,144.49,12.79,8.81,6.46,-18.04,nan],[prb:nan,3,7,6,15,24,144.49,12.79,8.81,6.46,-18.04,nan],[prb:nan,3,4,6,0,21,134.46,13.01,8.28,6.73,-2.91,nan],[prb:nan,3,4,6,1,21,134.46,12.82,8.47,6.6,-2.4,nan],[prp:-19.07,3,4,6,2,21,134.46,12.82,8.47,6.73,-19.07,nan],[prb:nan,3,4,6,2,21,134.46,12.82,8.47,6.73,-19.07,nan],[prb:nan,3,4,6,3,21,134.46,12.95,8.34,6.73,-2.4,nan]</t>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-19.75,2,0,3,0,9,124.66,12.73,8.23,6.46,-19.75,nan],[prb:nan,2,0,3,0,9,124.66,12.73,8.23,6.46,-19.75,nan],[prp:-19.75,2,0,3,1,9,124.66,12.67,8.29,6.46,-19.75,nan],[prb:nan,2,0,3,1,9,124.66,12.67,8.29,6.46,-19.75,nan],[prp:-18.7,2,0,3,2,9,124.66,12.86,8.1,6.73,-18.7,nan],[prb:nan,2,0,3,2,9,124.66,12.86,8.1,6.73,-18.7,nan],[prp:-19.07,2,0,3,3,9,124.66,12.76,8.2,6.6,-19.07,nan],[prb:nan,2,0,3,3,9,124.66,12.76,8.2,6.6,-19.07,nan]</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -814,10 +816,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>63865158140003</v>
+        <v>63865158140004</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -825,28 +827,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>63865158090004</v>
+        <v>63865158090008</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>63865158370003</t>
-        </is>
+      <c r="G6" t="n">
+        <v>63865158370005</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -862,32 +858,15 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,10,0,19,0,73,104.44,12.82,7.37,6.6,-22.08,nan],[prp:-22.08,10,0,19,0,73,104.44,12.82,7.37,6.6,-22.08,nan],[prb:nan,10,0,19,1,73,104.44,12.7,7.49,6.6,-21.87,nan],[prp:-21.87,10,0,19,1,73,104.44,12.7,7.49,6.6,-21.87,nan],[prb:nan,10,0,19,2,73,104.44,12.7,7.49,6.46,-18.48,nan],[prp:-18.48,10,0,19,2,73,104.44,12.7,7.49,6.46,-18.48,nan],[prb:nan,10,0,19,3,73,104.44,12.82,7.37,6.6,-18.36,nan],[prp:-18.36,10,0,19,3,73,104.44,12.82,7.37,6.6,-18.36,nan]</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>ELS10 OE19 0~3 MMC73 no RxP, MMC73 LB not full inserted.
-Reinsert then test pass.</t>
-        </is>
-      </c>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,4,6,8,8,31,159.81,13.07,8.97,6.73,-2.69,nan],[prp:-22.68,4,6,8,9,31,159.81,13.04,9,6.86,-22.68,nan],[prb:nan,4,6,8,9,31,159.81,13.04,9,6.86,-22.68,nan],[prp:-19.21,4,6,8,10,31,159.81,13.15,8.89,6.99,-19.21,nan],[prb:nan,4,6,8,10,31,159.81,13.15,8.89,6.99,-19.21,nan],[prp:-19.47,4,6,8,11,31,159.81,12.95,9.09,6.73,-19.47,nan],[prb:nan,4,6,8,11,31,159.81,12.95,9.09,6.73,-19.47,nan],[prp:-18.7,4,7,8,12,32,180.92,13.4,9.17,7.11,-18.7,nan],[prb:nan,4,7,8,12,32,180.92,13.4,9.17,7.11,-18.7,nan],[prp:-18.93,4,7,8,13,32,180.92,13.32,9.25,7.11,-18.93,nan],[prb:nan,4,7,8,13,32,180.92,13.32,9.25,7.11,-18.93,nan],[prp:-22.37,4,7,8,14,32,180.92,13.4,9.17,7.23,-22.37,nan],[prb:nan,4,7,8,14,32,180.92,13.4,9.17,7.23,-22.37,nan],[prp:-22.37,4,7,8,15,32,180.92,13.12,9.45,6.86,-22.37,nan],[prb:nan,4,7,8,15,32,180.92,13.12,9.45,6.86,-22.37,nan],[prp:-19.32,4,3,7,12,28,164.29,13.15,9.01,6.73,-19.32,nan],[prb:nan,4,3,7,12,28,164.29,13.15,9.01,6.73,-19.32,nan],[prb:nan,4,3,7,13,28,164.29,13.09,9.07,6.6,-2.67,nan],[prb:nan,4,3,7,14,28,164.29,13.04,9.12,6.73,-2.48,nan],[prb:nan,4,3,7,15,28,164.29,12.98,9.18,6.73,-2.16,nan],[prp:-20.76,3,6,6,8,23,130.09,12.79,8.35,6.6,-20.76,nan],[prb:nan,3,6,6,8,23,130.09,12.79,8.35,6.6,-20.76,nan],[prb:nan,3,6,6,9,23,130.09,12.95,8.19,6.6,-2.6,nan],[prb:nan,3,6,6,10,23,130.09,12.82,8.32,6.46,-1.81,nan],[prb:nan,3,6,6,11,23,130.09,12.82,8.32,6.6,-2.1,nan],[prb:nan,3,7,6,12,24,144.49,12.98,8.62,6.73,-2.24,nan],[prb:nan,3,7,6,13,24,144.49,13.12,8.48,6.86,-2.84,nan],[prb:nan,3,7,6,14,24,144.49,13.07,8.53,6.73,-2.41,nan],[prp:-18.04,3,7,6,15,24,144.49,12.79,8.81,6.46,-18.04,nan],[prb:nan,3,7,6,15,24,144.49,12.79,8.81,6.46,-18.04,nan],[prb:nan,3,4,6,0,21,134.46,13.01,8.28,6.73,-2.91,nan],[prb:nan,3,4,6,1,21,134.46,12.82,8.47,6.6,-2.4,nan],[prp:-19.07,3,4,6,2,21,134.46,12.82,8.47,6.73,-19.07,nan],[prb:nan,3,4,6,2,21,134.46,12.82,8.47,6.73,-19.07,nan],[prb:nan,3,4,6,3,21,134.46,12.95,8.34,6.73,-2.4,nan]</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>FXV</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Peter</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
@@ -901,10 +880,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>63865158140002</v>
+        <v>63865158140003</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -912,24 +891,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>63865158090001</v>
+        <v>63865158090004</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>63865158370007</t>
-        </is>
+      <c r="G7" t="n">
+        <v>63865158370003</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -945,19 +926,32 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,2,4,4,0,13,134.85,12.89,8.41,6.6,-2.34,nan],[prb:nan,2,4,4,1,13,134.85,12.79,8.51,6.6,-2.89,nan],[prb:nan,2,4,4,2,13,134.85,12.86,8.44,6.6,-2.45,nan],[prb:nan,2,4,4,3,13,134.85,12.98,8.32,6.73,0.15,nan]</t>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,10,0,19,0,73,104.44,12.82,7.37,6.6,-22.08,nan],[prp:-22.08,10,0,19,0,73,104.44,12.82,7.37,6.6,-22.08,nan],[prb:nan,10,0,19,1,73,104.44,12.7,7.49,6.6,-21.87,nan],[prp:-21.87,10,0,19,1,73,104.44,12.7,7.49,6.6,-21.87,nan],[prb:nan,10,0,19,2,73,104.44,12.7,7.49,6.46,-18.48,nan],[prp:-18.48,10,0,19,2,73,104.44,12.7,7.49,6.46,-18.48,nan],[prb:nan,10,0,19,3,73,104.44,12.82,7.37,6.6,-18.36,nan],[prp:-18.36,10,0,19,3,73,104.44,12.82,7.37,6.6,-18.36,nan]</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>High speed fail; ELS2 OE4 Lane0~3 no BER</t>
+          <t>ELS10 OE19 0~3 MMC73 no RxP, MMC73 LB not full inserted.
+Reinsert then test pass.</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
@@ -971,10 +965,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>63865158140006</v>
+        <v>63865158140002</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -982,17 +976,15 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>63865158090002</v>
+        <v>63865158090001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>63865158370002</t>
-        </is>
+      <c r="G8" t="n">
+        <v>63865158370007</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1010,15 +1002,19 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>bmc_burn_if_needed-check_bmc_format_and_version_and_burn_if_wrong_chameleon_bmc-ERROR-Exception;</t>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Failed to ping 192.168.10.30 after -0.5 seconds</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,2,4,4,0,13,134.85,12.89,8.41,6.6,-2.34,nan],[prb:nan,2,4,4,1,13,134.85,12.79,8.51,6.6,-2.89,nan],[prb:nan,2,4,4,2,13,134.85,12.86,8.44,6.6,-2.45,nan],[prb:nan,2,4,4,3,13,134.85,12.98,8.32,6.73,0.15,nan]</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>High speed fail; ELS2 OE4 Lane0~3 no BER</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
@@ -1037,10 +1033,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>63865158140007</v>
+        <v>63865158140006</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1048,26 +1044,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>63865158090009</v>
+        <v>63865158090002</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>63865158370006</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>63865158370002</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>bmc_burn_if_needed-check_bmc_format_and_version_and_burn_if_wrong_chameleon_bmc-ERROR-Exception;</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Failed to ping 192.168.10.30 after -0.5 seconds</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
@@ -1087,10 +1097,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>63865158140008</v>
+        <v>63865158140007</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1098,21 +1108,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>63865158090006</v>
+        <v>63865158090009</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>63865158370004</t>
-        </is>
+      <c r="G10" t="n">
+        <v>63865158370006</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1131,7 +1139,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,7,4,14,0,53,128.58,13.01,8.08,6.73,-19.91,nan],[prp:-19.91,7,4,14,0,53,128.58,13.01,8.08,6.73,-19.91,nan],[prb:nan,7,4,14,1,53,128.58,12.79,8.3,6.73,-19.91,nan],[prp:-19.91,7,4,14,1,53,128.58,12.79,8.3,6.73,-19.91,nan],[prb:nan,7,4,14,2,53,128.58,13.04,8.05,6.99,-20.09,nan],[prp:-20.09,7,4,14,2,53,128.58,13.04,8.05,6.99,-20.09,nan],[prb:nan,7,4,14,3,53,128.58,12.98,8.11,6.86,-19.91,nan],[prp:-19.91,7,4,14,3,53,128.58,12.98,8.11,6.86,-19.91,nan]</t>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,7,2,13,8,51,134.29,12.76,8.52,6.6,-19.63,nan],[prp:-19.63,7,2,13,8,51,134.29,12.76,8.52,6.6,-19.63,nan],[prb:nan,7,2,13,9,51,134.29,12.86,8.42,6.73,-19.75,nan],[prp:-19.75,7,2,13,9,51,134.29,12.86,8.42,6.73,-19.75,nan],[prb:nan,7,2,13,10,51,134.29,12.76,8.52,6.6,-20.97,nan],[prp:-20.97,7,2,13,10,51,134.29,12.76,8.52,6.6,-20.97,nan],[prb:nan,7,2,13,11,51,134.29,12.67,8.61,6.46,-20.97,nan],[prp:-20.97,7,2,13,11,51,134.29,12.67,8.61,6.46,-20.97,nan],[prb:nan,9,7,18,12,72,134.62,12.92,8.37,6.6,-20.6,nan],[prp:-20.6,9,7,18,12,72,134.62,12.92,8.37,6.6,-20.6,nan],[prb:nan,9,7,18,13,72,134.62,12.95,8.34,6.73,-20.41,nan],[prp:-20.41,9,7,18,13,72,134.62,12.95,8.34,6.73,-20.41,nan],[prb:nan,9,7,18,14,72,134.62,13.04,8.25,6.86,-19.47,nan],[prp:-19.47,9,7,18,14,72,134.62,13.04,8.25,6.86,-19.47,nan],[prb:nan,9,7,18,15,72,134.62,12.89,8.4,6.86,-19.75,nan],[prp:-19.75,9,7,18,15,72,134.62,12.89,8.4,6.86,-19.75,nan],[prb:nan,11,0,21,0,81,124.53,12.92,8.03,6.73,-21.19,nan],[prp:-21.19,11,0,21,0,81,124.53,12.92,8.03,6.73,-21.19,nan],[prb:nan,11,0,21,1,81,124.53,12.82,8.13,6.73,-21.87,nan],[prp:-21.87,11,0,21,1,81,124.53,12.82,8.13,6.73,-21.87,nan],[prb:nan,11,0,21,2,81,124.53,12.86,8.09,6.6,-20.6,nan],[prp:-20.6,11,0,21,2,81,124.53,12.86,8.09,6.6,-20.6,nan],[prb:nan,11,0,21,3,81,124.53,12.92,8.03,6.73,-20.41,nan],[prp:-20.41,11,0,21,3,81,124.53,12.92,8.03,6.73,-20.41,nan],[prb:nan,11,6,22,8,87,149.85,12.89,8.87,6.73,-20.09,nan],[prp:-20.09,11,6,22,8,87,149.85,12.89,8.87,6.73,-20.09,nan],[prb:nan,11,6,22,9,87,149.85,13.01,8.75,6.86,-20.09,nan],[prp:-20.09,11,6,22,9,87,149.85,13.01,8.75,6.86,-20.09,nan],[prb:nan,11,6,22,10,87,149.85,12.73,9.03,6.73,-19.47,nan],[prp:-19.47,11,6,22,10,87,149.85,12.73,9.03,6.73,-19.47,nan],[prb:nan,11,6,22,11,87,149.85,12.73,9.03,6.46,-19.47,nan],[prp:-19.47,11,6,22,11,87,149.85,12.73,9.03,6.46,-19.47,nan],[prb:nan,15,3,29,12,116,119.23,12.89,7.87,6.73,-21.87,nan],[prp:-21.87,15,3,29,12,116,119.23,12.89,7.87,6.73,-21.87,nan],[prb:nan,15,3,29,13,116,119.23,12.98,7.78,6.73,-21.87,nan],[prp:-21.87,15,3,29,13,116,119.23,12.98,7.78,6.73,-21.87,nan],[prb:nan,15,3,29,14,116,119.23,12.82,7.94,6.6,-19.32,nan],[prp:-19.32,15,3,29,14,116,119.23,12.82,7.94,6.6,-19.32,nan],[prb:nan,15,3,29,15,116,119.23,12.89,7.87,6.73,-19.91,nan],[prp:-19.91,15,3,29,15,116,119.23,12.89,7.87,6.73,-19.91,nan]</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1153,10 +1161,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>63865158140009</v>
+        <v>63865158140008</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1164,26 +1172,44 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>63865158090007</v>
+        <v>63865158090006</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>63865158370008</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>63865158370004</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,7,4,14,0,53,128.58,13.01,8.08,6.73,-19.91,nan],[prp:-19.91,7,4,14,0,53,128.58,13.01,8.08,6.73,-19.91,nan],[prb:nan,7,4,14,1,53,128.58,12.79,8.3,6.73,-19.91,nan],[prp:-19.91,7,4,14,1,53,128.58,12.79,8.3,6.73,-19.91,nan],[prb:nan,7,4,14,2,53,128.58,13.04,8.05,6.99,-20.09,nan],[prp:-20.09,7,4,14,2,53,128.58,13.04,8.05,6.99,-20.09,nan],[prb:nan,7,4,14,3,53,128.58,12.98,8.11,6.86,-19.91,nan],[prp:-19.91,7,4,14,3,53,128.58,12.98,8.11,6.86,-19.91,nan]</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
@@ -1203,10 +1229,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>63865158140010</v>
+        <v>63865158140009</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1214,57 +1240,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>63865158090005</v>
+        <v>63865158090007</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>63865158370008</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,14,0,27,0,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,0,27,1,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,0,27,2,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,0,27,3,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,1,27,4,106,0,31.17,-327.68,-1,-100],[eocl:-1.0,14,1,27,5,106,0,31.17,-327.68,-1,-100],[eocl:-1.0,14,1,27,6,106,0,31.17,-327.68,-1,-100],[eocl:-1.0,14,1,27,7,106,0,31.17,-327.68,-1,-100]</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Fiber fracture, replace E-FBK
-Replaced FBK then pass</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>FXV</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Peter</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
@@ -1278,10 +1285,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>63865158140012</v>
+        <v>63865158140010</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1289,24 +1296,59 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>63865158090027</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+        <v>63865158090005</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>63865158370051</v>
+      </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,14,0,27,0,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,0,27,1,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,0,27,2,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,0,27,3,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,1,27,4,106,0,31.17,-327.68,-1,-100],[eocl:-1.0,14,1,27,5,106,0,31.17,-327.68,-1,-100],[eocl:-1.0,14,1,27,6,106,0,31.17,-327.68,-1,-100],[eocl:-1.0,14,1,27,7,106,0,31.17,-327.68,-1,-100]</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fiber fracture, replace E-FBK
+Replaced FBK then pass</t>
+        </is>
+      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
@@ -1320,10 +1362,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" t="n">
-        <v>63865158140016</v>
+        <v>63865158140012</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1331,14 +1373,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>63865158090028</v>
+        <v>63865158090027</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>63865158370028</v>
+      </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
@@ -1366,10 +1410,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>63865158140015</v>
+        <v>63865158140016</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1377,17 +1421,15 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>63865158090024</v>
+        <v>63865158090028</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>63865158370015</t>
-        </is>
+      <c r="G15" t="n">
+        <v>63865158370019</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -1416,10 +1458,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>63865158140014</v>
+        <v>63865158140015</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1427,58 +1469,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>63865158090026</v>
+        <v>63865158090024</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>63865158370015</v>
+      </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:14.08,7,3,13,12,52,0,31.06,0.84,14.08,-100],[eocl:13.62,7,3,13,13,52,0,31.06,1.3,13.62,-100],[eocl:13.62,7,3,13,14,52,0,31.06,1.3,13.62,-100],[eocl:13.21,7,3,13,15,52,0,31.06,1.71,13.21,-100]</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>FBK stand alone IL still abnormal
-Need to replace an W-FBK
-Replaced FBK then pass</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>FXV</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Peter</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
@@ -1492,29 +1506,71 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>63865158140013</v>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+        <v>63865158140014</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>63865158090026</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>63865158370052</v>
+      </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:14.08,7,3,13,12,52,0,31.06,0.84,14.08,-100],[eocl:13.62,7,3,13,13,52,0,31.06,1.3,13.62,-100],[eocl:13.62,7,3,13,14,52,0,31.06,1.3,13.62,-100],[eocl:13.21,7,3,13,15,52,0,31.06,1.71,13.21,-100]</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>FBK stand alone IL still abnormal
+Need to replace an W-FBK
+Replaced FBK then pass</t>
+        </is>
+      </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
@@ -1528,70 +1584,29 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
-        <v>63865158140019</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>63865158090034</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+        <v>63865158140013</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>power_on-validate_power_converter_dma_data-ERROR-Exception;</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>csm1_asic_brd__pdb_node_controller': 'write_i2c_block' function failed: device=/dev/mst/192.168.10.20:23108,@dev@mst@dev-i2c-6, i2c_addr=0x60, addr_width=1, reg_addr=0xc7, size=2</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Spectrum-6 in Flash Recovery Mode. 
-Suspect ASIC issue.
-Tried master PDB then pass. Replacing with new PDB to retest.
-29-SEP: Passed with new PDB - &gt; retets on PDB station </t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>FXV</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Joy</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>On-going</t>
-        </is>
-      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
@@ -1605,10 +1620,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>63865158140020</v>
+        <v>63865158140019</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1616,32 +1631,65 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>63865158090033</v>
+        <v>63865158090034</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>63865158370017</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>63865158370042</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>power_on-validate_power_converter_dma_data-ERROR-Exception;</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>csm1_asic_brd__pdb_node_controller': 'write_i2c_block' function failed: device=/dev/mst/192.168.10.20:23108,@dev@mst@dev-i2c-6, i2c_addr=0x60, addr_width=1, reg_addr=0xc7, size=2</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spectrum-6 in Flash Recovery Mode. 
+Suspect ASIC issue.
+Tried master PDB then pass. Replacing with new PDB to retest.
+29-SEP: Passed with new PDB - &gt; retets on PDB station </t>
+        </is>
+      </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Joy</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>On-going</t>
+        </is>
+      </c>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
@@ -1649,43 +1697,33 @@
       <c r="Z19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>18</v>
-      </c>
-      <c r="C20" t="n">
-        <v>63865158140021</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>63865158090032</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>63865158370018</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-17.93,15,7,30,12,120,139.29,12.92,8.52,6.86,-17.93,nan],[prb:nan,15,7,30,12,120,139.29,12.92,8.52,6.86,-17.93,nan],[prp:-18.48,15,7,30,13,120,139.29,13.01,8.43,6.86,-18.48,nan],[prb:nan,15,7,30,13,120,139.29,13.01,8.43,6.86,-18.48,nan],[prp:-20.97,15,7,30,14,120,139.29,12.89,8.55,6.73,-20.97,nan],[prb:nan,15,7,30,14,120,139.29,12.89,8.55,6.73,-20.97,nan],[prp:-20.97,15,7,30,15,120,139.29,12.82,8.62,6.73,-20.97,nan],[prb:nan,15,7,30,15,120,139.29,12.82,8.62,6.73,-20.97,nan]</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
@@ -1705,10 +1743,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>63865158140022</v>
+        <v>63865158140020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1716,17 +1754,15 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>63865158090037</v>
+        <v>63865158090033</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>63865158370014</t>
-        </is>
+      <c r="G21" t="n">
+        <v>63865158370017</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1749,14 +1785,10 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,12,6,24,8,95,119.32,12.89,7.88,6.6,-20.09,nan],[prp:-20.09,12,6,24,8,95,119.32,12.89,7.88,6.6,-20.09,nan],[prb:nan,12,6,24,9,95,119.32,12.89,7.88,6.46,-19.75,nan],[prp:-19.75,12,6,24,9,95,119.32,12.89,7.88,6.46,-19.75,nan],[prb:nan,12,6,24,10,95,119.32,12.82,7.95,6.46,-22.68,nan],[prp:-22.68,12,6,24,10,95,119.32,12.82,7.95,6.46,-22.68,nan],[prb:nan,12,6,24,11,95,119.32,12.73,8.04,6.46,-22.68,nan],[prp:-22.68,12,6,24,11,95,119.32,12.73,8.04,6.46,-22.68,nan],[prb:nan,14,5,28,4,110,139.47,12.7,8.74,6.73,-2.79,nan],[prb:nan,14,5,28,5,110,139.47,12.61,8.83,6.73,-2.33,nan],[prb:nan,14,5,28,6,110,139.47,12.67,8.77,6.73,-2.66,nan],[prb:nan,14,5,28,7,110,139.47,12.76,8.68,6.73,-18.57,nan],[prp:-18.57,14,5,28,7,110,139.47,12.76,8.68,6.73,-18.57,nan],[prb:nan,5,1,9,4,34,144.37,13.18,8.41,6.86,-21.87,nan],[prp:-21.87,5,1,9,4,34,144.37,13.18,8.41,6.86,-21.87,nan],[prb:nan,5,1,9,5,34,144.37,13.01,8.58,6.73,-21.87,nan],[prp:-21.87,5,1,9,5,34,144.37,13.01,8.58,6.73,-21.87,nan],[prb:nan,5,1,9,6,34,144.37,13.15,8.44,6.73,-22.68,nan],[prp:-22.68,5,1,9,6,34,144.37,13.15,8.44,6.73,-22.68,nan],[prb:nan,5,1,9,7,34,144.37,13.23,8.36,6.99,-22.08,nan],[prp:-22.08,5,1,9,7,34,144.37,13.23,8.36,6.99,-22.08,nan],[prp:-5.2,2,1,3,6,10,129.27,12.76,8.35,6.6,-5.2,8e-10]</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>found FBK broken - FXV to understand what happened and send RC report</t>
-        </is>
-      </c>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-20.41,7,4,14,0,53,109.98,12.86,7.55,6.73,-20.41,nan],[prb:nan,7,4,14,0,53,109.98,12.86,7.55,6.73,-20.41,nan],[prp:-19.47,7,4,14,1,53,109.98,12.7,7.71,6.6,-19.47,nan],[prb:nan,7,4,14,1,53,109.98,12.7,7.71,6.6,-19.47,nan],[prp:-22.68,7,4,14,2,53,109.98,12.92,7.49,6.6,-22.68,nan],[prb:nan,7,4,14,2,53,109.98,12.92,7.49,6.6,-22.68,nan],[prp:-21.87,7,4,14,3,53,109.98,12.89,7.52,6.6,-21.87,nan],[prb:nan,7,4,14,3,53,109.98,12.89,7.52,6.6,-21.87,nan],[prp:-19.91,11,4,22,0,85,119.68,12.76,8.02,6.46,-19.91,nan],[prb:nan,11,4,22,0,85,119.68,12.76,8.02,6.46,-19.91,nan],[prp:-20.22,11,4,22,1,85,119.68,12.76,8.02,6.32,-20.22,nan],[prb:nan,11,4,22,1,85,119.68,12.76,8.02,6.32,-20.22,nan],[prp:-20.97,11,4,22,2,85,119.68,12.79,7.99,6.46,-20.97,nan],[prb:nan,11,4,22,2,85,119.68,12.79,7.99,6.46,-20.97,nan],[prp:-20.97,11,4,22,3,85,119.68,12.86,7.92,6.46,-20.97,nan],[prb:nan,11,4,22,3,85,119.68,12.86,7.92,6.46,-20.97,nan]</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
@@ -1775,10 +1807,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C22" t="n">
-        <v>63865158140023</v>
+        <v>63865158140021</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1786,17 +1818,15 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>63865158090031</v>
+        <v>63865158090032</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>63865158370009</t>
-        </is>
+      <c r="G22" t="n">
+        <v>63865158370018</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1807,9 +1837,21 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>reset_button-reset_test-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>reset_pushed-Verify reset button pushed</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
@@ -1829,10 +1871,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C23" t="n">
-        <v>63865158140025</v>
+        <v>63865158140022</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1840,27 +1882,45 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>63865158090022</v>
+        <v>63865158090037</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>63865158370010</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>63865158370014</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,12,6,24,8,95,119.32,12.89,7.88,6.6,-20.09,nan],[prp:-20.09,12,6,24,8,95,119.32,12.89,7.88,6.6,-20.09,nan],[prb:nan,12,6,24,9,95,119.32,12.89,7.88,6.46,-19.75,nan],[prp:-19.75,12,6,24,9,95,119.32,12.89,7.88,6.46,-19.75,nan],[prb:nan,12,6,24,10,95,119.32,12.82,7.95,6.46,-22.68,nan],[prp:-22.68,12,6,24,10,95,119.32,12.82,7.95,6.46,-22.68,nan],[prb:nan,12,6,24,11,95,119.32,12.73,8.04,6.46,-22.68,nan],[prp:-22.68,12,6,24,11,95,119.32,12.73,8.04,6.46,-22.68,nan],[prb:nan,14,5,28,4,110,139.47,12.7,8.74,6.73,-2.79,nan],[prb:nan,14,5,28,5,110,139.47,12.61,8.83,6.73,-2.33,nan],[prb:nan,14,5,28,6,110,139.47,12.67,8.77,6.73,-2.66,nan],[prb:nan,14,5,28,7,110,139.47,12.76,8.68,6.73,-18.57,nan],[prp:-18.57,14,5,28,7,110,139.47,12.76,8.68,6.73,-18.57,nan],[prb:nan,5,1,9,4,34,144.37,13.18,8.41,6.86,-21.87,nan],[prp:-21.87,5,1,9,4,34,144.37,13.18,8.41,6.86,-21.87,nan],[prb:nan,5,1,9,5,34,144.37,13.01,8.58,6.73,-21.87,nan],[prp:-21.87,5,1,9,5,34,144.37,13.01,8.58,6.73,-21.87,nan],[prb:nan,5,1,9,6,34,144.37,13.15,8.44,6.73,-22.68,nan],[prp:-22.68,5,1,9,6,34,144.37,13.15,8.44,6.73,-22.68,nan],[prb:nan,5,1,9,7,34,144.37,13.23,8.36,6.99,-22.08,nan],[prp:-22.08,5,1,9,7,34,144.37,13.23,8.36,6.99,-22.08,nan],[prp:-5.2,2,1,3,6,10,129.27,12.76,8.35,6.6,-5.2,8e-10]</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>found FBK broken - FXV to understand what happened and send RC report</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
@@ -1879,10 +1939,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C24" t="n">
-        <v>63865158140024</v>
+        <v>63865158140023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1890,15 +1950,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>63865158090023</v>
+        <v>63865158090031</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>63865158370009</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -1925,10 +1991,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C25" t="n">
-        <v>63865158140026</v>
+        <v>63865158140025</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1936,10 +2002,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>63865158090029</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+        <v>63865158090022</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>63865158370010</v>
+      </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
@@ -1967,10 +2039,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C26" t="n">
-        <v>63865158140028</v>
+        <v>63865158140024</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1978,17 +2050,15 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>63865158090021</v>
+        <v>63865158090023</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>63865158370024</t>
-        </is>
+      <c r="G26" t="n">
+        <v>63865158370016</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -2017,10 +2087,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C27" t="n">
-        <v>63865158140029</v>
+        <v>63865158140026</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2028,10 +2098,12 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>63865158090038</v>
+        <v>63865158090029</v>
       </c>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>63865158370044</v>
+      </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
@@ -2059,10 +2131,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C28" t="n">
-        <v>63865158140030</v>
+        <v>63865158140028</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2070,10 +2142,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>63865158090042</v>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
+        <v>63865158090021</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>63865158370024</v>
+      </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
@@ -2101,10 +2179,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C29" t="n">
-        <v>63865158140037</v>
+        <v>63865158140029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2112,18 +2190,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>63865158090018</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>63865158370013</t>
-        </is>
-      </c>
+        <v>63865158090038</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
@@ -2151,10 +2221,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C30" t="n">
-        <v>63865158140032</v>
+        <v>63865158140030</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2162,42 +2232,18 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>63865158090013</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>63865158370012</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
+        <v>63865158090042</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>group_pb_button-group_pb_test-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>group_pb_pushed-Verify group_pb button pushed</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
@@ -2217,10 +2263,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C31" t="n">
-        <v>63865158140033</v>
+        <v>63865158140037</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2228,10 +2274,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>63865158090011</v>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+        <v>63865158090018</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>63865158370013</v>
+      </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
@@ -2239,11 +2291,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>group_pb_pushed-Verify group_pb button pushed</t>
-        </is>
-      </c>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
@@ -2263,10 +2311,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C32" t="n">
-        <v>63865158140034</v>
+        <v>63865158140032</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2274,18 +2322,40 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>63865158090010</v>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+        <v>63865158090013</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>63865158370012</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>group_pb_button-group_pb_test-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>group_pb_pushed-Verify group_pb button pushed</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
@@ -2305,10 +2375,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C33" t="n">
-        <v>63865158140035</v>
+        <v>63865158140033</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2316,39 +2386,23 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>63865158090014</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+        <v>63865158090011</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,4,6,8,8,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,9,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,10,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,11,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,7,8,12,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,13,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,14,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,15,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,4,8,0,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,1,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,2,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,3,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,5,8,4,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,5,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,6,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,7,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,16,6,32,8,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,9,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,10,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,11,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,7,32,12,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,13,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,14,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,15,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,4,32,0,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,1,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,2,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,3,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,5,32,4,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,5,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,6,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,7,126,0,31.84,-327.68,-1,-100]</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Try to test the ELS module on AOT master unit</t>
-        </is>
-      </c>
+          <t>group_pb_pushed-Verify group_pb button pushed</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
@@ -2367,10 +2421,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C34" t="n">
-        <v>63865158140036</v>
+        <v>63865158140034</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2378,13 +2432,9 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>63865158090017</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+        <v>63865158090010</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -2413,10 +2463,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C35" t="n">
-        <v>63865158140031</v>
+        <v>63865158140035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2424,19 +2474,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>63865158090046</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
+        <v>63865158090014</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,4,6,8,8,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,9,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,10,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,11,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,7,8,12,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,13,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,14,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,15,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,4,8,0,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,1,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,2,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,3,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,5,8,4,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,5,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,6,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,7,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,16,6,32,8,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,9,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,10,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,11,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,7,32,12,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,13,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,14,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,15,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,4,32,0,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,1,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,2,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,3,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,5,32,4,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,5,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,6,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,7,126,0,31.84,-327.68,-1,-100]</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Try to test the ELS module on AOT master unit</t>
+        </is>
+      </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
@@ -2455,10 +2525,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C36" t="n">
-        <v>63865158140038</v>
+        <v>63865158140036</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2466,9 +2536,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>63865158090012</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
+        <v>63865158090017</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -2497,10 +2571,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C37" t="n">
-        <v>63865158140039</v>
+        <v>63865158140031</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2508,7 +2582,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>63865158090039</v>
+        <v>63865158090046</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
@@ -2539,10 +2613,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C38" t="n">
-        <v>63865158140040</v>
+        <v>63865158140038</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2550,18 +2624,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>63865158090016</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>63865158370055</t>
-        </is>
-      </c>
+        <v>63865158090012</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
@@ -2589,10 +2655,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C39" t="n">
-        <v>63865158140041</v>
+        <v>63865158140039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2600,18 +2666,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>63865158090015</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>63865158370056</t>
-        </is>
-      </c>
+        <v>63865158090039</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
@@ -2639,10 +2697,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C40" t="n">
-        <v>63865158140042</v>
+        <v>63865158140040</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2650,34 +2708,24 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>63865158090019</v>
+        <v>63865158090016</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>63865158370055</v>
+      </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,13,4,26,0,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,1,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,2,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,3,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,5,26,4,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,5,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,6,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,7,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,6,26,8,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,9,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,10,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,11,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,7,26,12,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,13,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,14,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,15,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,14,0,27,0,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,1,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,2,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,3,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,1,27,4,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,5,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,6,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,7,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,2,27,8,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,9,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,10,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,11,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,3,27,12,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,13,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,14,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,15,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,4,28,0,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,1,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,2,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,3,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,5,28,4,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,5,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,6,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,7,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,6,28,8,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,9,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,10,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,11,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,7,28,12,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,13,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,14,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,15,112,0,31.85,-327.68,-1,-100]</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
@@ -2697,10 +2745,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C41" t="n">
-        <v>63865158140043</v>
+        <v>63865158140041</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2708,58 +2756,30 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>63865158090020</v>
+        <v>63865158090015</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>63865158370056</v>
+      </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>power_on_with_fw-late_livefish_detection-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>csm1_swb_maglan_asic_pcie-Fast_boot_asic_HBI_HW_failure_detected-Asic HBI HW failure detection for csm1_swb_maglan_asic_pcie</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Spectrum-6 in Flash Recovery Mode. 
-Suspect ASIC issue.
-NV : share details </t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>NV</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>SPE</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Waiting Debug</t>
-        </is>
-      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
@@ -2773,21 +2793,45 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>40</v>
-      </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="C42" t="n">
+        <v>63865158140042</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>63865158090019</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,13,4,26,0,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,1,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,2,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,3,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,5,26,4,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,5,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,6,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,7,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,6,26,8,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,9,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,10,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,11,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,7,26,12,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,13,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,14,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,15,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,14,0,27,0,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,1,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,2,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,3,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,1,27,4,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,5,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,6,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,7,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,2,27,8,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,9,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,10,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,11,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,3,27,12,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,13,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,14,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,15,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,4,28,0,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,1,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,2,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,3,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,5,28,4,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,5,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,6,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,7,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,6,28,8,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,9,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,10,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,11,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,7,28,12,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,13,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,14,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,15,112,0,31.85,-327.68,-1,-100]</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
@@ -2807,27 +2851,69 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>41</v>
-      </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="C43" t="n">
+        <v>63865158140043</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>63865158090020</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>power_on_with_fw-late_livefish_detection-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>csm1_swb_maglan_asic_pcie-Fast_boot_asic_HBI_HW_failure_detected-Asic HBI HW failure detection for csm1_swb_maglan_asic_pcie</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spectrum-6 in Flash Recovery Mode. 
+Suspect ASIC issue.
+NV : share details </t>
+        </is>
+      </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>SPE</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Waiting Debug</t>
+        </is>
+      </c>
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
@@ -2841,7 +2927,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
@@ -2875,7 +2961,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
@@ -2909,7 +2995,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
@@ -2943,19 +3029,11 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>45</v>
-      </c>
-      <c r="C47" t="n">
-        <v>63865158140044</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>63865158100002</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
@@ -2985,45 +3063,21 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>46</v>
-      </c>
-      <c r="C48" t="n">
-        <v>63865158140045</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>63865158090025</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,2,2,3,8,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,9,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,10,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,11,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,3,3,12,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,13,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,14,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,15,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,0,3,0,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,1,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,2,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,3,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,1,3,4,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,5,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,6,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,7,10,0,31.47,-327.68,-1,-100]</t>
-        </is>
-      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
@@ -3043,10 +3097,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C49" t="n">
-        <v>63865158140046</v>
+        <v>63865158140044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3054,7 +3108,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>63865158090030</v>
+        <v>63865158100002</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
@@ -3085,10 +3139,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C50" t="n">
-        <v>63865158140047</v>
+        <v>63865158140045</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3096,18 +3150,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>63865158090035</v>
-      </c>
-      <c r="F50" t="inlineStr"/>
+        <v>63865158090025</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,2,2,3,8,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,9,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,10,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,11,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,3,3,12,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,13,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,14,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,15,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,0,3,0,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,1,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,2,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,3,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,1,3,4,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,5,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,6,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,7,10,0,31.47,-327.68,-1,-100]</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
@@ -3127,10 +3197,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C51" t="n">
-        <v>63865158140048</v>
+        <v>63865158140046</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3138,7 +3208,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>63865158090043</v>
+        <v>63865158090030</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
@@ -3169,10 +3239,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C52" t="n">
-        <v>63865158140049</v>
+        <v>63865158140047</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3180,7 +3250,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>63865158090036</v>
+        <v>63865158090035</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
@@ -3211,10 +3281,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C53" t="n">
-        <v>63865158140050</v>
+        <v>63865158140048</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3222,7 +3292,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>63865158090040</v>
+        <v>63865158090043</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
@@ -3253,10 +3323,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C54" t="n">
-        <v>63865158140052</v>
+        <v>63865158140049</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3264,7 +3334,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>63865158090044</v>
+        <v>63865158090036</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
@@ -3295,10 +3365,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C55" t="n">
-        <v>63865158140031</v>
+        <v>63865158140050</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3306,7 +3376,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>63865158090046</v>
+        <v>63865158090040</v>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
@@ -3337,10 +3407,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C56" t="n">
-        <v>63865158140055</v>
+        <v>63865158140052</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3348,7 +3418,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>63865158090045</v>
+        <v>63865158090044</v>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
@@ -3379,11 +3449,19 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>55</v>
-      </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+        <v>53</v>
+      </c>
+      <c r="C57" t="n">
+        <v>63865158140031</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>63865158090046</v>
+      </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
@@ -3413,11 +3491,19 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>56</v>
-      </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="C58" t="n">
+        <v>63865158140055</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>63865158090045</v>
+      </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
@@ -3447,7 +3533,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
@@ -3481,7 +3567,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
@@ -3515,7 +3601,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
@@ -3549,7 +3635,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
@@ -3583,7 +3669,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
@@ -3617,7 +3703,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
@@ -3644,6 +3730,74 @@
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>61</v>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>62</v>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/TS3_mapping.xlsx
+++ b/TS3_mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z66"/>
+  <dimension ref="A1:Z67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1070,14 +1070,10 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>bmc_burn_if_needed-check_bmc_format_and_version_and_burn_if_wrong_chameleon_bmc-ERROR-Exception;</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Failed to ping 192.168.10.30 after -0.5 seconds</t>
-        </is>
-      </c>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
@@ -1766,7 +1762,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -1844,14 +1840,10 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>reset_button-reset_test-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>reset_pushed-Verify reset button pushed</t>
-        </is>
-      </c>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
@@ -1894,10 +1886,14 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -1960,11 +1956,7 @@
       <c r="G24" t="n">
         <v>63865158370009</v>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -2100,17 +2092,33 @@
       <c r="E27" t="n">
         <v>63865158090029</v>
       </c>
-      <c r="F27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="G27" t="n">
         <v>63865158370044</v>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
@@ -2192,8 +2200,14 @@
       <c r="E29" t="n">
         <v>63865158090038</v>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>63865158370025</v>
+      </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
@@ -2234,8 +2248,14 @@
       <c r="E30" t="n">
         <v>63865158090042</v>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>63865158370054</v>
+      </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
@@ -2284,14 +2304,30 @@
       <c r="G31" t="n">
         <v>63865158370013</v>
       </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-21.37,7,0,13,0,49,119.35,12.86,7.91,6.46,-21.37,nan],[prb:nan,7,0,13,0,49,119.35,12.86,7.91,6.46,-21.37,nan],[prp:-21.19,7,0,13,1,49,119.35,12.67,8.1,6.17,-21.19,nan],[prb:nan,7,0,13,1,49,119.35,12.67,8.1,6.17,-21.19,nan],[prp:-21.87,7,0,13,2,49,119.35,12.79,7.98,6.46,-21.87,nan],[prb:nan,7,0,13,2,49,119.35,12.79,7.98,6.46,-21.87,nan],[prp:-22.68,7,0,13,3,49,119.35,12.86,7.91,6.32,-22.68,nan],[prb:nan,7,0,13,3,49,119.35,12.86,7.91,6.32,-22.68,nan],[prp:-19.21,4,6,8,8,31,130.02,12.82,8.32,6.73,-19.21,nan],[prb:nan,4,6,8,8,31,130.02,12.82,8.32,6.73,-19.21,nan],[prp:-20.09,4,6,8,9,31,130.02,12.92,8.22,6.86,-20.09,nan],[prb:nan,4,6,8,9,31,130.02,12.92,8.22,6.86,-20.09,nan],[prp:-22.92,4,6,8,10,31,130.02,12.73,8.41,6.73,-22.92,nan],[prb:nan,4,6,8,10,31,130.02,12.73,8.41,6.73,-22.92,nan],[prp:-22.92,4,6,8,11,31,130.02,12.73,8.41,6.6,-22.92,nan],[prb:nan,4,6,8,11,31,130.02,12.73,8.41,6.6,-22.92,nan]</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
@@ -2369,25 +2405,11 @@
       <c r="Z32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>29</v>
-      </c>
-      <c r="C33" t="n">
-        <v>63865158140033</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>63865158090011</v>
-      </c>
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
@@ -2395,11 +2417,19 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>sbc_storage_usb-passmark-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>group_pb_pushed-Verify group_pb button pushed</t>
+          <t>usb_passmark_pass-Verify usb device passed passmark</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -2421,10 +2451,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C34" t="n">
-        <v>63865158140034</v>
+        <v>63865158140033</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2432,10 +2462,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>63865158090010</v>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+        <v>63865158090011</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>63865158370022</v>
+      </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
@@ -2463,10 +2499,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C35" t="n">
-        <v>63865158140035</v>
+        <v>63865158140034</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2474,39 +2510,25 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>63865158090014</v>
+        <v>63865158090010</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="n">
+        <v>63865158370026</v>
+      </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,4,6,8,8,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,9,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,10,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,11,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,7,8,12,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,13,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,14,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,15,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,4,8,0,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,1,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,2,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,3,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,5,8,4,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,5,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,6,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,7,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,16,6,32,8,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,9,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,10,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,11,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,7,32,12,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,13,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,14,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,15,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,4,32,0,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,1,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,2,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,3,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,5,32,4,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,5,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,6,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,7,126,0,31.84,-327.68,-1,-100]</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Try to test the ELS module on AOT master unit</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
@@ -2525,10 +2547,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C36" t="n">
-        <v>63865158140036</v>
+        <v>63865158140035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2536,23 +2558,41 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>63865158090017</v>
+        <v>63865158090014</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="n">
+        <v>63865158370053</v>
+      </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,4,6,8,8,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,9,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,10,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,11,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,7,8,12,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,13,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,14,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,15,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,4,8,0,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,1,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,2,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,3,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,5,8,4,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,5,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,6,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,7,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,16,6,32,8,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,9,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,10,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,11,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,7,32,12,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,13,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,14,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,15,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,4,32,0,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,1,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,2,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,3,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,5,32,4,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,5,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,6,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,7,126,0,31.84,-327.68,-1,-100]</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Try to test the ELS module on AOT master unit</t>
+        </is>
+      </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
@@ -2571,10 +2611,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C37" t="n">
-        <v>63865158140031</v>
+        <v>63865158140036</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2582,18 +2622,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>63865158090046</v>
-      </c>
-      <c r="F37" t="inlineStr"/>
+        <v>63865158090017</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:13.23,9,0,17,0,65,0,31.17,1.71,13.23,-100],[eocl:13.23,9,0,17,1,65,0,31.17,1.71,13.23,-100],[eocl:13.23,9,0,17,2,65,0,31.17,1.71,13.23,-100],[eocl:13.64,9,0,17,3,65,0,31.17,1.3,13.64,-100],[eocl:14.6,9,1,17,4,66,0,31.09,0.33,14.6,-100],[eocl:14.09,9,1,17,5,66,0,31.09,0.84,14.09,-100],[eocl:14.09,9,1,17,6,66,0,31.09,0.84,14.09,-100],[eocl:13.63,9,1,17,7,66,0,31.09,1.3,13.63,-100],[eocl:13.25,9,2,17,8,67,0,31.3,1.71,13.25,-100],[eocl:13.25,9,2,17,9,67,0,31.3,1.71,13.25,-100],[eocl:13.25,9,2,17,10,67,0,31.3,1.71,13.25,-100],[eocl:12.87,9,2,17,11,67,0,31.3,2.09,12.87,-100],[eocl:13.65,9,3,17,12,68,0,31.26,1.3,13.65,-100],[eocl:13.65,9,3,17,13,68,0,31.26,1.3,13.65,-100],[eocl:13.65,9,3,17,14,68,0,31.26,1.3,13.65,-100],[eocl:13.24,9,3,17,15,68,0,31.26,1.71,13.24,-100]</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
@@ -2613,10 +2669,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C38" t="n">
-        <v>63865158140038</v>
+        <v>63865158140031</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2624,10 +2680,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>63865158090012</v>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
+        <v>63865158090046</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>63865158370021</v>
+      </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
@@ -2655,10 +2717,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C39" t="n">
-        <v>63865158140039</v>
+        <v>63865158140038</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2666,10 +2728,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>63865158090039</v>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+        <v>63865158090012</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>63865158370027</v>
+      </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
@@ -2697,10 +2765,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C40" t="n">
-        <v>63865158140040</v>
+        <v>63865158140039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2708,7 +2776,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>63865158090016</v>
+        <v>63865158090039</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2716,7 +2784,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>63865158370055</v>
+        <v>63865158370020</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -2745,10 +2813,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C41" t="n">
-        <v>63865158140041</v>
+        <v>63865158140040</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2756,7 +2824,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>63865158090015</v>
+        <v>63865158090016</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2764,7 +2832,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>63865158370056</v>
+        <v>63865158370055</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -2793,10 +2861,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C42" t="n">
-        <v>63865158140042</v>
+        <v>63865158140041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2804,34 +2872,32 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>63865158090019</v>
+        <v>63865158090015</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>63865158370056</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,13,4,26,0,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,1,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,2,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,3,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,5,26,4,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,5,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,6,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,7,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,6,26,8,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,9,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,10,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,11,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,7,26,12,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,13,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,14,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,15,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,14,0,27,0,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,1,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,2,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,3,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,1,27,4,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,5,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,6,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,7,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,2,27,8,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,9,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,10,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,11,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,3,27,12,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,13,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,14,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,15,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,4,28,0,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,1,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,2,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,3,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,5,28,4,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,5,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,6,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,7,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,6,28,8,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,9,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,10,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,11,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,7,28,12,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,13,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,14,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,15,112,0,31.85,-327.68,-1,-100]</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
@@ -2851,10 +2917,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C43" t="n">
-        <v>63865158140043</v>
+        <v>63865158140042</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2862,14 +2928,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>63865158090020</v>
+        <v>63865158090019</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>63865158370047</v>
+      </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
@@ -2882,38 +2950,20 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>power_on_with_fw-late_livefish_detection-FAIL-MEASUREMENT;</t>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>csm1_swb_maglan_asic_pcie-Fast_boot_asic_HBI_HW_failure_detected-Asic HBI HW failure detection for csm1_swb_maglan_asic_pcie</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Spectrum-6 in Flash Recovery Mode. 
-Suspect ASIC issue.
-NV : share details </t>
-        </is>
-      </c>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,13,4,26,0,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,1,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,2,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,3,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,5,26,4,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,5,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,6,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,7,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,6,26,8,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,9,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,10,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,11,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,7,26,12,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,13,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,14,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,15,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,14,0,27,0,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,1,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,2,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,3,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,1,27,4,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,5,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,6,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,7,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,2,27,8,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,9,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,10,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,11,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,3,27,12,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,13,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,14,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,15,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,4,28,0,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,1,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,2,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,3,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,5,28,4,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,5,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,6,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,7,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,6,28,8,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,9,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,10,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,11,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,7,28,12,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,13,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,14,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,15,112,0,31.85,-327.68,-1,-100]</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>NV</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>SPE</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Waiting Debug</t>
-        </is>
-      </c>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
@@ -2927,27 +2977,69 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>40</v>
-      </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="C44" t="n">
+        <v>63865158140043</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>63865158090020</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>power_on_with_fw-late_livefish_detection-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>csm1_swb_maglan_asic_pcie-Fast_boot_asic_HBI_HW_failure_detected-Asic HBI HW failure detection for csm1_swb_maglan_asic_pcie</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spectrum-6 in Flash Recovery Mode. 
+Suspect ASIC issue.
+NV : share details </t>
+        </is>
+      </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>SPE</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Waiting Debug</t>
+        </is>
+      </c>
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
@@ -2961,7 +3053,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
@@ -2995,7 +3087,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
@@ -3029,7 +3121,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
@@ -3063,7 +3155,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
@@ -3097,19 +3189,11 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>45</v>
-      </c>
-      <c r="C49" t="n">
-        <v>63865158140044</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>63865158100002</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
@@ -3139,10 +3223,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C50" t="n">
-        <v>63865158140045</v>
+        <v>63865158140044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3150,34 +3234,24 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>63865158090025</v>
+        <v>63865158100002</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>63865158390004</v>
+      </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,2,2,3,8,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,9,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,10,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,11,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,3,3,12,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,13,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,14,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,15,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,0,3,0,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,1,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,2,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,3,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,1,3,4,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,5,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,6,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,7,10,0,31.47,-327.68,-1,-100]</t>
-        </is>
-      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
@@ -3197,10 +3271,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C51" t="n">
-        <v>63865158140046</v>
+        <v>63865158140045</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3208,18 +3282,36 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>63865158090030</v>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
+        <v>63865158090025</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>63865158370045</v>
+      </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,2,2,3,8,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,9,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,10,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,11,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,3,3,12,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,13,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,14,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,15,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,0,3,0,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,1,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,2,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,3,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,1,3,4,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,5,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,6,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,7,10,0,31.47,-327.68,-1,-100]</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
@@ -3239,10 +3331,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C52" t="n">
-        <v>63865158140047</v>
+        <v>63865158140046</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3250,10 +3342,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>63865158090035</v>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
+        <v>63865158090030</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>63865158370048</v>
+      </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
@@ -3281,10 +3379,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C53" t="n">
-        <v>63865158140048</v>
+        <v>63865158140047</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3292,9 +3390,13 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>63865158090043</v>
-      </c>
-      <c r="F53" t="inlineStr"/>
+        <v>63865158090035</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -3323,10 +3425,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C54" t="n">
-        <v>63865158140049</v>
+        <v>63865158140048</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3334,10 +3436,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>63865158090036</v>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
+        <v>63865158090043</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>63865158370043</v>
+      </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
@@ -3365,10 +3473,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C55" t="n">
-        <v>63865158140050</v>
+        <v>63865158140049</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3376,10 +3484,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>63865158090040</v>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
+        <v>63865158090036</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>63865158370041</v>
+      </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
@@ -3407,10 +3521,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C56" t="n">
-        <v>63865158140052</v>
+        <v>63865158140050</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3418,10 +3532,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>63865158090044</v>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
+        <v>63865158090040</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>63865158370050</v>
+      </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
@@ -3449,10 +3569,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C57" t="n">
-        <v>63865158140031</v>
+        <v>63865158140052</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -3460,10 +3580,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>63865158090046</v>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
+        <v>63865158090044</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>63865158370046</v>
+      </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
@@ -3491,10 +3617,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C58" t="n">
-        <v>63865158140055</v>
+        <v>63865158140031</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -3502,10 +3628,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>63865158090045</v>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
+        <v>63865158090046</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>63865158370049</v>
+      </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
@@ -3533,14 +3665,32 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>55</v>
-      </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="C59" t="n">
+        <v>63865158140055</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>63865158090045</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>63865158370023</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
@@ -3567,10 +3717,16 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>56</v>
-      </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="C60" t="n">
+        <v>63865158140051</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
@@ -3601,11 +3757,19 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>57</v>
-      </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+        <v>56</v>
+      </c>
+      <c r="C61" t="n">
+        <v>63865158140056</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>63865158090047</v>
+      </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
@@ -3635,10 +3799,16 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>58</v>
-      </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="C62" t="n">
+        <v>63865158140057</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
@@ -3669,10 +3839,16 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>59</v>
-      </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="C63" t="n">
+        <v>63865158140062</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
@@ -3703,9 +3879,11 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>60</v>
-      </c>
-      <c r="C64" t="inlineStr"/>
+        <v>59</v>
+      </c>
+      <c r="C64" t="n">
+        <v>63865158140060</v>
+      </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
@@ -3737,10 +3915,16 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>61</v>
-      </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="C65" t="n">
+        <v>63865158140061</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
@@ -3771,9 +3955,11 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>62</v>
-      </c>
-      <c r="C66" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="C66" t="n">
+        <v>63865158140058</v>
+      </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
@@ -3798,6 +3984,42 @@
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="inlineStr"/>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>62</v>
+      </c>
+      <c r="C67" t="n">
+        <v>63865158140059</v>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr"/>
+      <c r="X67" t="inlineStr"/>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/TS3_mapping.xlsx
+++ b/TS3_mapping.xlsx
@@ -1012,14 +1012,27 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>High speed fail; ELS2 OE4 Lane0~3 no BER</t>
+          <t>High speed fail; ELS2 OE4 Lane0~3 no BER
+30-SEP : cookbook flow (LPBK remating / cleaning / crossing, Windu cross) -&gt; still fail replace CSM</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>SPE</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Waiting Debug</t>
+        </is>
+      </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
@@ -1663,9 +1676,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spectrum-6 in Flash Recovery Mode. 
-Suspect ASIC issue.
-Tried master PDB then pass. Replacing with new PDB to retest.
+          <t xml:space="preserve">Tried master PDB then pass. Replacing with new PDB to retest.
 29-SEP: Passed with new PDB - &gt; retets on PDB station </t>
         </is>
       </c>
@@ -3020,7 +3031,10 @@
         <is>
           <t xml:space="preserve">Spectrum-6 in Flash Recovery Mode. 
 Suspect ASIC issue.
-NV : share details </t>
+NV : share details 
+JE130526T0960963100707
+E6B171_9_2_8
+</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr"/>
@@ -3646,7 +3660,12 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>PASS FT - Fail at HS cold test GOOD RX , NO BER 
+30-SEP : cookbook flow (LPBK remating / cleaning / crossing, Windu cross) -&gt; still fail replace CSM</t>
+        </is>
+      </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>

--- a/TS3_mapping.xlsx
+++ b/TS3_mapping.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z67"/>
+  <dimension ref="A1:Z69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,8 +912,16 @@
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>MT2640600H02</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>FT</t>
@@ -959,80 +967,35 @@
       <c r="Z7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C8" t="n">
-        <v>63865158140002</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>63865158090001</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>63865158370007</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>CUST</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,2,4,4,0,13,134.85,12.89,8.41,6.6,-2.34,nan],[prb:nan,2,4,4,1,13,134.85,12.79,8.51,6.6,-2.89,nan],[prb:nan,2,4,4,2,13,134.85,12.86,8.44,6.6,-2.45,nan],[prb:nan,2,4,4,3,13,134.85,12.98,8.32,6.73,0.15,nan]</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>High speed fail; ELS2 OE4 Lane0~3 no BER
-30-SEP : cookbook flow (LPBK remating / cleaning / crossing, Windu cross) -&gt; still fail replace CSM</t>
-        </is>
-      </c>
+          <t>system_boot_group-check_sed_state-ERROR-OutOfBandException;</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>NV</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>SPE</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Waiting Debug</t>
-        </is>
-      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
@@ -1046,10 +1009,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>63865158140006</v>
+        <v>63865158140002</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1057,7 +1020,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>63865158090002</v>
+        <v>63865158090001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1065,7 +1028,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>63865158370002</v>
+        <v>63865158370007</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1086,13 +1049,34 @@
           <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,2,4,4,0,13,134.85,12.89,8.41,6.6,-2.34,nan],[prb:nan,2,4,4,1,13,134.85,12.79,8.51,6.6,-2.89,nan],[prb:nan,2,4,4,2,13,134.85,12.86,8.44,6.6,-2.45,nan],[prb:nan,2,4,4,3,13,134.85,12.98,8.32,6.73,0.15,nan]</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>High speed fail; ELS2 OE4 Lane0~3 no BER
+30-SEP : cookbook flow (LPBK remating / cleaning / crossing, Windu cross) -&gt; still fail replace CSM</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>SPE</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Waiting Debug</t>
+        </is>
+      </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
@@ -1106,10 +1090,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>63865158140007</v>
+        <v>63865158140006</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1117,7 +1101,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>63865158090009</v>
+        <v>63865158090002</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1125,11 +1109,11 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>63865158370006</v>
+        <v>63865158370002</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1146,11 +1130,7 @@
           <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,7,2,13,8,51,134.29,12.76,8.52,6.6,-19.63,nan],[prp:-19.63,7,2,13,8,51,134.29,12.76,8.52,6.6,-19.63,nan],[prb:nan,7,2,13,9,51,134.29,12.86,8.42,6.73,-19.75,nan],[prp:-19.75,7,2,13,9,51,134.29,12.86,8.42,6.73,-19.75,nan],[prb:nan,7,2,13,10,51,134.29,12.76,8.52,6.6,-20.97,nan],[prp:-20.97,7,2,13,10,51,134.29,12.76,8.52,6.6,-20.97,nan],[prb:nan,7,2,13,11,51,134.29,12.67,8.61,6.46,-20.97,nan],[prp:-20.97,7,2,13,11,51,134.29,12.67,8.61,6.46,-20.97,nan],[prb:nan,9,7,18,12,72,134.62,12.92,8.37,6.6,-20.6,nan],[prp:-20.6,9,7,18,12,72,134.62,12.92,8.37,6.6,-20.6,nan],[prb:nan,9,7,18,13,72,134.62,12.95,8.34,6.73,-20.41,nan],[prp:-20.41,9,7,18,13,72,134.62,12.95,8.34,6.73,-20.41,nan],[prb:nan,9,7,18,14,72,134.62,13.04,8.25,6.86,-19.47,nan],[prp:-19.47,9,7,18,14,72,134.62,13.04,8.25,6.86,-19.47,nan],[prb:nan,9,7,18,15,72,134.62,12.89,8.4,6.86,-19.75,nan],[prp:-19.75,9,7,18,15,72,134.62,12.89,8.4,6.86,-19.75,nan],[prb:nan,11,0,21,0,81,124.53,12.92,8.03,6.73,-21.19,nan],[prp:-21.19,11,0,21,0,81,124.53,12.92,8.03,6.73,-21.19,nan],[prb:nan,11,0,21,1,81,124.53,12.82,8.13,6.73,-21.87,nan],[prp:-21.87,11,0,21,1,81,124.53,12.82,8.13,6.73,-21.87,nan],[prb:nan,11,0,21,2,81,124.53,12.86,8.09,6.6,-20.6,nan],[prp:-20.6,11,0,21,2,81,124.53,12.86,8.09,6.6,-20.6,nan],[prb:nan,11,0,21,3,81,124.53,12.92,8.03,6.73,-20.41,nan],[prp:-20.41,11,0,21,3,81,124.53,12.92,8.03,6.73,-20.41,nan],[prb:nan,11,6,22,8,87,149.85,12.89,8.87,6.73,-20.09,nan],[prp:-20.09,11,6,22,8,87,149.85,12.89,8.87,6.73,-20.09,nan],[prb:nan,11,6,22,9,87,149.85,13.01,8.75,6.86,-20.09,nan],[prp:-20.09,11,6,22,9,87,149.85,13.01,8.75,6.86,-20.09,nan],[prb:nan,11,6,22,10,87,149.85,12.73,9.03,6.73,-19.47,nan],[prp:-19.47,11,6,22,10,87,149.85,12.73,9.03,6.73,-19.47,nan],[prb:nan,11,6,22,11,87,149.85,12.73,9.03,6.46,-19.47,nan],[prp:-19.47,11,6,22,11,87,149.85,12.73,9.03,6.46,-19.47,nan],[prb:nan,15,3,29,12,116,119.23,12.89,7.87,6.73,-21.87,nan],[prp:-21.87,15,3,29,12,116,119.23,12.89,7.87,6.73,-21.87,nan],[prb:nan,15,3,29,13,116,119.23,12.98,7.78,6.73,-21.87,nan],[prp:-21.87,15,3,29,13,116,119.23,12.98,7.78,6.73,-21.87,nan],[prb:nan,15,3,29,14,116,119.23,12.82,7.94,6.6,-19.32,nan],[prp:-19.32,15,3,29,14,116,119.23,12.82,7.94,6.6,-19.32,nan],[prb:nan,15,3,29,15,116,119.23,12.89,7.87,6.73,-19.91,nan],[prp:-19.91,15,3,29,15,116,119.23,12.89,7.87,6.73,-19.91,nan]</t>
-        </is>
-      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -1170,10 +1150,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>63865158140008</v>
+        <v>63865158140007</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1181,7 +1161,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>63865158090006</v>
+        <v>63865158090009</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1189,18 +1169,14 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>63865158370004</v>
+        <v>63865158370006</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1216,7 +1192,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,7,4,14,0,53,128.58,13.01,8.08,6.73,-19.91,nan],[prp:-19.91,7,4,14,0,53,128.58,13.01,8.08,6.73,-19.91,nan],[prb:nan,7,4,14,1,53,128.58,12.79,8.3,6.73,-19.91,nan],[prp:-19.91,7,4,14,1,53,128.58,12.79,8.3,6.73,-19.91,nan],[prb:nan,7,4,14,2,53,128.58,13.04,8.05,6.99,-20.09,nan],[prp:-20.09,7,4,14,2,53,128.58,13.04,8.05,6.99,-20.09,nan],[prb:nan,7,4,14,3,53,128.58,12.98,8.11,6.86,-19.91,nan],[prp:-19.91,7,4,14,3,53,128.58,12.98,8.11,6.86,-19.91,nan]</t>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,7,2,13,8,51,134.29,12.76,8.52,6.6,-19.63,nan],[prp:-19.63,7,2,13,8,51,134.29,12.76,8.52,6.6,-19.63,nan],[prb:nan,7,2,13,9,51,134.29,12.86,8.42,6.73,-19.75,nan],[prp:-19.75,7,2,13,9,51,134.29,12.86,8.42,6.73,-19.75,nan],[prb:nan,7,2,13,10,51,134.29,12.76,8.52,6.6,-20.97,nan],[prp:-20.97,7,2,13,10,51,134.29,12.76,8.52,6.6,-20.97,nan],[prb:nan,7,2,13,11,51,134.29,12.67,8.61,6.46,-20.97,nan],[prp:-20.97,7,2,13,11,51,134.29,12.67,8.61,6.46,-20.97,nan],[prb:nan,9,7,18,12,72,134.62,12.92,8.37,6.6,-20.6,nan],[prp:-20.6,9,7,18,12,72,134.62,12.92,8.37,6.6,-20.6,nan],[prb:nan,9,7,18,13,72,134.62,12.95,8.34,6.73,-20.41,nan],[prp:-20.41,9,7,18,13,72,134.62,12.95,8.34,6.73,-20.41,nan],[prb:nan,9,7,18,14,72,134.62,13.04,8.25,6.86,-19.47,nan],[prp:-19.47,9,7,18,14,72,134.62,13.04,8.25,6.86,-19.47,nan],[prb:nan,9,7,18,15,72,134.62,12.89,8.4,6.86,-19.75,nan],[prp:-19.75,9,7,18,15,72,134.62,12.89,8.4,6.86,-19.75,nan],[prb:nan,11,0,21,0,81,124.53,12.92,8.03,6.73,-21.19,nan],[prp:-21.19,11,0,21,0,81,124.53,12.92,8.03,6.73,-21.19,nan],[prb:nan,11,0,21,1,81,124.53,12.82,8.13,6.73,-21.87,nan],[prp:-21.87,11,0,21,1,81,124.53,12.82,8.13,6.73,-21.87,nan],[prb:nan,11,0,21,2,81,124.53,12.86,8.09,6.6,-20.6,nan],[prp:-20.6,11,0,21,2,81,124.53,12.86,8.09,6.6,-20.6,nan],[prb:nan,11,0,21,3,81,124.53,12.92,8.03,6.73,-20.41,nan],[prp:-20.41,11,0,21,3,81,124.53,12.92,8.03,6.73,-20.41,nan],[prb:nan,11,6,22,8,87,149.85,12.89,8.87,6.73,-20.09,nan],[prp:-20.09,11,6,22,8,87,149.85,12.89,8.87,6.73,-20.09,nan],[prb:nan,11,6,22,9,87,149.85,13.01,8.75,6.86,-20.09,nan],[prp:-20.09,11,6,22,9,87,149.85,13.01,8.75,6.86,-20.09,nan],[prb:nan,11,6,22,10,87,149.85,12.73,9.03,6.73,-19.47,nan],[prp:-19.47,11,6,22,10,87,149.85,12.73,9.03,6.73,-19.47,nan],[prb:nan,11,6,22,11,87,149.85,12.73,9.03,6.46,-19.47,nan],[prp:-19.47,11,6,22,11,87,149.85,12.73,9.03,6.46,-19.47,nan],[prb:nan,15,3,29,12,116,119.23,12.89,7.87,6.73,-21.87,nan],[prp:-21.87,15,3,29,12,116,119.23,12.89,7.87,6.73,-21.87,nan],[prb:nan,15,3,29,13,116,119.23,12.98,7.78,6.73,-21.87,nan],[prp:-21.87,15,3,29,13,116,119.23,12.98,7.78,6.73,-21.87,nan],[prb:nan,15,3,29,14,116,119.23,12.82,7.94,6.6,-19.32,nan],[prp:-19.32,15,3,29,14,116,119.23,12.82,7.94,6.6,-19.32,nan],[prb:nan,15,3,29,15,116,119.23,12.89,7.87,6.73,-19.91,nan],[prp:-19.91,15,3,29,15,116,119.23,12.89,7.87,6.73,-19.91,nan]</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1238,10 +1214,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" t="n">
-        <v>63865158140009</v>
+        <v>63865158140008</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1249,7 +1225,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>63865158090007</v>
+        <v>63865158090006</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1257,7 +1233,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>63865158370008</v>
+        <v>63865158370004</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1270,11 +1246,31 @@
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>MT2640600GZ1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,7,4,14,0,53,128.58,13.01,8.08,6.73,-19.91,nan],[prp:-19.91,7,4,14,0,53,128.58,13.01,8.08,6.73,-19.91,nan],[prb:nan,7,4,14,1,53,128.58,12.79,8.3,6.73,-19.91,nan],[prp:-19.91,7,4,14,1,53,128.58,12.79,8.3,6.73,-19.91,nan],[prb:nan,7,4,14,2,53,128.58,13.04,8.05,6.99,-20.09,nan],[prp:-20.09,7,4,14,2,53,128.58,13.04,8.05,6.99,-20.09,nan],[prb:nan,7,4,14,3,53,128.58,12.98,8.11,6.86,-19.91,nan],[prp:-19.91,7,4,14,3,53,128.58,12.98,8.11,6.86,-19.91,nan]</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
@@ -1288,33 +1284,13 @@
       <c r="Z12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>10</v>
-      </c>
-      <c r="C13" t="n">
-        <v>63865158140010</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>63865158090005</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>63865158370051</v>
-      </c>
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
@@ -1322,42 +1298,21 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>AOT</t>
+          <t>CUST</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,14,0,27,0,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,0,27,1,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,0,27,2,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,0,27,3,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,1,27,4,106,0,31.17,-327.68,-1,-100],[eocl:-1.0,14,1,27,5,106,0,31.17,-327.68,-1,-100],[eocl:-1.0,14,1,27,6,106,0,31.17,-327.68,-1,-100],[eocl:-1.0,14,1,27,7,106,0,31.17,-327.68,-1,-100]</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Fiber fracture, replace E-FBK
-Replaced FBK then pass</t>
-        </is>
-      </c>
+          <t>laser_tests_prerequisites-linkup_setup-ERROR-ShellException;</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>FXV</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Peter</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
@@ -1371,10 +1326,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C14" t="n">
-        <v>63865158140012</v>
+        <v>63865158140009</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1382,7 +1337,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>63865158090027</v>
+        <v>63865158090007</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1390,10 +1345,18 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>63865158370028</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+        <v>63865158370008</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -1419,10 +1382,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>63865158140016</v>
+        <v>63865158140010</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1430,7 +1393,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>63865158090028</v>
+        <v>63865158090005</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1438,22 +1401,51 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>63865158370019</v>
+        <v>63865158370051</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,14,0,27,0,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,0,27,1,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,0,27,2,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,0,27,3,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,1,27,4,106,0,31.17,-327.68,-1,-100],[eocl:-1.0,14,1,27,5,106,0,31.17,-327.68,-1,-100],[eocl:-1.0,14,1,27,6,106,0,31.17,-327.68,-1,-100],[eocl:-1.0,14,1,27,7,106,0,31.17,-327.68,-1,-100]</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Fiber fracture, replace E-FBK
+Replaced FBK then pass</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
@@ -1467,10 +1459,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>63865158140015</v>
+        <v>63865158140012</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1478,7 +1470,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>63865158090024</v>
+        <v>63865158090027</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1486,7 +1478,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>63865158370015</v>
+        <v>63865158370028</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -1515,10 +1507,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>63865158140014</v>
+        <v>63865158140016</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1526,7 +1518,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>63865158090026</v>
+        <v>63865158090028</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1534,52 +1526,22 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>63865158370052</v>
+        <v>63865158370019</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:14.08,7,3,13,12,52,0,31.06,0.84,14.08,-100],[eocl:13.62,7,3,13,13,52,0,31.06,1.3,13.62,-100],[eocl:13.62,7,3,13,14,52,0,31.06,1.3,13.62,-100],[eocl:13.21,7,3,13,15,52,0,31.06,1.71,13.21,-100]</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>FBK stand alone IL still abnormal
-Need to replace an W-FBK
-Replaced FBK then pass</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>FXV</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Peter</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
@@ -1593,15 +1555,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>63865158140013</v>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+        <v>63865158140015</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>63865158090024</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>63865158370015</v>
+      </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
@@ -1629,10 +1603,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>63865158140019</v>
+        <v>63865158140014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1640,7 +1614,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>63865158090034</v>
+        <v>63865158090026</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1648,13 +1622,9 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>63865158370042</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
+        <v>63865158370052</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -1666,18 +1636,19 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>power_on-validate_power_converter_dma_data-ERROR-Exception;</t>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>csm1_asic_brd__pdb_node_controller': 'write_i2c_block' function failed: device=/dev/mst/192.168.10.20:23108,@dev@mst@dev-i2c-6, i2c_addr=0x60, addr_width=1, reg_addr=0xc7, size=2</t>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:14.08,7,3,13,12,52,0,31.06,0.84,14.08,-100],[eocl:13.62,7,3,13,13,52,0,31.06,1.3,13.62,-100],[eocl:13.62,7,3,13,14,52,0,31.06,1.3,13.62,-100],[eocl:13.21,7,3,13,15,52,0,31.06,1.71,13.21,-100]</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tried master PDB then pass. Replacing with new PDB to retest.
-29-SEP: Passed with new PDB - &gt; retets on PDB station </t>
+          <t>FBK stand alone IL still abnormal
+Need to replace an W-FBK
+Replaced FBK then pass</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
@@ -1689,12 +1660,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Joy</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>On-going</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="V19" t="inlineStr"/>
@@ -1704,9 +1675,17 @@
       <c r="Z19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>15</v>
+      </c>
+      <c r="C20" t="n">
+        <v>63865158140013</v>
+      </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
@@ -1716,21 +1695,9 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-17.93,15,7,30,12,120,139.29,12.92,8.52,6.86,-17.93,nan],[prb:nan,15,7,30,12,120,139.29,12.92,8.52,6.86,-17.93,nan],[prp:-18.48,15,7,30,13,120,139.29,13.01,8.43,6.86,-18.48,nan],[prb:nan,15,7,30,13,120,139.29,13.01,8.43,6.86,-18.48,nan],[prp:-20.97,15,7,30,14,120,139.29,12.89,8.55,6.73,-20.97,nan],[prb:nan,15,7,30,14,120,139.29,12.89,8.55,6.73,-20.97,nan],[prp:-20.97,15,7,30,15,120,139.29,12.82,8.62,6.73,-20.97,nan],[prb:nan,15,7,30,15,120,139.29,12.82,8.62,6.73,-20.97,nan]</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
@@ -1750,10 +1717,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>63865158140020</v>
+        <v>63865158140019</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1761,7 +1728,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>63865158090033</v>
+        <v>63865158090034</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1769,11 +1736,11 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>63865158370017</v>
+        <v>63865158370042</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -1782,25 +1749,42 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>AOT</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+          <t>power_on-validate_power_converter_dma_data-ERROR-Exception;</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-20.41,7,4,14,0,53,109.98,12.86,7.55,6.73,-20.41,nan],[prb:nan,7,4,14,0,53,109.98,12.86,7.55,6.73,-20.41,nan],[prp:-19.47,7,4,14,1,53,109.98,12.7,7.71,6.6,-19.47,nan],[prb:nan,7,4,14,1,53,109.98,12.7,7.71,6.6,-19.47,nan],[prp:-22.68,7,4,14,2,53,109.98,12.92,7.49,6.6,-22.68,nan],[prb:nan,7,4,14,2,53,109.98,12.92,7.49,6.6,-22.68,nan],[prp:-21.87,7,4,14,3,53,109.98,12.89,7.52,6.6,-21.87,nan],[prb:nan,7,4,14,3,53,109.98,12.89,7.52,6.6,-21.87,nan],[prp:-19.91,11,4,22,0,85,119.68,12.76,8.02,6.46,-19.91,nan],[prb:nan,11,4,22,0,85,119.68,12.76,8.02,6.46,-19.91,nan],[prp:-20.22,11,4,22,1,85,119.68,12.76,8.02,6.32,-20.22,nan],[prb:nan,11,4,22,1,85,119.68,12.76,8.02,6.32,-20.22,nan],[prp:-20.97,11,4,22,2,85,119.68,12.79,7.99,6.46,-20.97,nan],[prb:nan,11,4,22,2,85,119.68,12.79,7.99,6.46,-20.97,nan],[prp:-20.97,11,4,22,3,85,119.68,12.86,7.92,6.46,-20.97,nan],[prb:nan,11,4,22,3,85,119.68,12.86,7.92,6.46,-20.97,nan]</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr"/>
+          <t>csm1_asic_brd__pdb_node_controller': 'write_i2c_block' function failed: device=/dev/mst/192.168.10.20:23108,@dev@mst@dev-i2c-6, i2c_addr=0x60, addr_width=1, reg_addr=0xc7, size=2</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tried master PDB then pass. Replacing with new PDB to retest.
+29-SEP: Passed with new PDB - &gt; retets on PDB station </t>
+        </is>
+      </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Joy</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>On-going</t>
+        </is>
+      </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
@@ -1808,38 +1792,14 @@
       <c r="Z21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>18</v>
-      </c>
-      <c r="C22" t="n">
-        <v>63865158140021</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>63865158090032</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>63865158370018</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -1854,7 +1814,11 @@
           <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-17.93,15,7,30,12,120,139.29,12.92,8.52,6.86,-17.93,nan],[prb:nan,15,7,30,12,120,139.29,12.92,8.52,6.86,-17.93,nan],[prp:-18.48,15,7,30,13,120,139.29,13.01,8.43,6.86,-18.48,nan],[prb:nan,15,7,30,13,120,139.29,13.01,8.43,6.86,-18.48,nan],[prp:-20.97,15,7,30,14,120,139.29,12.89,8.55,6.73,-20.97,nan],[prb:nan,15,7,30,14,120,139.29,12.89,8.55,6.73,-20.97,nan],[prp:-20.97,15,7,30,15,120,139.29,12.82,8.62,6.73,-20.97,nan],[prb:nan,15,7,30,15,120,139.29,12.82,8.62,6.73,-20.97,nan]</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
@@ -1874,10 +1838,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C23" t="n">
-        <v>63865158140022</v>
+        <v>63865158140020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1885,7 +1849,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>63865158090037</v>
+        <v>63865158090033</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1893,18 +1857,14 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>63865158370014</v>
+        <v>63865158370017</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -1920,14 +1880,10 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,12,6,24,8,95,119.32,12.89,7.88,6.6,-20.09,nan],[prp:-20.09,12,6,24,8,95,119.32,12.89,7.88,6.6,-20.09,nan],[prb:nan,12,6,24,9,95,119.32,12.89,7.88,6.46,-19.75,nan],[prp:-19.75,12,6,24,9,95,119.32,12.89,7.88,6.46,-19.75,nan],[prb:nan,12,6,24,10,95,119.32,12.82,7.95,6.46,-22.68,nan],[prp:-22.68,12,6,24,10,95,119.32,12.82,7.95,6.46,-22.68,nan],[prb:nan,12,6,24,11,95,119.32,12.73,8.04,6.46,-22.68,nan],[prp:-22.68,12,6,24,11,95,119.32,12.73,8.04,6.46,-22.68,nan],[prb:nan,14,5,28,4,110,139.47,12.7,8.74,6.73,-2.79,nan],[prb:nan,14,5,28,5,110,139.47,12.61,8.83,6.73,-2.33,nan],[prb:nan,14,5,28,6,110,139.47,12.67,8.77,6.73,-2.66,nan],[prb:nan,14,5,28,7,110,139.47,12.76,8.68,6.73,-18.57,nan],[prp:-18.57,14,5,28,7,110,139.47,12.76,8.68,6.73,-18.57,nan],[prb:nan,5,1,9,4,34,144.37,13.18,8.41,6.86,-21.87,nan],[prp:-21.87,5,1,9,4,34,144.37,13.18,8.41,6.86,-21.87,nan],[prb:nan,5,1,9,5,34,144.37,13.01,8.58,6.73,-21.87,nan],[prp:-21.87,5,1,9,5,34,144.37,13.01,8.58,6.73,-21.87,nan],[prb:nan,5,1,9,6,34,144.37,13.15,8.44,6.73,-22.68,nan],[prp:-22.68,5,1,9,6,34,144.37,13.15,8.44,6.73,-22.68,nan],[prb:nan,5,1,9,7,34,144.37,13.23,8.36,6.99,-22.08,nan],[prp:-22.08,5,1,9,7,34,144.37,13.23,8.36,6.99,-22.08,nan],[prp:-5.2,2,1,3,6,10,129.27,12.76,8.35,6.6,-5.2,8e-10]</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>found FBK broken - FXV to understand what happened and send RC report</t>
-        </is>
-      </c>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-20.41,7,4,14,0,53,109.98,12.86,7.55,6.73,-20.41,nan],[prb:nan,7,4,14,0,53,109.98,12.86,7.55,6.73,-20.41,nan],[prp:-19.47,7,4,14,1,53,109.98,12.7,7.71,6.6,-19.47,nan],[prb:nan,7,4,14,1,53,109.98,12.7,7.71,6.6,-19.47,nan],[prp:-22.68,7,4,14,2,53,109.98,12.92,7.49,6.6,-22.68,nan],[prb:nan,7,4,14,2,53,109.98,12.92,7.49,6.6,-22.68,nan],[prp:-21.87,7,4,14,3,53,109.98,12.89,7.52,6.6,-21.87,nan],[prb:nan,7,4,14,3,53,109.98,12.89,7.52,6.6,-21.87,nan],[prp:-19.91,11,4,22,0,85,119.68,12.76,8.02,6.46,-19.91,nan],[prb:nan,11,4,22,0,85,119.68,12.76,8.02,6.46,-19.91,nan],[prp:-20.22,11,4,22,1,85,119.68,12.76,8.02,6.32,-20.22,nan],[prb:nan,11,4,22,1,85,119.68,12.76,8.02,6.32,-20.22,nan],[prp:-20.97,11,4,22,2,85,119.68,12.79,7.99,6.46,-20.97,nan],[prb:nan,11,4,22,2,85,119.68,12.79,7.99,6.46,-20.97,nan],[prp:-20.97,11,4,22,3,85,119.68,12.86,7.92,6.46,-20.97,nan],[prb:nan,11,4,22,3,85,119.68,12.86,7.92,6.46,-20.97,nan]</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
@@ -1946,10 +1902,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C24" t="n">
-        <v>63865158140023</v>
+        <v>63865158140021</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1957,7 +1913,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>63865158090031</v>
+        <v>63865158090032</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1965,15 +1921,27 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>63865158370009</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
+        <v>63865158370018</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
@@ -1994,10 +1962,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C25" t="n">
-        <v>63865158140025</v>
+        <v>63865158140022</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2005,7 +1973,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>63865158090022</v>
+        <v>63865158090037</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2013,16 +1981,36 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>63865158370010</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+        <v>63865158370014</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,12,6,24,8,95,119.32,12.89,7.88,6.6,-20.09,nan],[prp:-20.09,12,6,24,8,95,119.32,12.89,7.88,6.6,-20.09,nan],[prb:nan,12,6,24,9,95,119.32,12.89,7.88,6.46,-19.75,nan],[prp:-19.75,12,6,24,9,95,119.32,12.89,7.88,6.46,-19.75,nan],[prb:nan,12,6,24,10,95,119.32,12.82,7.95,6.46,-22.68,nan],[prp:-22.68,12,6,24,10,95,119.32,12.82,7.95,6.46,-22.68,nan],[prb:nan,12,6,24,11,95,119.32,12.73,8.04,6.46,-22.68,nan],[prp:-22.68,12,6,24,11,95,119.32,12.73,8.04,6.46,-22.68,nan],[prb:nan,14,5,28,4,110,139.47,12.7,8.74,6.73,-2.79,nan],[prb:nan,14,5,28,5,110,139.47,12.61,8.83,6.73,-2.33,nan],[prb:nan,14,5,28,6,110,139.47,12.67,8.77,6.73,-2.66,nan],[prb:nan,14,5,28,7,110,139.47,12.76,8.68,6.73,-18.57,nan],[prp:-18.57,14,5,28,7,110,139.47,12.76,8.68,6.73,-18.57,nan],[prb:nan,5,1,9,4,34,144.37,13.18,8.41,6.86,-21.87,nan],[prp:-21.87,5,1,9,4,34,144.37,13.18,8.41,6.86,-21.87,nan],[prb:nan,5,1,9,5,34,144.37,13.01,8.58,6.73,-21.87,nan],[prp:-21.87,5,1,9,5,34,144.37,13.01,8.58,6.73,-21.87,nan],[prb:nan,5,1,9,6,34,144.37,13.15,8.44,6.73,-22.68,nan],[prp:-22.68,5,1,9,6,34,144.37,13.15,8.44,6.73,-22.68,nan],[prb:nan,5,1,9,7,34,144.37,13.23,8.36,6.99,-22.08,nan],[prp:-22.08,5,1,9,7,34,144.37,13.23,8.36,6.99,-22.08,nan],[prp:-5.2,2,1,3,6,10,129.27,12.76,8.35,6.6,-5.2,8e-10]</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
@@ -2042,10 +2030,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C26" t="n">
-        <v>63865158140024</v>
+        <v>63865158140023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2053,7 +2041,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>63865158090023</v>
+        <v>63865158090031</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2061,7 +2049,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>63865158370016</v>
+        <v>63865158370009</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -2090,10 +2078,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C27" t="n">
-        <v>63865158140026</v>
+        <v>63865158140025</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2101,7 +2089,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>63865158090029</v>
+        <v>63865158090022</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2109,27 +2097,15 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>63865158370044</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
+        <v>63865158370010</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
@@ -2150,10 +2126,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C28" t="n">
-        <v>63865158140028</v>
+        <v>63865158140024</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2161,7 +2137,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>63865158090021</v>
+        <v>63865158090023</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2169,7 +2145,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>63865158370024</v>
+        <v>63865158370016</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2198,10 +2174,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C29" t="n">
-        <v>63865158140029</v>
+        <v>63865158140026</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2209,7 +2185,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>63865158090038</v>
+        <v>63865158090029</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2217,15 +2193,27 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>63865158370025</v>
-      </c>
-      <c r="H29" t="inlineStr"/>
+        <v>63865158370044</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
@@ -2246,10 +2234,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C30" t="n">
-        <v>63865158140030</v>
+        <v>63865158140028</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2257,7 +2245,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>63865158090042</v>
+        <v>63865158090021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2265,7 +2253,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>63865158370054</v>
+        <v>63865158370024</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -2294,10 +2282,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C31" t="n">
-        <v>63865158140037</v>
+        <v>63865158140029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2305,7 +2293,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>63865158090018</v>
+        <v>63865158090038</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2313,32 +2301,16 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>63865158370013</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+        <v>63865158370025</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-21.37,7,0,13,0,49,119.35,12.86,7.91,6.46,-21.37,nan],[prb:nan,7,0,13,0,49,119.35,12.86,7.91,6.46,-21.37,nan],[prp:-21.19,7,0,13,1,49,119.35,12.67,8.1,6.17,-21.19,nan],[prb:nan,7,0,13,1,49,119.35,12.67,8.1,6.17,-21.19,nan],[prp:-21.87,7,0,13,2,49,119.35,12.79,7.98,6.46,-21.87,nan],[prb:nan,7,0,13,2,49,119.35,12.79,7.98,6.46,-21.87,nan],[prp:-22.68,7,0,13,3,49,119.35,12.86,7.91,6.32,-22.68,nan],[prb:nan,7,0,13,3,49,119.35,12.86,7.91,6.32,-22.68,nan],[prp:-19.21,4,6,8,8,31,130.02,12.82,8.32,6.73,-19.21,nan],[prb:nan,4,6,8,8,31,130.02,12.82,8.32,6.73,-19.21,nan],[prp:-20.09,4,6,8,9,31,130.02,12.92,8.22,6.86,-20.09,nan],[prb:nan,4,6,8,9,31,130.02,12.92,8.22,6.86,-20.09,nan],[prp:-22.92,4,6,8,10,31,130.02,12.73,8.41,6.73,-22.92,nan],[prb:nan,4,6,8,10,31,130.02,12.73,8.41,6.73,-22.92,nan],[prp:-22.92,4,6,8,11,31,130.02,12.73,8.41,6.6,-22.92,nan],[prb:nan,4,6,8,11,31,130.02,12.73,8.41,6.6,-22.92,nan]</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
@@ -2358,10 +2330,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C32" t="n">
-        <v>63865158140032</v>
+        <v>63865158140030</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2369,7 +2341,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>63865158090013</v>
+        <v>63865158090042</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2377,32 +2349,16 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>63865158370012</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
+        <v>63865158370054</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>group_pb_button-group_pb_test-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>group_pb_pushed-Verify group_pb button pushed</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
@@ -2416,14 +2372,38 @@
       <c r="Z32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>27</v>
+      </c>
+      <c r="C33" t="n">
+        <v>63865158140037</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>63865158090018</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>63865158370013</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
@@ -2435,12 +2415,12 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>sbc_storage_usb-passmark-FAIL-MEASUREMENT;</t>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>usb_passmark_pass-Verify usb device passed passmark</t>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-21.37,7,0,13,0,49,119.35,12.86,7.91,6.46,-21.37,nan],[prb:nan,7,0,13,0,49,119.35,12.86,7.91,6.46,-21.37,nan],[prp:-21.19,7,0,13,1,49,119.35,12.67,8.1,6.17,-21.19,nan],[prb:nan,7,0,13,1,49,119.35,12.67,8.1,6.17,-21.19,nan],[prp:-21.87,7,0,13,2,49,119.35,12.79,7.98,6.46,-21.87,nan],[prb:nan,7,0,13,2,49,119.35,12.79,7.98,6.46,-21.87,nan],[prp:-22.68,7,0,13,3,49,119.35,12.86,7.91,6.32,-22.68,nan],[prb:nan,7,0,13,3,49,119.35,12.86,7.91,6.32,-22.68,nan],[prp:-19.21,4,6,8,8,31,130.02,12.82,8.32,6.73,-19.21,nan],[prb:nan,4,6,8,8,31,130.02,12.82,8.32,6.73,-19.21,nan],[prp:-20.09,4,6,8,9,31,130.02,12.92,8.22,6.86,-20.09,nan],[prb:nan,4,6,8,9,31,130.02,12.92,8.22,6.86,-20.09,nan],[prp:-22.92,4,6,8,10,31,130.02,12.73,8.41,6.73,-22.92,nan],[prb:nan,4,6,8,10,31,130.02,12.73,8.41,6.73,-22.92,nan],[prp:-22.92,4,6,8,11,31,130.02,12.73,8.41,6.6,-22.92,nan],[prb:nan,4,6,8,11,31,130.02,12.73,8.41,6.6,-22.92,nan]</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -2462,10 +2442,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C34" t="n">
-        <v>63865158140033</v>
+        <v>63865158140032</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2473,7 +2453,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>63865158090011</v>
+        <v>63865158090013</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2481,16 +2461,32 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>63865158370022</v>
-      </c>
-      <c r="H34" t="inlineStr"/>
+        <v>63865158370012</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>group_pb_button-group_pb_test-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>group_pb_pushed-Verify group_pb button pushed</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
@@ -2504,41 +2500,33 @@
       <c r="Z34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>30</v>
-      </c>
-      <c r="C35" t="n">
-        <v>63865158140034</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>63865158090010</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>63865158370026</v>
-      </c>
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>sbc_storage_usb-passmark-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>usb_passmark_pass-Verify usb device passed passmark</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
@@ -2558,10 +2546,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C36" t="n">
-        <v>63865158140035</v>
+        <v>63865158140033</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2569,7 +2557,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>63865158090014</v>
+        <v>63865158090011</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2577,33 +2565,17 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>63865158370053</v>
+        <v>63865158370022</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,4,6,8,8,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,9,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,10,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,11,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,7,8,12,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,13,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,14,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,15,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,4,8,0,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,1,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,2,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,3,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,5,8,4,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,5,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,6,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,7,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,16,6,32,8,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,9,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,10,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,11,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,7,32,12,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,13,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,14,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,15,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,4,32,0,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,1,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,2,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,3,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,5,32,4,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,5,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,6,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,7,126,0,31.84,-327.68,-1,-100]</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Try to test the ELS module on AOT master unit</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
@@ -2622,10 +2594,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C37" t="n">
-        <v>63865158140036</v>
+        <v>63865158140034</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2633,34 +2605,24 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>63865158090017</v>
+        <v>63865158090010</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>63865158370026</v>
+      </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:13.23,9,0,17,0,65,0,31.17,1.71,13.23,-100],[eocl:13.23,9,0,17,1,65,0,31.17,1.71,13.23,-100],[eocl:13.23,9,0,17,2,65,0,31.17,1.71,13.23,-100],[eocl:13.64,9,0,17,3,65,0,31.17,1.3,13.64,-100],[eocl:14.6,9,1,17,4,66,0,31.09,0.33,14.6,-100],[eocl:14.09,9,1,17,5,66,0,31.09,0.84,14.09,-100],[eocl:14.09,9,1,17,6,66,0,31.09,0.84,14.09,-100],[eocl:13.63,9,1,17,7,66,0,31.09,1.3,13.63,-100],[eocl:13.25,9,2,17,8,67,0,31.3,1.71,13.25,-100],[eocl:13.25,9,2,17,9,67,0,31.3,1.71,13.25,-100],[eocl:13.25,9,2,17,10,67,0,31.3,1.71,13.25,-100],[eocl:12.87,9,2,17,11,67,0,31.3,2.09,12.87,-100],[eocl:13.65,9,3,17,12,68,0,31.26,1.3,13.65,-100],[eocl:13.65,9,3,17,13,68,0,31.26,1.3,13.65,-100],[eocl:13.65,9,3,17,14,68,0,31.26,1.3,13.65,-100],[eocl:13.24,9,3,17,15,68,0,31.26,1.71,13.24,-100]</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
@@ -2680,10 +2642,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C38" t="n">
-        <v>63865158140031</v>
+        <v>63865158140035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2691,7 +2653,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>63865158090046</v>
+        <v>63865158090014</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2699,17 +2661,33 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>63865158370021</v>
+        <v>63865158370053</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,4,6,8,8,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,9,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,10,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,11,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,7,8,12,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,13,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,14,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,15,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,4,8,0,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,1,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,2,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,3,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,5,8,4,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,5,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,6,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,7,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,16,6,32,8,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,9,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,10,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,11,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,7,32,12,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,13,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,14,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,15,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,4,32,0,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,1,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,2,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,3,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,5,32,4,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,5,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,6,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,7,126,0,31.84,-327.68,-1,-100]</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Try to test the ELS module on AOT master unit</t>
+        </is>
+      </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
@@ -2728,10 +2706,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C39" t="n">
-        <v>63865158140038</v>
+        <v>63865158140036</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2739,24 +2717,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>63865158090012</v>
+        <v>63865158090017</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>63865158370027</v>
-      </c>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:13.23,9,0,17,0,65,0,31.17,1.71,13.23,-100],[eocl:13.23,9,0,17,1,65,0,31.17,1.71,13.23,-100],[eocl:13.23,9,0,17,2,65,0,31.17,1.71,13.23,-100],[eocl:13.64,9,0,17,3,65,0,31.17,1.3,13.64,-100],[eocl:14.6,9,1,17,4,66,0,31.09,0.33,14.6,-100],[eocl:14.09,9,1,17,5,66,0,31.09,0.84,14.09,-100],[eocl:14.09,9,1,17,6,66,0,31.09,0.84,14.09,-100],[eocl:13.63,9,1,17,7,66,0,31.09,1.3,13.63,-100],[eocl:13.25,9,2,17,8,67,0,31.3,1.71,13.25,-100],[eocl:13.25,9,2,17,9,67,0,31.3,1.71,13.25,-100],[eocl:13.25,9,2,17,10,67,0,31.3,1.71,13.25,-100],[eocl:12.87,9,2,17,11,67,0,31.3,2.09,12.87,-100],[eocl:13.65,9,3,17,12,68,0,31.26,1.3,13.65,-100],[eocl:13.65,9,3,17,13,68,0,31.26,1.3,13.65,-100],[eocl:13.65,9,3,17,14,68,0,31.26,1.3,13.65,-100],[eocl:13.24,9,3,17,15,68,0,31.26,1.71,13.24,-100]</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
@@ -2776,10 +2764,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C40" t="n">
-        <v>63865158140039</v>
+        <v>63865158140031</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2787,7 +2775,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>63865158090039</v>
+        <v>63865158090046</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2795,7 +2783,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>63865158370020</v>
+        <v>63865158370021</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -2824,10 +2812,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C41" t="n">
-        <v>63865158140040</v>
+        <v>63865158140038</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2835,7 +2823,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>63865158090016</v>
+        <v>63865158090012</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2843,7 +2831,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>63865158370055</v>
+        <v>63865158370027</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -2872,10 +2860,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C42" t="n">
-        <v>63865158140041</v>
+        <v>63865158140039</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2883,7 +2871,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>63865158090015</v>
+        <v>63865158090039</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2891,18 +2879,10 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>63865158370056</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+        <v>63865158370020</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
@@ -2928,10 +2908,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C43" t="n">
-        <v>63865158140042</v>
+        <v>63865158140040</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2939,7 +2919,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>63865158090019</v>
+        <v>63865158090016</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2947,28 +2927,16 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>63865158370047</v>
+        <v>63865158370055</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,13,4,26,0,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,1,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,2,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,3,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,5,26,4,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,5,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,6,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,7,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,6,26,8,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,9,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,10,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,11,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,7,26,12,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,13,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,14,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,15,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,14,0,27,0,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,1,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,2,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,3,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,1,27,4,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,5,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,6,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,7,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,2,27,8,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,9,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,10,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,11,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,3,27,12,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,13,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,14,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,15,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,4,28,0,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,1,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,2,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,3,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,5,28,4,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,5,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,6,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,7,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,6,28,8,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,9,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,10,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,11,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,7,28,12,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,13,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,14,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,15,112,0,31.85,-327.68,-1,-100]</t>
-        </is>
-      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -2988,10 +2956,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C44" t="n">
-        <v>63865158140043</v>
+        <v>63865158140041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2999,61 +2967,38 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>63865158090020</v>
+        <v>63865158090015</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>63865158370056</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>power_on_with_fw-late_livefish_detection-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>csm1_swb_maglan_asic_pcie-Fast_boot_asic_HBI_HW_failure_detected-Asic HBI HW failure detection for csm1_swb_maglan_asic_pcie</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Spectrum-6 in Flash Recovery Mode. 
-Suspect ASIC issue.
-NV : share details 
-JE130526T0960963100707
-E6B171_9_2_8
-</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>NV</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>SPE</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Waiting Debug</t>
-        </is>
-      </c>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
@@ -3067,21 +3012,47 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>40</v>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="C45" t="n">
+        <v>63865158140042</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>63865158090019</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>63865158370047</v>
+      </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,13,4,26,0,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,1,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,2,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,3,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,5,26,4,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,5,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,6,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,7,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,6,26,8,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,9,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,10,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,11,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,7,26,12,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,13,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,14,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,15,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,14,0,27,0,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,1,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,2,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,3,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,1,27,4,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,5,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,6,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,7,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,2,27,8,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,9,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,10,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,11,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,3,27,12,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,13,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,14,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,15,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,4,28,0,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,1,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,2,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,3,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,5,28,4,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,5,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,6,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,7,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,6,28,8,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,9,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,10,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,11,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,7,28,12,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,13,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,14,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,15,112,0,31.85,-327.68,-1,-100]</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
@@ -3101,27 +3072,72 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>41</v>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="C46" t="n">
+        <v>63865158140043</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>63865158090020</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>power_on_with_fw-late_livefish_detection-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>csm1_swb_maglan_asic_pcie-Fast_boot_asic_HBI_HW_failure_detected-Asic HBI HW failure detection for csm1_swb_maglan_asic_pcie</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spectrum-6 in Flash Recovery Mode. 
+Suspect ASIC issue.
+NV : share details 
+JE130526T0960963100707
+E6B171_9_2_8
+</t>
+        </is>
+      </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>SPE</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Waiting Debug</t>
+        </is>
+      </c>
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
@@ -3135,7 +3151,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
@@ -3169,7 +3185,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
@@ -3203,7 +3219,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
@@ -3237,27 +3253,13 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>45</v>
-      </c>
-      <c r="C50" t="n">
-        <v>63865158140044</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>63865158100002</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
-        <v>63865158390004</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
@@ -3285,47 +3287,21 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>46</v>
-      </c>
-      <c r="C51" t="n">
-        <v>63865158140045</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>63865158090025</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>63865158370045</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,2,2,3,8,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,9,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,10,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,11,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,3,3,12,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,13,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,14,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,15,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,0,3,0,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,1,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,2,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,3,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,1,3,4,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,5,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,6,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,7,10,0,31.47,-327.68,-1,-100]</t>
-        </is>
-      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
@@ -3345,10 +3321,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C52" t="n">
-        <v>63865158140046</v>
+        <v>63865158140044</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3356,7 +3332,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>63865158090030</v>
+        <v>63865158100002</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -3364,7 +3340,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>63865158370048</v>
+        <v>63865158390004</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -3393,10 +3369,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C53" t="n">
-        <v>63865158140047</v>
+        <v>63865158140045</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3404,22 +3380,36 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>63865158090035</v>
+        <v>63865158090025</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="n">
+        <v>63865158370045</v>
+      </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,2,2,3,8,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,9,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,10,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,11,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,3,3,12,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,13,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,14,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,15,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,0,3,0,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,1,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,2,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,3,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,1,3,4,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,5,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,6,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,7,10,0,31.47,-327.68,-1,-100]</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
@@ -3439,10 +3429,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C54" t="n">
-        <v>63865158140048</v>
+        <v>63865158140046</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3450,7 +3440,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>63865158090043</v>
+        <v>63865158090030</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3458,7 +3448,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>63865158370043</v>
+        <v>63865158370048</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
@@ -3487,10 +3477,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C55" t="n">
-        <v>63865158140049</v>
+        <v>63865158140047</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3498,16 +3488,14 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>63865158090036</v>
+        <v>63865158090035</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>63865158370041</v>
-      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
@@ -3535,10 +3523,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C56" t="n">
-        <v>63865158140050</v>
+        <v>63865158140048</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3546,7 +3534,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>63865158090040</v>
+        <v>63865158090043</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -3554,7 +3542,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>63865158370050</v>
+        <v>63865158370043</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
@@ -3583,10 +3571,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C57" t="n">
-        <v>63865158140052</v>
+        <v>63865158140049</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -3594,7 +3582,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>63865158090044</v>
+        <v>63865158090036</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -3602,7 +3590,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>63865158370046</v>
+        <v>63865158370041</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
@@ -3631,10 +3619,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C58" t="n">
-        <v>63865158140031</v>
+        <v>63865158140050</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -3642,7 +3630,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>63865158090046</v>
+        <v>63865158090040</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -3650,7 +3638,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>63865158370049</v>
+        <v>63865158370050</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -3660,12 +3648,7 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>PASS FT - Fail at HS cold test GOOD RX , NO BER 
-30-SEP : cookbook flow (LPBK remating / cleaning / crossing, Windu cross) -&gt; still fail replace CSM</t>
-        </is>
-      </c>
+      <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
@@ -3684,10 +3667,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C59" t="n">
-        <v>63865158140055</v>
+        <v>63865158140052</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3695,7 +3678,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>63865158090045</v>
+        <v>63865158090044</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -3703,13 +3686,9 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>63865158370023</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+        <v>63865158370046</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
@@ -3736,28 +3715,49 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C60" t="n">
-        <v>63865158140051</v>
+        <v>63865158140031</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
+      <c r="E60" t="n">
+        <v>63865158090046</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>63865158370049</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>PASS FT - Fail at HS cold test GOOD RX , NO BER 
+30-SEP : cookbook flow (LPBK remating / cleaning / crossing, Windu cross) -&gt; still fail replace CSM</t>
+        </is>
+      </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C61" t="n">
-        <v>63865158140056</v>
+        <v>63865158140055</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3787,10 +3787,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>63865158090047</v>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
+        <v>63865158090045</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>63865158370023</v>
+      </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
@@ -3818,10 +3824,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C62" t="n">
-        <v>63865158140057</v>
+        <v>63865158140051</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3858,17 +3864,19 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C63" t="n">
-        <v>63865158140062</v>
+        <v>63865158140056</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="n">
+        <v>63865158090047</v>
+      </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
@@ -3898,12 +3906,16 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C64" t="n">
-        <v>63865158140060</v>
-      </c>
-      <c r="D64" t="inlineStr"/>
+        <v>63865158140057</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
@@ -3934,10 +3946,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C65" t="n">
-        <v>63865158140061</v>
+        <v>63865158140062</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -3974,10 +3986,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C66" t="n">
-        <v>63865158140058</v>
+        <v>63865158140060</v>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
@@ -4010,12 +4022,16 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C67" t="n">
-        <v>63865158140059</v>
-      </c>
-      <c r="D67" t="inlineStr"/>
+        <v>63865158140061</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
@@ -4039,6 +4055,78 @@
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>61</v>
+      </c>
+      <c r="C68" t="n">
+        <v>63865158140058</v>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr"/>
+      <c r="X68" t="inlineStr"/>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>62</v>
+      </c>
+      <c r="C69" t="n">
+        <v>63865158140059</v>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr"/>
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/TS3_mapping.xlsx
+++ b/TS3_mapping.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/TS3_mapping.xlsx
+++ b/TS3_mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z69"/>
+  <dimension ref="A1:Z74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -586,11 +586,19 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>DEV032313</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
@@ -779,8 +787,16 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>MT2640600GZR</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
@@ -843,7 +859,11 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
@@ -911,7 +931,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>MT2640600H02</t>
@@ -1003,80 +1027,39 @@
       <c r="Z8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" t="n">
-        <v>63865158140002</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>63865158090001</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>63865158370007</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>CUST</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+          <t>fuse_mismatch_group1-read_fuse_missmatch-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,2,4,4,0,13,134.85,12.89,8.41,6.6,-2.34,nan],[prb:nan,2,4,4,1,13,134.85,12.79,8.51,6.6,-2.89,nan],[prb:nan,2,4,4,2,13,134.85,12.86,8.44,6.6,-2.45,nan],[prb:nan,2,4,4,3,13,134.85,12.98,8.32,6.73,0.15,nan]</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>High speed fail; ELS2 OE4 Lane0~3 no BER
-30-SEP : cookbook flow (LPBK remating / cleaning / crossing, Windu cross) -&gt; still fail replace CSM</t>
-        </is>
-      </c>
+          <t>csm1_swb_maglan_asic_pcie_mng.yu_boot.fuse_ctrl.redundency_missmatch_cause-crspace_reg_read:mng.yu_boot.fuse_ctrl.redundency_missmatch_cause</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>NV</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>SPE</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Waiting Debug</t>
-        </is>
-      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
@@ -1090,10 +1073,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>63865158140006</v>
+        <v>63865158140002</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1101,7 +1084,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>63865158090002</v>
+        <v>63865158090001</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1109,7 +1092,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>63865158370002</v>
+        <v>63865158370007</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1117,7 +1100,11 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
@@ -1130,13 +1117,34 @@
           <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,2,4,4,0,13,134.85,12.89,8.41,6.6,-2.34,nan],[prb:nan,2,4,4,1,13,134.85,12.79,8.51,6.6,-2.89,nan],[prb:nan,2,4,4,2,13,134.85,12.86,8.44,6.6,-2.45,nan],[prb:nan,2,4,4,3,13,134.85,12.98,8.32,6.73,0.15,nan]</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>High speed fail; ELS2 OE4 Lane0~3 no BER
+30-SEP : cookbook flow (LPBK remating / cleaning / crossing, Windu cross) -&gt; still fail replace CSM</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>SPE</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Waiting Debug</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
@@ -1150,10 +1158,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>63865158140007</v>
+        <v>63865158140006</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1161,7 +1169,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>63865158090009</v>
+        <v>63865158090002</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1169,15 +1177,19 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>63865158370006</v>
+        <v>63865158370002</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
@@ -1190,11 +1202,7 @@
           <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,7,2,13,8,51,134.29,12.76,8.52,6.6,-19.63,nan],[prp:-19.63,7,2,13,8,51,134.29,12.76,8.52,6.6,-19.63,nan],[prb:nan,7,2,13,9,51,134.29,12.86,8.42,6.73,-19.75,nan],[prp:-19.75,7,2,13,9,51,134.29,12.86,8.42,6.73,-19.75,nan],[prb:nan,7,2,13,10,51,134.29,12.76,8.52,6.6,-20.97,nan],[prp:-20.97,7,2,13,10,51,134.29,12.76,8.52,6.6,-20.97,nan],[prb:nan,7,2,13,11,51,134.29,12.67,8.61,6.46,-20.97,nan],[prp:-20.97,7,2,13,11,51,134.29,12.67,8.61,6.46,-20.97,nan],[prb:nan,9,7,18,12,72,134.62,12.92,8.37,6.6,-20.6,nan],[prp:-20.6,9,7,18,12,72,134.62,12.92,8.37,6.6,-20.6,nan],[prb:nan,9,7,18,13,72,134.62,12.95,8.34,6.73,-20.41,nan],[prp:-20.41,9,7,18,13,72,134.62,12.95,8.34,6.73,-20.41,nan],[prb:nan,9,7,18,14,72,134.62,13.04,8.25,6.86,-19.47,nan],[prp:-19.47,9,7,18,14,72,134.62,13.04,8.25,6.86,-19.47,nan],[prb:nan,9,7,18,15,72,134.62,12.89,8.4,6.86,-19.75,nan],[prp:-19.75,9,7,18,15,72,134.62,12.89,8.4,6.86,-19.75,nan],[prb:nan,11,0,21,0,81,124.53,12.92,8.03,6.73,-21.19,nan],[prp:-21.19,11,0,21,0,81,124.53,12.92,8.03,6.73,-21.19,nan],[prb:nan,11,0,21,1,81,124.53,12.82,8.13,6.73,-21.87,nan],[prp:-21.87,11,0,21,1,81,124.53,12.82,8.13,6.73,-21.87,nan],[prb:nan,11,0,21,2,81,124.53,12.86,8.09,6.6,-20.6,nan],[prp:-20.6,11,0,21,2,81,124.53,12.86,8.09,6.6,-20.6,nan],[prb:nan,11,0,21,3,81,124.53,12.92,8.03,6.73,-20.41,nan],[prp:-20.41,11,0,21,3,81,124.53,12.92,8.03,6.73,-20.41,nan],[prb:nan,11,6,22,8,87,149.85,12.89,8.87,6.73,-20.09,nan],[prp:-20.09,11,6,22,8,87,149.85,12.89,8.87,6.73,-20.09,nan],[prb:nan,11,6,22,9,87,149.85,13.01,8.75,6.86,-20.09,nan],[prp:-20.09,11,6,22,9,87,149.85,13.01,8.75,6.86,-20.09,nan],[prb:nan,11,6,22,10,87,149.85,12.73,9.03,6.73,-19.47,nan],[prp:-19.47,11,6,22,10,87,149.85,12.73,9.03,6.73,-19.47,nan],[prb:nan,11,6,22,11,87,149.85,12.73,9.03,6.46,-19.47,nan],[prp:-19.47,11,6,22,11,87,149.85,12.73,9.03,6.46,-19.47,nan],[prb:nan,15,3,29,12,116,119.23,12.89,7.87,6.73,-21.87,nan],[prp:-21.87,15,3,29,12,116,119.23,12.89,7.87,6.73,-21.87,nan],[prb:nan,15,3,29,13,116,119.23,12.98,7.78,6.73,-21.87,nan],[prp:-21.87,15,3,29,13,116,119.23,12.98,7.78,6.73,-21.87,nan],[prb:nan,15,3,29,14,116,119.23,12.82,7.94,6.6,-19.32,nan],[prp:-19.32,15,3,29,14,116,119.23,12.82,7.94,6.6,-19.32,nan],[prb:nan,15,3,29,15,116,119.23,12.89,7.87,6.73,-19.91,nan],[prp:-19.91,15,3,29,15,116,119.23,12.89,7.87,6.73,-19.91,nan]</t>
-        </is>
-      </c>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
@@ -1214,10 +1222,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>63865158140008</v>
+        <v>63865158140007</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1225,7 +1233,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>63865158090006</v>
+        <v>63865158090009</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1233,7 +1241,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>63865158370004</v>
+        <v>63865158370006</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1245,17 +1253,13 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>MT2640600GZ1</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>FT</t>
@@ -1268,7 +1272,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,7,4,14,0,53,128.58,13.01,8.08,6.73,-19.91,nan],[prp:-19.91,7,4,14,0,53,128.58,13.01,8.08,6.73,-19.91,nan],[prb:nan,7,4,14,1,53,128.58,12.79,8.3,6.73,-19.91,nan],[prp:-19.91,7,4,14,1,53,128.58,12.79,8.3,6.73,-19.91,nan],[prb:nan,7,4,14,2,53,128.58,13.04,8.05,6.99,-20.09,nan],[prp:-20.09,7,4,14,2,53,128.58,13.04,8.05,6.99,-20.09,nan],[prb:nan,7,4,14,3,53,128.58,12.98,8.11,6.86,-19.91,nan],[prp:-19.91,7,4,14,3,53,128.58,12.98,8.11,6.86,-19.91,nan]</t>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,7,2,13,8,51,134.29,12.76,8.52,6.6,-19.63,nan],[prp:-19.63,7,2,13,8,51,134.29,12.76,8.52,6.6,-19.63,nan],[prb:nan,7,2,13,9,51,134.29,12.86,8.42,6.73,-19.75,nan],[prp:-19.75,7,2,13,9,51,134.29,12.86,8.42,6.73,-19.75,nan],[prb:nan,7,2,13,10,51,134.29,12.76,8.52,6.6,-20.97,nan],[prp:-20.97,7,2,13,10,51,134.29,12.76,8.52,6.6,-20.97,nan],[prb:nan,7,2,13,11,51,134.29,12.67,8.61,6.46,-20.97,nan],[prp:-20.97,7,2,13,11,51,134.29,12.67,8.61,6.46,-20.97,nan],[prb:nan,9,7,18,12,72,134.62,12.92,8.37,6.6,-20.6,nan],[prp:-20.6,9,7,18,12,72,134.62,12.92,8.37,6.6,-20.6,nan],[prb:nan,9,7,18,13,72,134.62,12.95,8.34,6.73,-20.41,nan],[prp:-20.41,9,7,18,13,72,134.62,12.95,8.34,6.73,-20.41,nan],[prb:nan,9,7,18,14,72,134.62,13.04,8.25,6.86,-19.47,nan],[prp:-19.47,9,7,18,14,72,134.62,13.04,8.25,6.86,-19.47,nan],[prb:nan,9,7,18,15,72,134.62,12.89,8.4,6.86,-19.75,nan],[prp:-19.75,9,7,18,15,72,134.62,12.89,8.4,6.86,-19.75,nan],[prb:nan,11,0,21,0,81,124.53,12.92,8.03,6.73,-21.19,nan],[prp:-21.19,11,0,21,0,81,124.53,12.92,8.03,6.73,-21.19,nan],[prb:nan,11,0,21,1,81,124.53,12.82,8.13,6.73,-21.87,nan],[prp:-21.87,11,0,21,1,81,124.53,12.82,8.13,6.73,-21.87,nan],[prb:nan,11,0,21,2,81,124.53,12.86,8.09,6.6,-20.6,nan],[prp:-20.6,11,0,21,2,81,124.53,12.86,8.09,6.6,-20.6,nan],[prb:nan,11,0,21,3,81,124.53,12.92,8.03,6.73,-20.41,nan],[prp:-20.41,11,0,21,3,81,124.53,12.92,8.03,6.73,-20.41,nan],[prb:nan,11,6,22,8,87,149.85,12.89,8.87,6.73,-20.09,nan],[prp:-20.09,11,6,22,8,87,149.85,12.89,8.87,6.73,-20.09,nan],[prb:nan,11,6,22,9,87,149.85,13.01,8.75,6.86,-20.09,nan],[prp:-20.09,11,6,22,9,87,149.85,13.01,8.75,6.86,-20.09,nan],[prb:nan,11,6,22,10,87,149.85,12.73,9.03,6.73,-19.47,nan],[prp:-19.47,11,6,22,10,87,149.85,12.73,9.03,6.73,-19.47,nan],[prb:nan,11,6,22,11,87,149.85,12.73,9.03,6.46,-19.47,nan],[prp:-19.47,11,6,22,11,87,149.85,12.73,9.03,6.46,-19.47,nan],[prb:nan,15,3,29,12,116,119.23,12.89,7.87,6.73,-21.87,nan],[prp:-21.87,15,3,29,12,116,119.23,12.89,7.87,6.73,-21.87,nan],[prb:nan,15,3,29,13,116,119.23,12.98,7.78,6.73,-21.87,nan],[prp:-21.87,15,3,29,13,116,119.23,12.98,7.78,6.73,-21.87,nan],[prb:nan,15,3,29,14,116,119.23,12.82,7.94,6.6,-19.32,nan],[prp:-19.32,15,3,29,14,116,119.23,12.82,7.94,6.6,-19.32,nan],[prb:nan,15,3,29,15,116,119.23,12.89,7.87,6.73,-19.91,nan],[prp:-19.91,15,3,29,15,116,119.23,12.89,7.87,6.73,-19.91,nan]</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1284,29 +1288,73 @@
       <c r="Z12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" t="n">
+        <v>63865158140008</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>63865158090006</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>63865158370004</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>MT2640600GZ1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>CUST</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>laser_tests_prerequisites-linkup_setup-ERROR-ShellException;</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,7,4,14,0,53,128.58,13.01,8.08,6.73,-19.91,nan],[prp:-19.91,7,4,14,0,53,128.58,13.01,8.08,6.73,-19.91,nan],[prb:nan,7,4,14,1,53,128.58,12.79,8.3,6.73,-19.91,nan],[prp:-19.91,7,4,14,1,53,128.58,12.79,8.3,6.73,-19.91,nan],[prb:nan,7,4,14,2,53,128.58,13.04,8.05,6.99,-20.09,nan],[prp:-20.09,7,4,14,2,53,128.58,13.04,8.05,6.99,-20.09,nan],[prb:nan,7,4,14,3,53,128.58,12.98,8.11,6.86,-19.91,nan],[prp:-19.91,7,4,14,3,53,128.58,12.98,8.11,6.86,-19.91,nan]</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
@@ -1320,48 +1368,28 @@
       <c r="Z13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>9</v>
-      </c>
-      <c r="C14" t="n">
-        <v>63865158140009</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>63865158090007</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>63865158370008</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>CUST</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>laser_tests_prerequisites-linkup_setup-ERROR-ShellException;</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
@@ -1376,33 +1404,13 @@
       <c r="Z14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>10</v>
-      </c>
-      <c r="C15" t="n">
-        <v>63865158140010</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>63865158090005</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>63865158370051</v>
-      </c>
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
@@ -1410,42 +1418,21 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>AOT</t>
+          <t>CUST</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,14,0,27,0,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,0,27,1,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,0,27,2,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,0,27,3,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,1,27,4,106,0,31.17,-327.68,-1,-100],[eocl:-1.0,14,1,27,5,106,0,31.17,-327.68,-1,-100],[eocl:-1.0,14,1,27,6,106,0,31.17,-327.68,-1,-100],[eocl:-1.0,14,1,27,7,106,0,31.17,-327.68,-1,-100]</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Fiber fracture, replace E-FBK
-Replaced FBK then pass</t>
-        </is>
-      </c>
+          <t>fuse_mismatch_group1-read_fuse_missmatch-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>FXV</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Peter</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
@@ -1459,10 +1446,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>63865158140012</v>
+        <v>63865158140009</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1470,7 +1457,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>63865158090027</v>
+        <v>63865158090007</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1478,12 +1465,28 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>63865158370028</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+        <v>63865158370008</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>MT2640600GZ0</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -1507,10 +1510,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>63865158140016</v>
+        <v>63865158140010</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1518,7 +1521,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>63865158090028</v>
+        <v>63865158090005</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1526,22 +1529,59 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>63865158370019</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
+        <v>63865158370051</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,14,0,27,0,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,0,27,1,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,0,27,2,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,0,27,3,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,1,27,4,106,0,31.17,-327.68,-1,-100],[eocl:-1.0,14,1,27,5,106,0,31.17,-327.68,-1,-100],[eocl:-1.0,14,1,27,6,106,0,31.17,-327.68,-1,-100],[eocl:-1.0,14,1,27,7,106,0,31.17,-327.68,-1,-100]</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Fiber fracture, replace E-FBK
+Replaced FBK then pass</t>
+        </is>
+      </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
@@ -1549,41 +1589,33 @@
       <c r="Z17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>13</v>
-      </c>
-      <c r="C18" t="n">
-        <v>63865158140015</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>63865158090024</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>63865158370015</v>
-      </c>
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-21.37,6,0,11,0,41,159.27,12.98,9.04,6.6,-21.37,nan],[prb:nan,6,0,11,0,41,159.27,12.98,9.04,6.6,-21.37,nan],[prp:-22.08,6,0,11,1,41,159.27,12.92,9.1,6.46,-22.08,nan],[prb:nan,6,0,11,1,41,159.27,12.92,9.1,6.46,-22.08,nan],[prp:-21.61,6,0,11,2,41,159.27,13.01,9.01,6.6,-21.61,nan],[prb:nan,6,0,11,2,41,159.27,13.01,9.01,6.6,-21.61,nan],[prp:-20.6,6,0,11,3,41,159.27,13.15,8.87,6.73,-20.6,nan],[prb:nan,6,0,11,3,41,159.27,13.15,8.87,6.73,-20.6,nan]</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
@@ -1603,10 +1635,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C19" t="n">
-        <v>63865158140014</v>
+        <v>63865158140012</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1614,7 +1646,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>63865158090026</v>
+        <v>63865158090027</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1622,52 +1654,26 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>63865158370052</v>
+        <v>63865158370028</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:14.08,7,3,13,12,52,0,31.06,0.84,14.08,-100],[eocl:13.62,7,3,13,13,52,0,31.06,1.3,13.62,-100],[eocl:13.62,7,3,13,14,52,0,31.06,1.3,13.62,-100],[eocl:13.21,7,3,13,15,52,0,31.06,1.71,13.21,-100]</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>FBK stand alone IL still abnormal
-Need to replace an W-FBK
-Replaced FBK then pass</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>FXV</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Peter</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
@@ -1681,23 +1687,51 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>63865158140013</v>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+        <v>63865158140016</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>63865158090028</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>63865158370019</v>
+      </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>power_on-burn_os_if_needed_and_boot_os-ERROR-TimeoutError;</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">System did not boot within the timeout and 1 retries were already done, boot failed due to: Exceed timeout on command ControlKeys.USER_COMMAND without receiving expected-reply: Checkpoint </t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
@@ -1717,10 +1751,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C21" t="n">
-        <v>63865158140019</v>
+        <v>63865158140015</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1728,7 +1762,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>63865158090034</v>
+        <v>63865158090024</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1736,55 +1770,26 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>63865158370042</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
+        <v>63865158370015</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>power_on-validate_power_converter_dma_data-ERROR-Exception;</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>csm1_asic_brd__pdb_node_controller': 'write_i2c_block' function failed: device=/dev/mst/192.168.10.20:23108,@dev@mst@dev-i2c-6, i2c_addr=0x60, addr_width=1, reg_addr=0xc7, size=2</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tried master PDB then pass. Replacing with new PDB to retest.
-29-SEP: Passed with new PDB - &gt; retets on PDB station </t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>FXV</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Joy</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>On-going</t>
-        </is>
-      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
@@ -1792,39 +1797,81 @@
       <c r="Z21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>14</v>
+      </c>
+      <c r="C22" t="n">
+        <v>63865158140014</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>63865158090026</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>63865158370052</v>
+      </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>AOT</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-17.93,15,7,30,12,120,139.29,12.92,8.52,6.86,-17.93,nan],[prb:nan,15,7,30,12,120,139.29,12.92,8.52,6.86,-17.93,nan],[prp:-18.48,15,7,30,13,120,139.29,13.01,8.43,6.86,-18.48,nan],[prb:nan,15,7,30,13,120,139.29,13.01,8.43,6.86,-18.48,nan],[prp:-20.97,15,7,30,14,120,139.29,12.89,8.55,6.73,-20.97,nan],[prb:nan,15,7,30,14,120,139.29,12.89,8.55,6.73,-20.97,nan],[prp:-20.97,15,7,30,15,120,139.29,12.82,8.62,6.73,-20.97,nan],[prb:nan,15,7,30,15,120,139.29,12.82,8.62,6.73,-20.97,nan]</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr"/>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:14.08,7,3,13,12,52,0,31.06,0.84,14.08,-100],[eocl:13.62,7,3,13,13,52,0,31.06,1.3,13.62,-100],[eocl:13.62,7,3,13,14,52,0,31.06,1.3,13.62,-100],[eocl:13.21,7,3,13,15,52,0,31.06,1.71,13.21,-100]</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>FBK stand alone IL still abnormal
+Need to replace an W-FBK
+Replaced FBK then pass</t>
+        </is>
+      </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
@@ -1838,51 +1885,27 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C23" t="n">
-        <v>63865158140020</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>63865158090033</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>63865158370017</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+        <v>63865158140013</v>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-20.41,7,4,14,0,53,109.98,12.86,7.55,6.73,-20.41,nan],[prb:nan,7,4,14,0,53,109.98,12.86,7.55,6.73,-20.41,nan],[prp:-19.47,7,4,14,1,53,109.98,12.7,7.71,6.6,-19.47,nan],[prb:nan,7,4,14,1,53,109.98,12.7,7.71,6.6,-19.47,nan],[prp:-22.68,7,4,14,2,53,109.98,12.92,7.49,6.6,-22.68,nan],[prb:nan,7,4,14,2,53,109.98,12.92,7.49,6.6,-22.68,nan],[prp:-21.87,7,4,14,3,53,109.98,12.89,7.52,6.6,-21.87,nan],[prb:nan,7,4,14,3,53,109.98,12.89,7.52,6.6,-21.87,nan],[prp:-19.91,11,4,22,0,85,119.68,12.76,8.02,6.46,-19.91,nan],[prb:nan,11,4,22,0,85,119.68,12.76,8.02,6.46,-19.91,nan],[prp:-20.22,11,4,22,1,85,119.68,12.76,8.02,6.32,-20.22,nan],[prb:nan,11,4,22,1,85,119.68,12.76,8.02,6.32,-20.22,nan],[prp:-20.97,11,4,22,2,85,119.68,12.79,7.99,6.46,-20.97,nan],[prb:nan,11,4,22,2,85,119.68,12.79,7.99,6.46,-20.97,nan],[prp:-20.97,11,4,22,3,85,119.68,12.86,7.92,6.46,-20.97,nan],[prb:nan,11,4,22,3,85,119.68,12.86,7.92,6.46,-20.97,nan]</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
@@ -1902,10 +1925,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>63865158140021</v>
+        <v>63865158140019</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1913,7 +1936,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>63865158090032</v>
+        <v>63865158090034</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1921,7 +1944,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>63865158370018</v>
+        <v>63865158370042</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1929,26 +1952,51 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>AOT</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
+          <t>power_on-validate_power_converter_dma_data-ERROR-Exception;</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>csm1_asic_brd__pdb_node_controller': 'write_i2c_block' function failed: device=/dev/mst/192.168.10.20:23108,@dev@mst@dev-i2c-6, i2c_addr=0x60, addr_width=1, reg_addr=0xc7, size=2</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tried master PDB then pass. Replacing with new PDB to retest.
+29-SEP: Passed with new PDB - &gt; retets on PDB station </t>
+        </is>
+      </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Joy</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>On-going</t>
+        </is>
+      </c>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
@@ -1956,43 +2004,15 @@
       <c r="Z24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>19</v>
-      </c>
-      <c r="C25" t="n">
-        <v>63865158140022</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>63865158090037</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>63865158370014</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
@@ -2008,7 +2028,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,12,6,24,8,95,119.32,12.89,7.88,6.6,-20.09,nan],[prp:-20.09,12,6,24,8,95,119.32,12.89,7.88,6.6,-20.09,nan],[prb:nan,12,6,24,9,95,119.32,12.89,7.88,6.46,-19.75,nan],[prp:-19.75,12,6,24,9,95,119.32,12.89,7.88,6.46,-19.75,nan],[prb:nan,12,6,24,10,95,119.32,12.82,7.95,6.46,-22.68,nan],[prp:-22.68,12,6,24,10,95,119.32,12.82,7.95,6.46,-22.68,nan],[prb:nan,12,6,24,11,95,119.32,12.73,8.04,6.46,-22.68,nan],[prp:-22.68,12,6,24,11,95,119.32,12.73,8.04,6.46,-22.68,nan],[prb:nan,14,5,28,4,110,139.47,12.7,8.74,6.73,-2.79,nan],[prb:nan,14,5,28,5,110,139.47,12.61,8.83,6.73,-2.33,nan],[prb:nan,14,5,28,6,110,139.47,12.67,8.77,6.73,-2.66,nan],[prb:nan,14,5,28,7,110,139.47,12.76,8.68,6.73,-18.57,nan],[prp:-18.57,14,5,28,7,110,139.47,12.76,8.68,6.73,-18.57,nan],[prb:nan,5,1,9,4,34,144.37,13.18,8.41,6.86,-21.87,nan],[prp:-21.87,5,1,9,4,34,144.37,13.18,8.41,6.86,-21.87,nan],[prb:nan,5,1,9,5,34,144.37,13.01,8.58,6.73,-21.87,nan],[prp:-21.87,5,1,9,5,34,144.37,13.01,8.58,6.73,-21.87,nan],[prb:nan,5,1,9,6,34,144.37,13.15,8.44,6.73,-22.68,nan],[prp:-22.68,5,1,9,6,34,144.37,13.15,8.44,6.73,-22.68,nan],[prb:nan,5,1,9,7,34,144.37,13.23,8.36,6.99,-22.08,nan],[prp:-22.08,5,1,9,7,34,144.37,13.23,8.36,6.99,-22.08,nan],[prp:-5.2,2,1,3,6,10,129.27,12.76,8.35,6.6,-5.2,8e-10]</t>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-17.93,15,7,30,12,120,139.29,12.92,8.52,6.86,-17.93,nan],[prb:nan,15,7,30,12,120,139.29,12.92,8.52,6.86,-17.93,nan],[prp:-18.48,15,7,30,13,120,139.29,13.01,8.43,6.86,-18.48,nan],[prb:nan,15,7,30,13,120,139.29,13.01,8.43,6.86,-18.48,nan],[prp:-20.97,15,7,30,14,120,139.29,12.89,8.55,6.73,-20.97,nan],[prb:nan,15,7,30,14,120,139.29,12.89,8.55,6.73,-20.97,nan],[prp:-20.97,15,7,30,15,120,139.29,12.82,8.62,6.73,-20.97,nan],[prb:nan,15,7,30,15,120,139.29,12.82,8.62,6.73,-20.97,nan]</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -2030,10 +2050,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C26" t="n">
-        <v>63865158140023</v>
+        <v>63865158140020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2041,7 +2061,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>63865158090031</v>
+        <v>63865158090033</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2049,16 +2069,40 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>63865158370009</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+        <v>63865158370017</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-20.41,7,4,14,0,53,109.98,12.86,7.55,6.73,-20.41,nan],[prb:nan,7,4,14,0,53,109.98,12.86,7.55,6.73,-20.41,nan],[prp:-19.47,7,4,14,1,53,109.98,12.7,7.71,6.6,-19.47,nan],[prb:nan,7,4,14,1,53,109.98,12.7,7.71,6.6,-19.47,nan],[prp:-22.68,7,4,14,2,53,109.98,12.92,7.49,6.6,-22.68,nan],[prb:nan,7,4,14,2,53,109.98,12.92,7.49,6.6,-22.68,nan],[prp:-21.87,7,4,14,3,53,109.98,12.89,7.52,6.6,-21.87,nan],[prb:nan,7,4,14,3,53,109.98,12.89,7.52,6.6,-21.87,nan],[prp:-19.91,11,4,22,0,85,119.68,12.76,8.02,6.46,-19.91,nan],[prb:nan,11,4,22,0,85,119.68,12.76,8.02,6.46,-19.91,nan],[prp:-20.22,11,4,22,1,85,119.68,12.76,8.02,6.32,-20.22,nan],[prb:nan,11,4,22,1,85,119.68,12.76,8.02,6.32,-20.22,nan],[prp:-20.97,11,4,22,2,85,119.68,12.79,7.99,6.46,-20.97,nan],[prb:nan,11,4,22,2,85,119.68,12.79,7.99,6.46,-20.97,nan],[prp:-20.97,11,4,22,3,85,119.68,12.86,7.92,6.46,-20.97,nan],[prb:nan,11,4,22,3,85,119.68,12.86,7.92,6.46,-20.97,nan]</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
@@ -2078,10 +2122,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C27" t="n">
-        <v>63865158140025</v>
+        <v>63865158140021</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2089,7 +2133,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>63865158090022</v>
+        <v>63865158090032</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2097,15 +2141,31 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>63865158370010</v>
-      </c>
-      <c r="H27" t="inlineStr"/>
+        <v>63865158370018</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
@@ -2120,41 +2180,33 @@
       <c r="Z27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>22</v>
-      </c>
-      <c r="C28" t="n">
-        <v>63865158140024</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>63865158090023</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>63865158370016</v>
-      </c>
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>post_prbs_test_asic_reset-create_mst_devices_chipset-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>mst_devices_Linkx-MST Linkx device presence</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
@@ -2174,10 +2226,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C29" t="n">
-        <v>63865158140026</v>
+        <v>63865158140022</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2185,7 +2237,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>63865158090029</v>
+        <v>63865158090037</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2193,16 +2245,28 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>63865158370044</v>
+        <v>63865158370014</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>MT2640600GZP</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
@@ -2214,7 +2278,11 @@
           <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,12,6,24,8,95,119.32,12.89,7.88,6.6,-20.09,nan],[prp:-20.09,12,6,24,8,95,119.32,12.89,7.88,6.6,-20.09,nan],[prb:nan,12,6,24,9,95,119.32,12.89,7.88,6.46,-19.75,nan],[prp:-19.75,12,6,24,9,95,119.32,12.89,7.88,6.46,-19.75,nan],[prb:nan,12,6,24,10,95,119.32,12.82,7.95,6.46,-22.68,nan],[prp:-22.68,12,6,24,10,95,119.32,12.82,7.95,6.46,-22.68,nan],[prb:nan,12,6,24,11,95,119.32,12.73,8.04,6.46,-22.68,nan],[prp:-22.68,12,6,24,11,95,119.32,12.73,8.04,6.46,-22.68,nan],[prb:nan,14,5,28,4,110,139.47,12.7,8.74,6.73,-2.79,nan],[prb:nan,14,5,28,5,110,139.47,12.61,8.83,6.73,-2.33,nan],[prb:nan,14,5,28,6,110,139.47,12.67,8.77,6.73,-2.66,nan],[prb:nan,14,5,28,7,110,139.47,12.76,8.68,6.73,-18.57,nan],[prp:-18.57,14,5,28,7,110,139.47,12.76,8.68,6.73,-18.57,nan],[prb:nan,5,1,9,4,34,144.37,13.18,8.41,6.86,-21.87,nan],[prp:-21.87,5,1,9,4,34,144.37,13.18,8.41,6.86,-21.87,nan],[prb:nan,5,1,9,5,34,144.37,13.01,8.58,6.73,-21.87,nan],[prp:-21.87,5,1,9,5,34,144.37,13.01,8.58,6.73,-21.87,nan],[prb:nan,5,1,9,6,34,144.37,13.15,8.44,6.73,-22.68,nan],[prp:-22.68,5,1,9,6,34,144.37,13.15,8.44,6.73,-22.68,nan],[prb:nan,5,1,9,7,34,144.37,13.23,8.36,6.99,-22.08,nan],[prp:-22.08,5,1,9,7,34,144.37,13.23,8.36,6.99,-22.08,nan],[prp:-5.2,2,1,3,6,10,129.27,12.76,8.35,6.6,-5.2,8e-10]</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
@@ -2234,10 +2302,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C30" t="n">
-        <v>63865158140028</v>
+        <v>63865158140023</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2245,7 +2313,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>63865158090021</v>
+        <v>63865158090031</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2253,7 +2321,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>63865158370024</v>
+        <v>63865158370009</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -2282,10 +2350,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C31" t="n">
-        <v>63865158140029</v>
+        <v>63865158140025</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2293,7 +2361,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>63865158090038</v>
+        <v>63865158090022</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2301,7 +2369,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>63865158370025</v>
+        <v>63865158370010</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -2330,10 +2398,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C32" t="n">
-        <v>63865158140030</v>
+        <v>63865158140024</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2341,7 +2409,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>63865158090042</v>
+        <v>63865158090023</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2349,7 +2417,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>63865158370054</v>
+        <v>63865158370016</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -2378,10 +2446,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C33" t="n">
-        <v>63865158140037</v>
+        <v>63865158140026</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2389,7 +2457,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>63865158090018</v>
+        <v>63865158090029</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2397,11 +2465,11 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>63865158370013</v>
+        <v>63865158370044</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -2420,7 +2488,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-21.37,7,0,13,0,49,119.35,12.86,7.91,6.46,-21.37,nan],[prb:nan,7,0,13,0,49,119.35,12.86,7.91,6.46,-21.37,nan],[prp:-21.19,7,0,13,1,49,119.35,12.67,8.1,6.17,-21.19,nan],[prb:nan,7,0,13,1,49,119.35,12.67,8.1,6.17,-21.19,nan],[prp:-21.87,7,0,13,2,49,119.35,12.79,7.98,6.46,-21.87,nan],[prb:nan,7,0,13,2,49,119.35,12.79,7.98,6.46,-21.87,nan],[prp:-22.68,7,0,13,3,49,119.35,12.86,7.91,6.32,-22.68,nan],[prb:nan,7,0,13,3,49,119.35,12.86,7.91,6.32,-22.68,nan],[prp:-19.21,4,6,8,8,31,130.02,12.82,8.32,6.73,-19.21,nan],[prb:nan,4,6,8,8,31,130.02,12.82,8.32,6.73,-19.21,nan],[prp:-20.09,4,6,8,9,31,130.02,12.92,8.22,6.86,-20.09,nan],[prb:nan,4,6,8,9,31,130.02,12.92,8.22,6.86,-20.09,nan],[prp:-22.92,4,6,8,10,31,130.02,12.73,8.41,6.73,-22.92,nan],[prb:nan,4,6,8,10,31,130.02,12.73,8.41,6.73,-22.92,nan],[prp:-22.92,4,6,8,11,31,130.02,12.73,8.41,6.6,-22.92,nan],[prb:nan,4,6,8,11,31,130.02,12.73,8.41,6.6,-22.92,nan]</t>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-21.87,7,1,13,4,50,119.6,12.89,7.89,6.6,-21.87,nan],[prb:nan,7,1,13,4,50,119.6,12.89,7.89,6.6,-21.87,nan],[prp:-22.37,7,1,13,5,50,119.6,12.82,7.96,6.46,-22.37,nan],[prb:nan,7,1,13,5,50,119.6,12.82,7.96,6.46,-22.37,nan],[prp:-18.15,7,1,13,6,50,119.6,12.79,7.99,6.46,-18.15,nan],[prb:nan,7,1,13,6,50,119.6,12.79,7.99,6.46,-18.15,nan],[prp:-18.15,7,1,13,7,50,119.6,12.89,7.89,6.46,-18.15,nan],[prb:nan,7,1,13,7,50,119.6,12.89,7.89,6.46,-18.15,nan],[prp:-20.09,7,3,13,12,52,124.17,12.82,8.12,6.32,-20.09,nan],[prb:nan,7,3,13,12,52,124.17,12.82,8.12,6.32,-20.09,nan],[prp:-20.09,7,3,13,13,52,124.17,12.86,8.08,6.46,-20.09,nan],[prb:nan,7,3,13,13,52,124.17,12.86,8.08,6.46,-20.09,nan],[prp:-22.37,7,3,13,14,52,124.17,12.79,8.15,6.46,-22.37,nan],[prb:nan,7,3,13,14,52,124.17,12.79,8.15,6.46,-22.37,nan],[prp:-22.37,7,3,13,15,52,124.17,12.73,8.21,6.46,-22.37,nan],[prb:nan,7,3,13,15,52,124.17,12.73,8.21,6.46,-22.37,nan],[prb:nan,4,6,8,8,31,149.44,12.76,8.98,6.6,-2.13,nan],[prp:-20.76,4,6,8,9,31,149.44,12.82,8.92,6.73,-20.76,nan],[prb:nan,4,6,8,9,31,149.44,12.82,8.92,6.73,-20.76,nan],[prp:-21.61,4,6,8,10,31,149.44,12.98,8.76,6.86,-21.61,nan],[prb:nan,4,6,8,10,31,149.44,12.98,8.76,6.86,-21.61,nan],[prp:-22.08,4,6,8,11,31,149.44,12.89,8.85,6.73,-22.08,nan],[prb:nan,4,6,8,11,31,149.44,12.89,8.85,6.73,-22.08,nan],[prp:-20.22,4,7,8,12,32,144.48,12.86,8.74,6.73,-20.22,nan],[prb:nan,4,7,8,12,32,144.48,12.86,8.74,6.73,-20.22,nan],[prp:-20.22,4,7,8,13,32,144.48,13.01,8.59,6.99,-20.22,nan],[prb:nan,4,7,8,13,32,144.48,13.01,8.59,6.99,-20.22,nan],[prp:-21.19,4,7,8,14,32,144.48,12.89,8.71,6.73,-21.19,nan],[prb:nan,4,7,8,14,32,144.48,12.89,8.71,6.73,-21.19,nan],[prp:-21.37,4,7,8,15,32,144.48,12.86,8.74,6.6,-21.37,nan],[prb:nan,4,7,8,15,32,144.48,12.86,8.74,6.6,-21.37,nan],[prp:-20.76,4,3,7,12,28,131.33,13.04,8.14,6.6,-20.76,nan],[prb:nan,4,3,7,12,28,131.33,13.04,8.14,6.6,-20.76,nan],[prb:nan,4,3,7,13,28,131.33,13.15,8.03,6.73,-2.97,nan],[prb:nan,4,3,7,14,28,131.33,12.95,8.23,6.6,-2.7,nan],[prb:nan,4,3,7,15,28,131.33,12.98,8.2,6.6,-2.39,nan],[prp:-21.61,3,6,6,8,23,124.67,12.89,8.07,6.6,-21.61,nan],[prb:nan,3,6,6,8,23,124.67,12.89,8.07,6.6,-21.61,nan],[prb:nan,3,6,6,9,23,124.67,12.98,7.98,6.73,-2.18,nan],[prb:nan,3,6,6,10,23,124.67,12.89,8.07,6.73,-2.41,nan],[prb:nan,3,6,6,11,23,124.67,12.86,8.1,6.73,-1.99,nan],[prb:nan,3,7,6,12,24,134.46,12.86,8.43,6.73,-2.66,nan],[prb:nan,3,7,6,13,24,134.46,12.89,8.4,6.73,-2.79,nan],[prb:nan,3,7,6,14,24,134.46,12.86,8.43,6.73,-2.81,nan],[prp:-22.92,3,7,6,15,24,134.46,12.79,8.5,6.6,-22.92,nan],[prb:nan,3,7,6,15,24,134.46,12.79,8.5,6.6,-22.92,nan],[prb:nan,3,4,6,0,21,129.87,12.82,8.32,6.73,-2.69,nan],[prb:nan,3,4,6,1,21,129.87,12.61,8.53,6.46,-2.88,nan],[prp:-20.22,3,4,6,2,21,129.87,12.79,8.35,6.6,-20.22,nan],[prb:nan,3,4,6,2,21,129.87,12.79,8.35,6.6,-20.22,nan],[prb:nan,3,4,6,3,21,129.87,12.82,8.32,6.6,-2.5,nan]</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -2442,10 +2510,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C34" t="n">
-        <v>63865158140032</v>
+        <v>63865158140028</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2453,7 +2521,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>63865158090013</v>
+        <v>63865158090021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2461,32 +2529,16 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>63865158370012</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
+        <v>63865158370024</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>group_pb_button-group_pb_test-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>group_pb_pushed-Verify group_pb button pushed</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
@@ -2500,33 +2552,41 @@
       <c r="Z34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>25</v>
+      </c>
+      <c r="C35" t="n">
+        <v>63865158140029</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>63865158090038</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>63865158370025</v>
+      </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>sbc_storage_usb-passmark-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>usb_passmark_pass-Verify usb device passed passmark</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
@@ -2546,10 +2606,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C36" t="n">
-        <v>63865158140033</v>
+        <v>63865158140030</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2557,7 +2617,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>63865158090011</v>
+        <v>63865158090042</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2565,16 +2625,40 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>63865158370022</v>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+        <v>63865158370054</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,8,0,15,0,57,150,12.79,8.97,6.6,-22.08,nan],[prp:-22.08,8,0,15,0,57,150,12.79,8.97,6.6,-22.08,nan],[prb:nan,8,0,15,1,57,150,12.73,9.03,6.6,-22.08,nan],[prp:-22.08,8,0,15,1,57,150,12.73,9.03,6.6,-22.08,nan],[prb:nan,8,0,15,2,57,150,12.82,8.94,6.73,-21.61,nan],[prp:-21.61,8,0,15,2,57,150,12.82,8.94,6.73,-21.61,nan],[prb:nan,8,0,15,3,57,150,12.86,8.9,6.86,-21.87,nan],[prp:-21.87,8,0,15,3,57,150,12.86,8.9,6.86,-21.87,nan],[prb:nan,6,7,12,12,48,129.64,12.86,8.27,6.73,-19.91,nan],[prp:-19.91,6,7,12,12,48,129.64,12.86,8.27,6.73,-19.91,nan],[prb:nan,6,7,12,13,48,129.64,12.95,8.18,6.73,-20.41,nan],[prp:-20.41,6,7,12,13,48,129.64,12.95,8.18,6.73,-20.41,nan],[prb:nan,6,7,12,14,48,129.64,12.89,8.24,6.6,-23.28,nan],[prp:-23.28,6,7,12,14,48,129.64,12.89,8.24,6.6,-23.28,nan],[prb:nan,6,7,12,15,48,129.64,12.76,8.37,6.6,-22.37,nan],[prp:-22.37,6,7,12,15,48,129.64,12.76,8.37,6.6,-22.37,nan]</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
@@ -2594,10 +2678,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C37" t="n">
-        <v>63865158140034</v>
+        <v>63865158140037</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2605,7 +2689,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>63865158090010</v>
+        <v>63865158090018</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2613,16 +2697,44 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>63865158370026</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+        <v>63865158370013</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>MT2640600GZQ</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-21.37,7,0,13,0,49,119.35,12.86,7.91,6.46,-21.37,nan],[prb:nan,7,0,13,0,49,119.35,12.86,7.91,6.46,-21.37,nan],[prp:-21.19,7,0,13,1,49,119.35,12.67,8.1,6.17,-21.19,nan],[prb:nan,7,0,13,1,49,119.35,12.67,8.1,6.17,-21.19,nan],[prp:-21.87,7,0,13,2,49,119.35,12.79,7.98,6.46,-21.87,nan],[prb:nan,7,0,13,2,49,119.35,12.79,7.98,6.46,-21.87,nan],[prp:-22.68,7,0,13,3,49,119.35,12.86,7.91,6.32,-22.68,nan],[prb:nan,7,0,13,3,49,119.35,12.86,7.91,6.32,-22.68,nan],[prp:-19.21,4,6,8,8,31,130.02,12.82,8.32,6.73,-19.21,nan],[prb:nan,4,6,8,8,31,130.02,12.82,8.32,6.73,-19.21,nan],[prp:-20.09,4,6,8,9,31,130.02,12.92,8.22,6.86,-20.09,nan],[prb:nan,4,6,8,9,31,130.02,12.92,8.22,6.86,-20.09,nan],[prp:-22.92,4,6,8,10,31,130.02,12.73,8.41,6.73,-22.92,nan],[prb:nan,4,6,8,10,31,130.02,12.73,8.41,6.73,-22.92,nan],[prp:-22.92,4,6,8,11,31,130.02,12.73,8.41,6.6,-22.92,nan],[prb:nan,4,6,8,11,31,130.02,12.73,8.41,6.6,-22.92,nan]</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
@@ -2642,10 +2754,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C38" t="n">
-        <v>63865158140035</v>
+        <v>63865158140032</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2653,7 +2765,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>63865158090014</v>
+        <v>63865158090013</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2661,33 +2773,33 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>63865158370053</v>
-      </c>
-      <c r="H38" t="inlineStr"/>
+        <v>63865158370012</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>AOT</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+          <t>group_pb_button-group_pb_test-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,4,6,8,8,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,9,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,10,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,11,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,7,8,12,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,13,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,14,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,15,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,4,8,0,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,1,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,2,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,3,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,5,8,4,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,5,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,6,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,7,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,16,6,32,8,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,9,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,10,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,11,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,7,32,12,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,13,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,14,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,15,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,4,32,0,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,1,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,2,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,3,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,5,32,4,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,5,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,6,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,7,126,0,31.84,-327.68,-1,-100]</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Try to test the ELS module on AOT master unit</t>
-        </is>
-      </c>
+          <t>group_pb_pushed-Verify group_pb button pushed</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
@@ -2700,30 +2812,12 @@
       <c r="Z38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>32</v>
-      </c>
-      <c r="C39" t="n">
-        <v>63865158140036</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>63865158090017</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
@@ -2732,17 +2826,17 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>AOT</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+          <t>sbc_storage_usb-passmark-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:13.23,9,0,17,0,65,0,31.17,1.71,13.23,-100],[eocl:13.23,9,0,17,1,65,0,31.17,1.71,13.23,-100],[eocl:13.23,9,0,17,2,65,0,31.17,1.71,13.23,-100],[eocl:13.64,9,0,17,3,65,0,31.17,1.3,13.64,-100],[eocl:14.6,9,1,17,4,66,0,31.09,0.33,14.6,-100],[eocl:14.09,9,1,17,5,66,0,31.09,0.84,14.09,-100],[eocl:14.09,9,1,17,6,66,0,31.09,0.84,14.09,-100],[eocl:13.63,9,1,17,7,66,0,31.09,1.3,13.63,-100],[eocl:13.25,9,2,17,8,67,0,31.3,1.71,13.25,-100],[eocl:13.25,9,2,17,9,67,0,31.3,1.71,13.25,-100],[eocl:13.25,9,2,17,10,67,0,31.3,1.71,13.25,-100],[eocl:12.87,9,2,17,11,67,0,31.3,2.09,12.87,-100],[eocl:13.65,9,3,17,12,68,0,31.26,1.3,13.65,-100],[eocl:13.65,9,3,17,13,68,0,31.26,1.3,13.65,-100],[eocl:13.65,9,3,17,14,68,0,31.26,1.3,13.65,-100],[eocl:13.24,9,3,17,15,68,0,31.26,1.71,13.24,-100]</t>
+          <t>usb_passmark_pass-Verify usb device passed passmark</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
@@ -2764,10 +2858,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C40" t="n">
-        <v>63865158140031</v>
+        <v>63865158140033</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2775,7 +2869,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>63865158090046</v>
+        <v>63865158090011</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2783,16 +2877,32 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>63865158370021</v>
-      </c>
-      <c r="H40" t="inlineStr"/>
+        <v>63865158370022</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>query_fnm_linkup-linkup_polling_fnm-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>linkup_matrix_fnm-Failed: ['port 65/0', 'port 65/1']</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
@@ -2812,10 +2922,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C41" t="n">
-        <v>63865158140038</v>
+        <v>63865158140034</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2823,7 +2933,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>63865158090012</v>
+        <v>63865158090010</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2831,16 +2941,32 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>63865158370027</v>
-      </c>
-      <c r="H41" t="inlineStr"/>
+        <v>63865158370026</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,10,5,20,4,78,149.65,12.98,8.77,6.86,-22.37,nan],[prp:-22.37,10,5,20,4,78,149.65,12.98,8.77,6.86,-22.37,nan],[prb:nan,10,5,20,5,78,149.65,13.01,8.74,6.86,-22.37,nan],[prp:-22.37,10,5,20,5,78,149.65,13.01,8.74,6.86,-22.37,nan],[prb:nan,10,5,20,6,78,149.65,13.04,8.71,6.86,-20.97,nan],[prp:-20.97,10,5,20,6,78,149.65,13.04,8.71,6.86,-20.97,nan],[prb:nan,10,5,20,7,78,149.65,13.09,8.66,6.86,-20.22,nan],[prp:-20.22,10,5,20,7,78,149.65,13.09,8.66,6.86,-20.22,nan]</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
@@ -2860,10 +2986,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C42" t="n">
-        <v>63865158140039</v>
+        <v>63865158140035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2871,7 +2997,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>63865158090039</v>
+        <v>63865158090014</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2879,17 +3005,33 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>63865158370020</v>
+        <v>63865158370053</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,4,6,8,8,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,9,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,10,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,11,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,7,8,12,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,13,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,14,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,15,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,4,8,0,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,1,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,2,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,3,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,5,8,4,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,5,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,6,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,7,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,16,6,32,8,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,9,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,10,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,11,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,7,32,12,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,13,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,14,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,15,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,4,32,0,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,1,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,2,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,3,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,5,32,4,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,5,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,6,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,7,126,0,31.84,-327.68,-1,-100]</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Try to test the ELS module on AOT master unit</t>
+        </is>
+      </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
@@ -2908,10 +3050,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C43" t="n">
-        <v>63865158140040</v>
+        <v>63865158140036</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2919,7 +3061,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>63865158090016</v>
+        <v>63865158090017</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2927,16 +3069,28 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>63865158370055</v>
+        <v>63865158370037</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:13.23,9,0,17,0,65,0,31.17,1.71,13.23,-100],[eocl:13.23,9,0,17,1,65,0,31.17,1.71,13.23,-100],[eocl:13.23,9,0,17,2,65,0,31.17,1.71,13.23,-100],[eocl:13.64,9,0,17,3,65,0,31.17,1.3,13.64,-100],[eocl:14.6,9,1,17,4,66,0,31.09,0.33,14.6,-100],[eocl:14.09,9,1,17,5,66,0,31.09,0.84,14.09,-100],[eocl:14.09,9,1,17,6,66,0,31.09,0.84,14.09,-100],[eocl:13.63,9,1,17,7,66,0,31.09,1.3,13.63,-100],[eocl:13.25,9,2,17,8,67,0,31.3,1.71,13.25,-100],[eocl:13.25,9,2,17,9,67,0,31.3,1.71,13.25,-100],[eocl:13.25,9,2,17,10,67,0,31.3,1.71,13.25,-100],[eocl:12.87,9,2,17,11,67,0,31.3,2.09,12.87,-100],[eocl:13.65,9,3,17,12,68,0,31.26,1.3,13.65,-100],[eocl:13.65,9,3,17,13,68,0,31.26,1.3,13.65,-100],[eocl:13.65,9,3,17,14,68,0,31.26,1.3,13.65,-100],[eocl:13.24,9,3,17,15,68,0,31.26,1.71,13.24,-100]</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -2956,10 +3110,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C44" t="n">
-        <v>63865158140041</v>
+        <v>63865158140031</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2967,7 +3121,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>63865158090015</v>
+        <v>63865158090046</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2975,18 +3129,10 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>63865158370056</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+        <v>63865158370021</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
@@ -3012,10 +3158,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C45" t="n">
-        <v>63865158140042</v>
+        <v>63865158140038</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3023,7 +3169,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>63865158090019</v>
+        <v>63865158090012</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3031,28 +3177,16 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>63865158370047</v>
+        <v>63865158370027</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,13,4,26,0,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,1,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,2,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,3,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,5,26,4,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,5,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,6,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,7,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,6,26,8,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,9,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,10,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,11,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,7,26,12,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,13,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,14,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,15,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,14,0,27,0,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,1,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,2,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,3,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,1,27,4,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,5,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,6,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,7,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,2,27,8,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,9,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,10,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,11,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,3,27,12,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,13,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,14,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,15,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,4,28,0,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,1,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,2,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,3,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,5,28,4,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,5,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,6,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,7,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,6,28,8,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,9,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,10,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,11,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,7,28,12,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,13,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,14,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,15,112,0,31.85,-327.68,-1,-100]</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
@@ -3072,10 +3206,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C46" t="n">
-        <v>63865158140043</v>
+        <v>63865158140039</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3083,61 +3217,30 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>63865158090020</v>
+        <v>63865158090039</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>63865158370020</v>
+      </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>power_on_with_fw-late_livefish_detection-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>csm1_swb_maglan_asic_pcie-Fast_boot_asic_HBI_HW_failure_detected-Asic HBI HW failure detection for csm1_swb_maglan_asic_pcie</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Spectrum-6 in Flash Recovery Mode. 
-Suspect ASIC issue.
-NV : share details 
-JE130526T0960963100707
-E6B171_9_2_8
-</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>NV</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>SPE</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Waiting Debug</t>
-        </is>
-      </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
@@ -3151,13 +3254,27 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>40</v>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="C47" t="n">
+        <v>63865158140040</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>63865158090016</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>63865158370055</v>
+      </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
@@ -3185,15 +3302,37 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>41</v>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+        <v>37</v>
+      </c>
+      <c r="C48" t="n">
+        <v>63865158140041</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>63865158090015</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>63865158370056</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
@@ -3219,21 +3358,47 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>42</v>
-      </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="C49" t="n">
+        <v>63865158140042</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>63865158090019</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>63865158370047</v>
+      </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,13,4,26,0,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,1,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,2,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,3,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,5,26,4,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,5,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,6,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,7,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,6,26,8,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,9,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,10,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,11,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,7,26,12,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,13,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,14,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,15,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,14,0,27,0,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,1,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,2,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,3,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,1,27,4,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,5,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,6,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,7,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,2,27,8,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,9,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,10,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,11,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,3,27,12,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,13,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,14,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,15,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,4,28,0,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,1,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,2,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,3,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,5,28,4,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,5,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,6,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,7,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,6,28,8,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,9,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,10,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,11,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,7,28,12,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,13,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,14,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,15,112,0,31.85,-327.68,-1,-100]</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
@@ -3253,27 +3418,72 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>43</v>
-      </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="C50" t="n">
+        <v>63865158140043</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>63865158090020</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>power_on_with_fw-late_livefish_detection-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>csm1_swb_maglan_asic_pcie-Fast_boot_asic_HBI_HW_failure_detected-Asic HBI HW failure detection for csm1_swb_maglan_asic_pcie</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spectrum-6 in Flash Recovery Mode. 
+Suspect ASIC issue.
+NV : share details 
+JE130526T0960963100707
+E6B171_9_2_8
+</t>
+        </is>
+      </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>SPE</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Waiting Debug</t>
+        </is>
+      </c>
       <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
@@ -3287,7 +3497,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
@@ -3321,27 +3531,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>45</v>
-      </c>
-      <c r="C52" t="n">
-        <v>63865158140044</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>63865158100002</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
-        <v>63865158390004</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
@@ -3369,47 +3565,21 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>46</v>
-      </c>
-      <c r="C53" t="n">
-        <v>63865158140045</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>63865158090025</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
-        <v>63865158370045</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,2,2,3,8,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,9,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,10,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,11,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,3,3,12,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,13,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,14,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,15,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,0,3,0,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,1,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,2,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,3,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,1,3,4,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,5,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,6,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,7,10,0,31.47,-327.68,-1,-100]</t>
-        </is>
-      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
@@ -3429,27 +3599,13 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>47</v>
-      </c>
-      <c r="C54" t="n">
-        <v>63865158140046</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>63865158090030</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>63865158370048</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
@@ -3477,24 +3633,12 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>48</v>
-      </c>
-      <c r="C55" t="n">
-        <v>63865158140047</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>63865158090035</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
@@ -3523,10 +3667,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C56" t="n">
-        <v>63865158140048</v>
+        <v>63865158140044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3534,7 +3678,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>63865158090043</v>
+        <v>63865158100002</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -3542,7 +3686,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>63865158370043</v>
+        <v>63865158390004</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
@@ -3571,10 +3715,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C57" t="n">
-        <v>63865158140049</v>
+        <v>63865158140045</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -3582,7 +3726,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>63865158090036</v>
+        <v>63865158090025</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -3590,16 +3734,40 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>63865158370041</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+        <v>63865158370045</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,2,2,3,8,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,9,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,10,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,11,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,3,3,12,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,13,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,14,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,15,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,0,3,0,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,1,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,2,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,3,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,1,3,4,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,5,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,6,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,7,10,0,31.47,-327.68,-1,-100]</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -3613,41 +3781,33 @@
       <c r="Z57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>51</v>
-      </c>
-      <c r="C58" t="n">
-        <v>63865158140050</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>63865158090040</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>63865158370050</v>
-      </c>
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:11.26,12,4,24,0,93,250,32.47,3.85,11.26,-100],[eocl:11.5,12,4,24,1,93,250,32.47,3.61,11.5,-100],[eocl:11.26,12,4,24,2,93,250,32.47,3.85,11.26,-100],[eocl:11.02,12,4,24,3,93,250,32.47,4.09,11.02,-100],[eocl:11.06,12,5,24,4,94,250,32.77,4.09,11.06,-100],[eocl:11.3,12,5,24,5,94,250,32.77,3.85,11.3,-100],[eocl:11.06,12,5,24,6,94,250,32.77,4.09,11.06,-100],[eocl:11.06,12,5,24,7,94,250,32.77,4.09,11.06,-100],[eocl:11.01,12,6,24,8,95,250,32.36,4.09,11.01,-100],[eocl:11.25,12,6,24,9,95,250,32.36,3.85,11.25,-100],[eocl:11.01,12,6,24,10,95,250,32.36,4.09,11.01,-100],[eocl:11.01,12,6,24,11,95,250,32.36,4.09,11.01,-100],[eocl:11.5,12,7,24,12,96,250,32.47,3.61,11.5,-100],[eocl:11.5,12,7,24,13,96,250,32.47,3.61,11.5,-100],[eocl:11.77,12,7,24,14,96,250,32.47,3.34,11.77,-100],[eocl:11.77,12,7,24,15,96,250,32.47,3.34,11.77,-100]</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
@@ -3667,10 +3827,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C59" t="n">
-        <v>63865158140052</v>
+        <v>63865158140046</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3678,7 +3838,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>63865158090044</v>
+        <v>63865158090030</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -3686,16 +3846,28 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>63865158370046</v>
+        <v>63865158370048</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,4,6,8,8,31,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,6,8,9,31,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,6,8,10,31,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,6,8,11,31,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,7,8,12,32,0,31.3,-327.68,-1,-100],[eocl:-1.0,4,7,8,13,32,0,31.3,-327.68,-1,-100],[eocl:-1.0,4,7,8,14,32,0,31.3,-327.68,-1,-100],[eocl:-1.0,4,7,8,15,32,0,31.3,-327.68,-1,-100],[eocl:-1.0,4,4,8,0,29,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,4,8,1,29,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,4,8,2,29,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,4,8,3,29,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,5,8,4,30,0,31.35,-327.68,-1,-100],[eocl:-1.0,4,5,8,5,30,0,31.35,-327.68,-1,-100],[eocl:-1.0,4,5,8,6,30,0,31.35,-327.68,-1,-100],[eocl:-1.0,4,5,8,7,30,0,31.35,-327.68,-1,-100],[eocl:-1.0,1,2,1,8,3,0,31.61,-327.68,-1,-100],[eocl:-1.0,1,2,1,9,3,0,31.61,-327.68,-1,-100],[eocl:-1.0,1,2,1,10,3,0,31.61,-327.68,-1,-100],[eocl:-1.0,1,2,1,11,3,0,31.61,-327.68,-1,-100],[eocl:-1.0,1,3,1,12,4,0,31.47,-327.68,-1,-100],[eocl:-1.0,1,3,1,13,4,0,31.47,-327.68,-1,-100],[eocl:-1.0,1,3,1,14,4,0,31.47,-327.68,-1,-100],[eocl:-1.0,1,3,1,15,4,0,31.47,-327.68,-1,-100],[eocl:-1.0,1,0,1,0,1,0,31.5,-327.68,-1,-100],[eocl:-1.0,1,0,1,1,1,0,31.5,-327.68,-1,-100],[eocl:-1.0,1,0,1,2,1,0,31.5,-327.68,-1,-100],[eocl:-1.0,1,0,1,3,1,0,31.5,-327.68,-1,-100],[eocl:-1.0,1,1,1,4,2,0,31.71,-327.68,-1,-100],[eocl:-1.0,1,1,1,5,2,0,31.71,-327.68,-1,-100],[eocl:-1.0,1,1,1,6,2,0,31.71,-327.68,-1,-100],[eocl:-1.0,1,1,1,7,2,0,31.71,-327.68,-1,-100]</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
@@ -3715,10 +3887,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C60" t="n">
-        <v>63865158140031</v>
+        <v>63865158140047</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -3726,7 +3898,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>63865158090046</v>
+        <v>63865158090035</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3734,30 +3906,33 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>63865158370049</v>
+        <v>63865158370029</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>PASS FT - Fail at HS cold test GOOD RX , NO BER 
-30-SEP : cookbook flow (LPBK remating / cleaning / crossing, Windu cross) -&gt; still fail replace CSM</t>
-        </is>
-      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,9,6,18,8,71,124.64,12.86,8.1,6.73,-18.24,nan],[prp:-18.24,9,6,18,8,71,124.64,12.86,8.1,6.73,-18.24,nan],[prb:nan,9,6,18,9,71,124.64,12.86,8.1,6.73,-18.15,nan],[prp:-18.15,9,6,18,9,71,124.64,12.86,8.1,6.73,-18.15,nan],[prb:nan,9,6,18,10,71,124.64,12.79,8.17,6.73,-19.47,nan],[prp:-19.47,9,6,18,10,71,124.64,12.79,8.17,6.73,-19.47,nan],[prb:nan,9,6,18,11,71,124.64,12.7,8.26,6.6,-19.47,nan],[prp:-19.47,9,6,18,11,71,124.64,12.7,8.26,6.6,-19.47,nan],[prb:nan,5,1,9,4,34,128.8,12.95,8.15,6.86,-22.68,nan],[prp:-22.68,5,1,9,4,34,128.8,12.95,8.15,6.86,-22.68,nan],[prb:nan,5,1,9,5,34,128.8,12.82,8.28,6.86,-21.87,nan],[prp:-21.87,5,1,9,5,34,128.8,12.82,8.28,6.86,-21.87,nan],[prb:nan,5,1,9,6,34,128.8,12.95,8.15,6.86,-22.37,nan],[prp:-22.37,5,1,9,6,34,128.8,12.95,8.15,6.86,-22.37,nan],[prb:nan,5,1,9,7,34,128.8,12.95,8.15,6.86,-22.08,nan],[prp:-22.08,5,1,9,7,34,128.8,12.95,8.15,6.86,-22.08,nan]</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
@@ -3776,10 +3951,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C61" t="n">
-        <v>63865158140055</v>
+        <v>63865158140048</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3787,7 +3962,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>63865158090045</v>
+        <v>63865158090043</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -3795,16 +3970,28 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>63865158370023</v>
+        <v>63865158370043</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,10,0,19,0,73,0,31.02,0,-1,-100],[eocl:-1.0,10,0,19,1,73,0,31.02,0,-1,-100],[eocl:-1.0,10,0,19,2,73,0,31.02,0,-1,-100],[eocl:-1.0,10,0,19,3,73,0,31.02,0,-1,-100],[eocl:-1.0,10,1,19,4,74,0,31.07,0,-1,-100],[eocl:-1.0,10,1,19,5,74,0,31.07,0,-1,-100],[eocl:-1.0,10,1,19,6,74,0,31.07,0,-1,-100],[eocl:-1.0,10,1,19,7,74,0,31.07,0,-1,-100],[eocl:-1.0,10,2,19,8,75,0,31.46,0,-1,-100],[eocl:-1.0,10,2,19,9,75,0,31.46,0,-1,-100],[eocl:-1.0,10,2,19,10,75,0,31.46,0,-1,-100],[eocl:-1.0,10,2,19,11,75,0,31.46,0,-1,-100],[eocl:-1.0,10,3,19,12,76,0,31.59,0,-1,-100],[eocl:-1.0,10,3,19,13,76,0,31.59,0,-1,-100],[eocl:-1.0,10,3,19,14,76,0,31.59,0,-1,-100],[eocl:-1.0,10,3,19,15,76,0,31.59,0,-1,-100]</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
@@ -3824,19 +4011,27 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C62" t="n">
-        <v>63865158140051</v>
+        <v>63865158140049</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
+      <c r="E62" t="n">
+        <v>63865158090036</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>63865158370041</v>
+      </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
@@ -3864,10 +4059,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C63" t="n">
-        <v>63865158140056</v>
+        <v>63865158140050</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -3875,10 +4070,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>63865158090047</v>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
+        <v>63865158090040</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>63865158370050</v>
+      </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
@@ -3906,19 +4107,27 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C64" t="n">
-        <v>63865158140057</v>
+        <v>63865158140052</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
+      <c r="E64" t="n">
+        <v>63865158090044</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>63865158370046</v>
+      </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
@@ -3946,19 +4155,27 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C65" t="n">
-        <v>63865158140062</v>
+        <v>63865158140031</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
+      <c r="E65" t="n">
+        <v>63865158090046</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>63865158370049</v>
+      </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
@@ -3986,24 +4203,61 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C66" t="n">
-        <v>63865158140060</v>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
+        <v>63865158140055</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>63865158090045</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>63865158370023</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>query_fnm_linkup-linkup_polling_fnm-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>linkup_matrix_fnm-Failed: ['port 65/0', 'port 65/1']</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>PASS FT - Fail at HS cold test GOOD RX , NO BER 
+30-SEP : cookbook flow (LPBK remating / cleaning / crossing, Windu cross) -&gt; still fail replace CSM</t>
+        </is>
+      </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
@@ -4022,19 +4276,27 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C67" t="n">
-        <v>63865158140061</v>
+        <v>63865158140051</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
+      <c r="E67" t="n">
+        <v>63865158090049</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>63865158370039</v>
+      </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
@@ -4062,13 +4324,19 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C68" t="n">
-        <v>63865158140058</v>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
+        <v>63865158140056</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>63865158090047</v>
+      </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
@@ -4098,15 +4366,27 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C69" t="n">
-        <v>63865158140059</v>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
+        <v>63865158140057</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>63865158090051</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>63865158370038</v>
+      </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
@@ -4127,6 +4407,198 @@
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="inlineStr"/>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>58</v>
+      </c>
+      <c r="C70" t="n">
+        <v>63865158140062</v>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr"/>
+      <c r="X70" t="inlineStr"/>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>59</v>
+      </c>
+      <c r="C71" t="n">
+        <v>63865158140060</v>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr"/>
+      <c r="X71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>60</v>
+      </c>
+      <c r="C72" t="n">
+        <v>63865158140061</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>63865158090050</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>63865158370040</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr"/>
+      <c r="X72" t="inlineStr"/>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>61</v>
+      </c>
+      <c r="C73" t="n">
+        <v>63865158140058</v>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>62</v>
+      </c>
+      <c r="C74" t="n">
+        <v>63865158140059</v>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr"/>
+      <c r="X74" t="inlineStr"/>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/TS3_mapping.xlsx
+++ b/TS3_mapping.xlsx
@@ -3464,6 +3464,8 @@
 NV : share details 
 JE130526T0960963100707
 E6B171_9_2_8
+01 OCT: ULT E6B171_9_2_8 passed FT on rev_2B.
+It passed HBI HS test, without failures (FT1 and FT2).
 </t>
         </is>
       </c>
@@ -3512,7 +3514,11 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>units that will be tested in the automation</t>
+        </is>
+      </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
@@ -3648,7 +3654,11 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>units that will be tested in the automation</t>
+        </is>
+      </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>

--- a/TS3_mapping.xlsx
+++ b/TS3_mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z74"/>
+  <dimension ref="A1:Z75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,7 +797,11 @@
           <t>MT2640600GZR</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>FT</t>
@@ -826,59 +830,31 @@
       <c r="Z5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" t="n">
-        <v>63865158140004</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>63865158090008</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>63865158370005</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>DEV032309</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>CUST</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+          <t>fuse_mismatch_group1-read_fuse_missmatch-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,4,6,8,8,31,159.81,13.07,8.97,6.73,-2.69,nan],[prp:-22.68,4,6,8,9,31,159.81,13.04,9,6.86,-22.68,nan],[prb:nan,4,6,8,9,31,159.81,13.04,9,6.86,-22.68,nan],[prp:-19.21,4,6,8,10,31,159.81,13.15,8.89,6.99,-19.21,nan],[prb:nan,4,6,8,10,31,159.81,13.15,8.89,6.99,-19.21,nan],[prp:-19.47,4,6,8,11,31,159.81,12.95,9.09,6.73,-19.47,nan],[prb:nan,4,6,8,11,31,159.81,12.95,9.09,6.73,-19.47,nan],[prp:-18.7,4,7,8,12,32,180.92,13.4,9.17,7.11,-18.7,nan],[prb:nan,4,7,8,12,32,180.92,13.4,9.17,7.11,-18.7,nan],[prp:-18.93,4,7,8,13,32,180.92,13.32,9.25,7.11,-18.93,nan],[prb:nan,4,7,8,13,32,180.92,13.32,9.25,7.11,-18.93,nan],[prp:-22.37,4,7,8,14,32,180.92,13.4,9.17,7.23,-22.37,nan],[prb:nan,4,7,8,14,32,180.92,13.4,9.17,7.23,-22.37,nan],[prp:-22.37,4,7,8,15,32,180.92,13.12,9.45,6.86,-22.37,nan],[prb:nan,4,7,8,15,32,180.92,13.12,9.45,6.86,-22.37,nan],[prp:-19.32,4,3,7,12,28,164.29,13.15,9.01,6.73,-19.32,nan],[prb:nan,4,3,7,12,28,164.29,13.15,9.01,6.73,-19.32,nan],[prb:nan,4,3,7,13,28,164.29,13.09,9.07,6.6,-2.67,nan],[prb:nan,4,3,7,14,28,164.29,13.04,9.12,6.73,-2.48,nan],[prb:nan,4,3,7,15,28,164.29,12.98,9.18,6.73,-2.16,nan],[prp:-20.76,3,6,6,8,23,130.09,12.79,8.35,6.6,-20.76,nan],[prb:nan,3,6,6,8,23,130.09,12.79,8.35,6.6,-20.76,nan],[prb:nan,3,6,6,9,23,130.09,12.95,8.19,6.6,-2.6,nan],[prb:nan,3,6,6,10,23,130.09,12.82,8.32,6.46,-1.81,nan],[prb:nan,3,6,6,11,23,130.09,12.82,8.32,6.6,-2.1,nan],[prb:nan,3,7,6,12,24,144.49,12.98,8.62,6.73,-2.24,nan],[prb:nan,3,7,6,13,24,144.49,13.12,8.48,6.86,-2.84,nan],[prb:nan,3,7,6,14,24,144.49,13.07,8.53,6.73,-2.41,nan],[prp:-18.04,3,7,6,15,24,144.49,12.79,8.81,6.46,-18.04,nan],[prb:nan,3,7,6,15,24,144.49,12.79,8.81,6.46,-18.04,nan],[prb:nan,3,4,6,0,21,134.46,13.01,8.28,6.73,-2.91,nan],[prb:nan,3,4,6,1,21,134.46,12.82,8.47,6.6,-2.4,nan],[prp:-19.07,3,4,6,2,21,134.46,12.82,8.47,6.73,-19.07,nan],[prb:nan,3,4,6,2,21,134.46,12.82,8.47,6.73,-19.07,nan],[prb:nan,3,4,6,3,21,134.46,12.95,8.34,6.73,-2.4,nan]</t>
+          <t>csm1_swb_maglan_asic_pcie_mng.yu_boot.fuse_ctrl.redundency_missmatch_cause-crspace_reg_read:mng.yu_boot.fuse_ctrl.redundency_missmatch_cause</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -900,10 +876,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>63865158140003</v>
+        <v>63865158140004</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -911,7 +887,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>63865158090004</v>
+        <v>63865158090008</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -919,7 +895,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>63865158370003</v>
+        <v>63865158370005</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -938,12 +914,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>MT2640600H02</t>
+          <t>MT2640600GZW</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -958,32 +934,15 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,10,0,19,0,73,104.44,12.82,7.37,6.6,-22.08,nan],[prp:-22.08,10,0,19,0,73,104.44,12.82,7.37,6.6,-22.08,nan],[prb:nan,10,0,19,1,73,104.44,12.7,7.49,6.6,-21.87,nan],[prp:-21.87,10,0,19,1,73,104.44,12.7,7.49,6.6,-21.87,nan],[prb:nan,10,0,19,2,73,104.44,12.7,7.49,6.46,-18.48,nan],[prp:-18.48,10,0,19,2,73,104.44,12.7,7.49,6.46,-18.48,nan],[prb:nan,10,0,19,3,73,104.44,12.82,7.37,6.6,-18.36,nan],[prp:-18.36,10,0,19,3,73,104.44,12.82,7.37,6.6,-18.36,nan]</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>ELS10 OE19 0~3 MMC73 no RxP, MMC73 LB not full inserted.
-Reinsert then test pass.</t>
-        </is>
-      </c>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,4,6,8,8,31,159.81,13.07,8.97,6.73,-2.69,nan],[prp:-22.68,4,6,8,9,31,159.81,13.04,9,6.86,-22.68,nan],[prb:nan,4,6,8,9,31,159.81,13.04,9,6.86,-22.68,nan],[prp:-19.21,4,6,8,10,31,159.81,13.15,8.89,6.99,-19.21,nan],[prb:nan,4,6,8,10,31,159.81,13.15,8.89,6.99,-19.21,nan],[prp:-19.47,4,6,8,11,31,159.81,12.95,9.09,6.73,-19.47,nan],[prb:nan,4,6,8,11,31,159.81,12.95,9.09,6.73,-19.47,nan],[prp:-18.7,4,7,8,12,32,180.92,13.4,9.17,7.11,-18.7,nan],[prb:nan,4,7,8,12,32,180.92,13.4,9.17,7.11,-18.7,nan],[prp:-18.93,4,7,8,13,32,180.92,13.32,9.25,7.11,-18.93,nan],[prb:nan,4,7,8,13,32,180.92,13.32,9.25,7.11,-18.93,nan],[prp:-22.37,4,7,8,14,32,180.92,13.4,9.17,7.23,-22.37,nan],[prb:nan,4,7,8,14,32,180.92,13.4,9.17,7.23,-22.37,nan],[prp:-22.37,4,7,8,15,32,180.92,13.12,9.45,6.86,-22.37,nan],[prb:nan,4,7,8,15,32,180.92,13.12,9.45,6.86,-22.37,nan],[prp:-19.32,4,3,7,12,28,164.29,13.15,9.01,6.73,-19.32,nan],[prb:nan,4,3,7,12,28,164.29,13.15,9.01,6.73,-19.32,nan],[prb:nan,4,3,7,13,28,164.29,13.09,9.07,6.6,-2.67,nan],[prb:nan,4,3,7,14,28,164.29,13.04,9.12,6.73,-2.48,nan],[prb:nan,4,3,7,15,28,164.29,12.98,9.18,6.73,-2.16,nan],[prp:-20.76,3,6,6,8,23,130.09,12.79,8.35,6.6,-20.76,nan],[prb:nan,3,6,6,8,23,130.09,12.79,8.35,6.6,-20.76,nan],[prb:nan,3,6,6,9,23,130.09,12.95,8.19,6.6,-2.6,nan],[prb:nan,3,6,6,10,23,130.09,12.82,8.32,6.46,-1.81,nan],[prb:nan,3,6,6,11,23,130.09,12.82,8.32,6.6,-2.1,nan],[prb:nan,3,7,6,12,24,144.49,12.98,8.62,6.73,-2.24,nan],[prb:nan,3,7,6,13,24,144.49,13.12,8.48,6.86,-2.84,nan],[prb:nan,3,7,6,14,24,144.49,13.07,8.53,6.73,-2.41,nan],[prp:-18.04,3,7,6,15,24,144.49,12.79,8.81,6.46,-18.04,nan],[prb:nan,3,7,6,15,24,144.49,12.79,8.81,6.46,-18.04,nan],[prb:nan,3,4,6,0,21,134.46,13.01,8.28,6.73,-2.91,nan],[prb:nan,3,4,6,1,21,134.46,12.82,8.47,6.6,-2.4,nan],[prp:-19.07,3,4,6,2,21,134.46,12.82,8.47,6.73,-19.07,nan],[prb:nan,3,4,6,2,21,134.46,12.82,8.47,6.73,-19.07,nan],[prb:nan,3,4,6,3,21,134.46,12.95,8.34,6.73,-2.4,nan]</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>FXV</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Peter</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
@@ -991,35 +950,96 @@
       <c r="Z7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>63865158140003</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>63865158090004</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>63865158370003</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>MT2640600H02</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>CUST</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>system_boot_group-check_sed_state-ERROR-OutOfBandException;</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,10,0,19,0,73,104.44,12.82,7.37,6.6,-22.08,nan],[prp:-22.08,10,0,19,0,73,104.44,12.82,7.37,6.6,-22.08,nan],[prb:nan,10,0,19,1,73,104.44,12.7,7.49,6.6,-21.87,nan],[prp:-21.87,10,0,19,1,73,104.44,12.7,7.49,6.6,-21.87,nan],[prb:nan,10,0,19,2,73,104.44,12.7,7.49,6.46,-18.48,nan],[prp:-18.48,10,0,19,2,73,104.44,12.7,7.49,6.46,-18.48,nan],[prb:nan,10,0,19,3,73,104.44,12.82,7.37,6.6,-18.36,nan],[prp:-18.36,10,0,19,3,73,104.44,12.82,7.37,6.6,-18.36,nan]</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>ELS10 OE19 0~3 MMC73 no RxP, MMC73 LB not full inserted.
+Reinsert then test pass.</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
@@ -1046,14 +1066,10 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>fuse_mismatch_group1-read_fuse_missmatch-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>csm1_swb_maglan_asic_pcie_mng.yu_boot.fuse_ctrl.redundency_missmatch_cause-crspace_reg_read:mng.yu_boot.fuse_ctrl.redundency_missmatch_cause</t>
-        </is>
-      </c>
+          <t>system_boot_group-check_sed_state-ERROR-OutOfBandException;</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
@@ -1067,84 +1083,39 @@
       <c r="Z9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" t="n">
-        <v>63865158140002</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>63865158090001</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>63865158370007</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>DEV032309</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>CUST</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+          <t>fuse_mismatch_group1-read_fuse_missmatch-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,2,4,4,0,13,134.85,12.89,8.41,6.6,-2.34,nan],[prb:nan,2,4,4,1,13,134.85,12.79,8.51,6.6,-2.89,nan],[prb:nan,2,4,4,2,13,134.85,12.86,8.44,6.6,-2.45,nan],[prb:nan,2,4,4,3,13,134.85,12.98,8.32,6.73,0.15,nan]</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>High speed fail; ELS2 OE4 Lane0~3 no BER
-30-SEP : cookbook flow (LPBK remating / cleaning / crossing, Windu cross) -&gt; still fail replace CSM</t>
-        </is>
-      </c>
+          <t>csm1_swb_maglan_asic_pcie_mng.yu_boot.fuse_ctrl.redundency_missmatch_cause-crspace_reg_read:mng.yu_boot.fuse_ctrl.redundency_missmatch_cause</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>NV</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>SPE</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Waiting Debug</t>
-        </is>
-      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
@@ -1158,10 +1129,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>63865158140006</v>
+        <v>63865158140002</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1169,7 +1140,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>63865158090002</v>
+        <v>63865158090001</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1177,7 +1148,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>63865158370002</v>
+        <v>63865158370007</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1202,13 +1173,34 @@
           <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,2,4,4,0,13,134.85,12.89,8.41,6.6,-2.34,nan],[prb:nan,2,4,4,1,13,134.85,12.79,8.51,6.6,-2.89,nan],[prb:nan,2,4,4,2,13,134.85,12.86,8.44,6.6,-2.45,nan],[prb:nan,2,4,4,3,13,134.85,12.98,8.32,6.73,0.15,nan]</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>High speed fail; ELS2 OE4 Lane0~3 no BER
+30-SEP : cookbook flow (LPBK remating / cleaning / crossing, Windu cross) -&gt; still fail replace CSM</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>SPE</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Waiting Debug</t>
+        </is>
+      </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
@@ -1222,10 +1214,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>63865158140007</v>
+        <v>63865158140006</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1233,7 +1225,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>63865158090009</v>
+        <v>63865158090002</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1241,18 +1233,14 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>63865158370006</v>
+        <v>63865158370002</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>DEV032309</t>
@@ -1270,11 +1258,7 @@
           <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,7,2,13,8,51,134.29,12.76,8.52,6.6,-19.63,nan],[prp:-19.63,7,2,13,8,51,134.29,12.76,8.52,6.6,-19.63,nan],[prb:nan,7,2,13,9,51,134.29,12.86,8.42,6.73,-19.75,nan],[prp:-19.75,7,2,13,9,51,134.29,12.86,8.42,6.73,-19.75,nan],[prb:nan,7,2,13,10,51,134.29,12.76,8.52,6.6,-20.97,nan],[prp:-20.97,7,2,13,10,51,134.29,12.76,8.52,6.6,-20.97,nan],[prb:nan,7,2,13,11,51,134.29,12.67,8.61,6.46,-20.97,nan],[prp:-20.97,7,2,13,11,51,134.29,12.67,8.61,6.46,-20.97,nan],[prb:nan,9,7,18,12,72,134.62,12.92,8.37,6.6,-20.6,nan],[prp:-20.6,9,7,18,12,72,134.62,12.92,8.37,6.6,-20.6,nan],[prb:nan,9,7,18,13,72,134.62,12.95,8.34,6.73,-20.41,nan],[prp:-20.41,9,7,18,13,72,134.62,12.95,8.34,6.73,-20.41,nan],[prb:nan,9,7,18,14,72,134.62,13.04,8.25,6.86,-19.47,nan],[prp:-19.47,9,7,18,14,72,134.62,13.04,8.25,6.86,-19.47,nan],[prb:nan,9,7,18,15,72,134.62,12.89,8.4,6.86,-19.75,nan],[prp:-19.75,9,7,18,15,72,134.62,12.89,8.4,6.86,-19.75,nan],[prb:nan,11,0,21,0,81,124.53,12.92,8.03,6.73,-21.19,nan],[prp:-21.19,11,0,21,0,81,124.53,12.92,8.03,6.73,-21.19,nan],[prb:nan,11,0,21,1,81,124.53,12.82,8.13,6.73,-21.87,nan],[prp:-21.87,11,0,21,1,81,124.53,12.82,8.13,6.73,-21.87,nan],[prb:nan,11,0,21,2,81,124.53,12.86,8.09,6.6,-20.6,nan],[prp:-20.6,11,0,21,2,81,124.53,12.86,8.09,6.6,-20.6,nan],[prb:nan,11,0,21,3,81,124.53,12.92,8.03,6.73,-20.41,nan],[prp:-20.41,11,0,21,3,81,124.53,12.92,8.03,6.73,-20.41,nan],[prb:nan,11,6,22,8,87,149.85,12.89,8.87,6.73,-20.09,nan],[prp:-20.09,11,6,22,8,87,149.85,12.89,8.87,6.73,-20.09,nan],[prb:nan,11,6,22,9,87,149.85,13.01,8.75,6.86,-20.09,nan],[prp:-20.09,11,6,22,9,87,149.85,13.01,8.75,6.86,-20.09,nan],[prb:nan,11,6,22,10,87,149.85,12.73,9.03,6.73,-19.47,nan],[prp:-19.47,11,6,22,10,87,149.85,12.73,9.03,6.73,-19.47,nan],[prb:nan,11,6,22,11,87,149.85,12.73,9.03,6.46,-19.47,nan],[prp:-19.47,11,6,22,11,87,149.85,12.73,9.03,6.46,-19.47,nan],[prb:nan,15,3,29,12,116,119.23,12.89,7.87,6.73,-21.87,nan],[prp:-21.87,15,3,29,12,116,119.23,12.89,7.87,6.73,-21.87,nan],[prb:nan,15,3,29,13,116,119.23,12.98,7.78,6.73,-21.87,nan],[prp:-21.87,15,3,29,13,116,119.23,12.98,7.78,6.73,-21.87,nan],[prb:nan,15,3,29,14,116,119.23,12.82,7.94,6.6,-19.32,nan],[prp:-19.32,15,3,29,14,116,119.23,12.82,7.94,6.6,-19.32,nan],[prb:nan,15,3,29,15,116,119.23,12.89,7.87,6.73,-19.91,nan],[prp:-19.91,15,3,29,15,116,119.23,12.89,7.87,6.73,-19.91,nan]</t>
-        </is>
-      </c>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
@@ -1294,10 +1278,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>63865158140008</v>
+        <v>63865158140007</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1305,7 +1289,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>63865158090006</v>
+        <v>63865158090009</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1313,7 +1297,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>63865158370004</v>
+        <v>63865158370006</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1332,12 +1316,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>MT2640600GZ1</t>
+          <t>MT2640600GZT</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1352,7 +1336,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,7,4,14,0,53,128.58,13.01,8.08,6.73,-19.91,nan],[prp:-19.91,7,4,14,0,53,128.58,13.01,8.08,6.73,-19.91,nan],[prb:nan,7,4,14,1,53,128.58,12.79,8.3,6.73,-19.91,nan],[prp:-19.91,7,4,14,1,53,128.58,12.79,8.3,6.73,-19.91,nan],[prb:nan,7,4,14,2,53,128.58,13.04,8.05,6.99,-20.09,nan],[prp:-20.09,7,4,14,2,53,128.58,13.04,8.05,6.99,-20.09,nan],[prb:nan,7,4,14,3,53,128.58,12.98,8.11,6.86,-19.91,nan],[prp:-19.91,7,4,14,3,53,128.58,12.98,8.11,6.86,-19.91,nan]</t>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,7,2,13,8,51,134.29,12.76,8.52,6.6,-19.63,nan],[prp:-19.63,7,2,13,8,51,134.29,12.76,8.52,6.6,-19.63,nan],[prb:nan,7,2,13,9,51,134.29,12.86,8.42,6.73,-19.75,nan],[prp:-19.75,7,2,13,9,51,134.29,12.86,8.42,6.73,-19.75,nan],[prb:nan,7,2,13,10,51,134.29,12.76,8.52,6.6,-20.97,nan],[prp:-20.97,7,2,13,10,51,134.29,12.76,8.52,6.6,-20.97,nan],[prb:nan,7,2,13,11,51,134.29,12.67,8.61,6.46,-20.97,nan],[prp:-20.97,7,2,13,11,51,134.29,12.67,8.61,6.46,-20.97,nan],[prb:nan,9,7,18,12,72,134.62,12.92,8.37,6.6,-20.6,nan],[prp:-20.6,9,7,18,12,72,134.62,12.92,8.37,6.6,-20.6,nan],[prb:nan,9,7,18,13,72,134.62,12.95,8.34,6.73,-20.41,nan],[prp:-20.41,9,7,18,13,72,134.62,12.95,8.34,6.73,-20.41,nan],[prb:nan,9,7,18,14,72,134.62,13.04,8.25,6.86,-19.47,nan],[prp:-19.47,9,7,18,14,72,134.62,13.04,8.25,6.86,-19.47,nan],[prb:nan,9,7,18,15,72,134.62,12.89,8.4,6.86,-19.75,nan],[prp:-19.75,9,7,18,15,72,134.62,12.89,8.4,6.86,-19.75,nan],[prb:nan,11,0,21,0,81,124.53,12.92,8.03,6.73,-21.19,nan],[prp:-21.19,11,0,21,0,81,124.53,12.92,8.03,6.73,-21.19,nan],[prb:nan,11,0,21,1,81,124.53,12.82,8.13,6.73,-21.87,nan],[prp:-21.87,11,0,21,1,81,124.53,12.82,8.13,6.73,-21.87,nan],[prb:nan,11,0,21,2,81,124.53,12.86,8.09,6.6,-20.6,nan],[prp:-20.6,11,0,21,2,81,124.53,12.86,8.09,6.6,-20.6,nan],[prb:nan,11,0,21,3,81,124.53,12.92,8.03,6.73,-20.41,nan],[prp:-20.41,11,0,21,3,81,124.53,12.92,8.03,6.73,-20.41,nan],[prb:nan,11,6,22,8,87,149.85,12.89,8.87,6.73,-20.09,nan],[prp:-20.09,11,6,22,8,87,149.85,12.89,8.87,6.73,-20.09,nan],[prb:nan,11,6,22,9,87,149.85,13.01,8.75,6.86,-20.09,nan],[prp:-20.09,11,6,22,9,87,149.85,13.01,8.75,6.86,-20.09,nan],[prb:nan,11,6,22,10,87,149.85,12.73,9.03,6.73,-19.47,nan],[prp:-19.47,11,6,22,10,87,149.85,12.73,9.03,6.73,-19.47,nan],[prb:nan,11,6,22,11,87,149.85,12.73,9.03,6.46,-19.47,nan],[prp:-19.47,11,6,22,11,87,149.85,12.73,9.03,6.46,-19.47,nan],[prb:nan,15,3,29,12,116,119.23,12.89,7.87,6.73,-21.87,nan],[prp:-21.87,15,3,29,12,116,119.23,12.89,7.87,6.73,-21.87,nan],[prb:nan,15,3,29,13,116,119.23,12.98,7.78,6.73,-21.87,nan],[prp:-21.87,15,3,29,13,116,119.23,12.98,7.78,6.73,-21.87,nan],[prb:nan,15,3,29,14,116,119.23,12.82,7.94,6.6,-19.32,nan],[prp:-19.32,15,3,29,14,116,119.23,12.82,7.94,6.6,-19.32,nan],[prb:nan,15,3,29,15,116,119.23,12.89,7.87,6.73,-19.91,nan],[prp:-19.91,15,3,29,15,116,119.23,12.89,7.87,6.73,-19.91,nan]</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1368,29 +1352,73 @@
       <c r="Z13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C14" t="n">
+        <v>63865158140008</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>63865158090006</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>63865158370004</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>MT2640600GZ1</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>CUST</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>laser_tests_prerequisites-linkup_setup-ERROR-ShellException;</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,7,4,14,0,53,128.58,13.01,8.08,6.73,-19.91,nan],[prp:-19.91,7,4,14,0,53,128.58,13.01,8.08,6.73,-19.91,nan],[prb:nan,7,4,14,1,53,128.58,12.79,8.3,6.73,-19.91,nan],[prp:-19.91,7,4,14,1,53,128.58,12.79,8.3,6.73,-19.91,nan],[prb:nan,7,4,14,2,53,128.58,13.04,8.05,6.99,-20.09,nan],[prp:-20.09,7,4,14,2,53,128.58,13.04,8.05,6.99,-20.09,nan],[prb:nan,7,4,14,3,53,128.58,12.98,8.11,6.86,-19.91,nan],[prp:-19.91,7,4,14,3,53,128.58,12.98,8.11,6.86,-19.91,nan]</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
@@ -1423,7 +1451,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>fuse_mismatch_group1-read_fuse_missmatch-FAIL-MEASUREMENT;</t>
+          <t>laser_tests_prerequisites-linkup_setup-ERROR-ShellException;</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
@@ -1440,57 +1468,33 @@
       <c r="Z15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>9</v>
-      </c>
-      <c r="C16" t="n">
-        <v>63865158140009</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>63865158090007</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>63865158370008</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>DEV032309</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>MT2640600GZ0</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>CUST</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>fuse_mismatch_group1-read_fuse_missmatch-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>csm1_swb_maglan_asic_pcie_mng.yu_boot.fuse_ctrl.redundency_missmatch_cause-crspace_reg_read:mng.yu_boot.fuse_ctrl.redundency_missmatch_cause</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
@@ -1510,10 +1514,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>63865158140010</v>
+        <v>63865158140009</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1521,7 +1525,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>63865158090005</v>
+        <v>63865158090007</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1529,59 +1533,54 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>63865158370051</v>
+        <v>63865158370008</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>DEV032309</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>MT2640600GZ0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>AOT</t>
+          <t>CUST</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+          <t>laser_tests_prerequisites-linkup_setup-ERROR-ShellException;</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,14,0,27,0,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,0,27,1,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,0,27,2,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,0,27,3,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,1,27,4,106,0,31.17,-327.68,-1,-100],[eocl:-1.0,14,1,27,5,106,0,31.17,-327.68,-1,-100],[eocl:-1.0,14,1,27,6,106,0,31.17,-327.68,-1,-100],[eocl:-1.0,14,1,27,7,106,0,31.17,-327.68,-1,-100]</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Fiber fracture, replace E-FBK
-Replaced FBK then pass</t>
-        </is>
-      </c>
+          <t>Shell command terminated with error: 1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>FXV</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Peter</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
@@ -1589,39 +1588,84 @@
       <c r="Z17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" t="n">
+        <v>63865158140010</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>63865158090005</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>63865158370051</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>AOT</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-21.37,6,0,11,0,41,159.27,12.98,9.04,6.6,-21.37,nan],[prb:nan,6,0,11,0,41,159.27,12.98,9.04,6.6,-21.37,nan],[prp:-22.08,6,0,11,1,41,159.27,12.92,9.1,6.46,-22.08,nan],[prb:nan,6,0,11,1,41,159.27,12.92,9.1,6.46,-22.08,nan],[prp:-21.61,6,0,11,2,41,159.27,13.01,9.01,6.6,-21.61,nan],[prb:nan,6,0,11,2,41,159.27,13.01,9.01,6.6,-21.61,nan],[prp:-20.6,6,0,11,3,41,159.27,13.15,8.87,6.73,-20.6,nan],[prb:nan,6,0,11,3,41,159.27,13.15,8.87,6.73,-20.6,nan]</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr"/>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,14,0,27,0,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,0,27,1,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,0,27,2,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,0,27,3,105,0,30.94,-327.68,-1,-100],[eocl:-1.0,14,1,27,4,106,0,31.17,-327.68,-1,-100],[eocl:-1.0,14,1,27,5,106,0,31.17,-327.68,-1,-100],[eocl:-1.0,14,1,27,6,106,0,31.17,-327.68,-1,-100],[eocl:-1.0,14,1,27,7,106,0,31.17,-327.68,-1,-100]</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Fiber fracture, replace E-FBK
+Replaced FBK then pass</t>
+        </is>
+      </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
@@ -1629,45 +1673,33 @@
       <c r="Z18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>11</v>
-      </c>
-      <c r="C19" t="n">
-        <v>63865158140012</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>63865158090027</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>63865158370028</v>
-      </c>
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>DEV032309</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-21.37,6,0,11,0,41,159.27,12.98,9.04,6.6,-21.37,nan],[prb:nan,6,0,11,0,41,159.27,12.98,9.04,6.6,-21.37,nan],[prp:-22.08,6,0,11,1,41,159.27,12.92,9.1,6.46,-22.08,nan],[prb:nan,6,0,11,1,41,159.27,12.92,9.1,6.46,-22.08,nan],[prp:-21.61,6,0,11,2,41,159.27,13.01,9.01,6.6,-21.61,nan],[prb:nan,6,0,11,2,41,159.27,13.01,9.01,6.6,-21.61,nan],[prp:-20.6,6,0,11,3,41,159.27,13.15,8.87,6.73,-20.6,nan],[prb:nan,6,0,11,3,41,159.27,13.15,8.87,6.73,-20.6,nan]</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
@@ -1687,10 +1719,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C20" t="n">
-        <v>63865158140016</v>
+        <v>63865158140012</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1698,7 +1730,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>63865158090028</v>
+        <v>63865158090027</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1706,7 +1738,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>63865158370019</v>
+        <v>63865158370028</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -1717,21 +1749,9 @@
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>power_on-burn_os_if_needed_and_boot_os-ERROR-TimeoutError;</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">System did not boot within the timeout and 1 retries were already done, boot failed due to: Exceed timeout on command ControlKeys.USER_COMMAND without receiving expected-reply: Checkpoint </t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
@@ -1751,10 +1771,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C21" t="n">
-        <v>63865158140015</v>
+        <v>63865158140016</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1762,7 +1782,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>63865158090024</v>
+        <v>63865158090028</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1770,7 +1790,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>63865158370015</v>
+        <v>63865158370019</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -1781,9 +1801,21 @@
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>power_on-burn_os_if_needed_and_boot_os-ERROR-TimeoutError;</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">System did not boot within the timeout and 1 retries were already done, boot failed due to: Exceed timeout on command ControlKeys.USER_COMMAND without receiving expected-reply: Checkpoint </t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
@@ -1803,10 +1835,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C22" t="n">
-        <v>63865158140014</v>
+        <v>63865158140015</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1814,7 +1846,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>63865158090026</v>
+        <v>63865158090024</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1822,7 +1854,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>63865158370052</v>
+        <v>63865158370015</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1833,45 +1865,15 @@
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:14.08,7,3,13,12,52,0,31.06,0.84,14.08,-100],[eocl:13.62,7,3,13,13,52,0,31.06,1.3,13.62,-100],[eocl:13.62,7,3,13,14,52,0,31.06,1.3,13.62,-100],[eocl:13.21,7,3,13,15,52,0,31.06,1.71,13.21,-100]</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>FBK stand alone IL still abnormal
-Need to replace an W-FBK
-Replaced FBK then pass</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>FXV</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Peter</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
@@ -1885,15 +1887,27 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" t="n">
-        <v>63865158140013</v>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+        <v>63865158140014</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>63865158090026</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>63865158370052</v>
+      </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
@@ -1903,15 +1917,45 @@
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:14.08,7,3,13,12,52,0,31.06,0.84,14.08,-100],[eocl:13.62,7,3,13,13,52,0,31.06,1.3,13.62,-100],[eocl:13.62,7,3,13,14,52,0,31.06,1.3,13.62,-100],[eocl:13.21,7,3,13,15,52,0,31.06,1.71,13.21,-100]</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>FBK stand alone IL still abnormal
+Need to replace an W-FBK
+Replaced FBK then pass</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
@@ -1925,32 +1969,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C24" t="n">
-        <v>63865158140019</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>63865158090034</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>63865158370042</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
+        <v>63865158140013</v>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
@@ -1959,44 +1987,15 @@
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>power_on-validate_power_converter_dma_data-ERROR-Exception;</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>csm1_asic_brd__pdb_node_controller': 'write_i2c_block' function failed: device=/dev/mst/192.168.10.20:23108,@dev@mst@dev-i2c-6, i2c_addr=0x60, addr_width=1, reg_addr=0xc7, size=2</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tried master PDB then pass. Replacing with new PDB to retest.
-29-SEP: Passed with new PDB - &gt; retets on PDB station </t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>FXV</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Joy</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>On-going</t>
-        </is>
-      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
@@ -2004,39 +2003,84 @@
       <c r="Z24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>63865158140019</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>63865158090034</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>63865158370042</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>AOT</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+          <t>power_on-validate_power_converter_dma_data-ERROR-Exception;</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-17.93,15,7,30,12,120,139.29,12.92,8.52,6.86,-17.93,nan],[prb:nan,15,7,30,12,120,139.29,12.92,8.52,6.86,-17.93,nan],[prp:-18.48,15,7,30,13,120,139.29,13.01,8.43,6.86,-18.48,nan],[prb:nan,15,7,30,13,120,139.29,13.01,8.43,6.86,-18.48,nan],[prp:-20.97,15,7,30,14,120,139.29,12.89,8.55,6.73,-20.97,nan],[prb:nan,15,7,30,14,120,139.29,12.89,8.55,6.73,-20.97,nan],[prp:-20.97,15,7,30,15,120,139.29,12.82,8.62,6.73,-20.97,nan],[prb:nan,15,7,30,15,120,139.29,12.82,8.62,6.73,-20.97,nan]</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr"/>
+          <t>csm1_asic_brd__pdb_node_controller': 'write_i2c_block' function failed: device=/dev/mst/192.168.10.20:23108,@dev@mst@dev-i2c-6, i2c_addr=0x60, addr_width=1, reg_addr=0xc7, size=2</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tried master PDB then pass. Replacing with new PDB to retest.
+29-SEP: Passed with new PDB - &gt; retets on PDB station </t>
+        </is>
+      </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Joy</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>On-going</t>
+        </is>
+      </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
@@ -2044,48 +2088,16 @@
       <c r="Z25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>17</v>
-      </c>
-      <c r="C26" t="n">
-        <v>63865158140020</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>63865158090033</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>63865158370017</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>DEV032309</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
@@ -2100,7 +2112,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-20.41,7,4,14,0,53,109.98,12.86,7.55,6.73,-20.41,nan],[prb:nan,7,4,14,0,53,109.98,12.86,7.55,6.73,-20.41,nan],[prp:-19.47,7,4,14,1,53,109.98,12.7,7.71,6.6,-19.47,nan],[prb:nan,7,4,14,1,53,109.98,12.7,7.71,6.6,-19.47,nan],[prp:-22.68,7,4,14,2,53,109.98,12.92,7.49,6.6,-22.68,nan],[prb:nan,7,4,14,2,53,109.98,12.92,7.49,6.6,-22.68,nan],[prp:-21.87,7,4,14,3,53,109.98,12.89,7.52,6.6,-21.87,nan],[prb:nan,7,4,14,3,53,109.98,12.89,7.52,6.6,-21.87,nan],[prp:-19.91,11,4,22,0,85,119.68,12.76,8.02,6.46,-19.91,nan],[prb:nan,11,4,22,0,85,119.68,12.76,8.02,6.46,-19.91,nan],[prp:-20.22,11,4,22,1,85,119.68,12.76,8.02,6.32,-20.22,nan],[prb:nan,11,4,22,1,85,119.68,12.76,8.02,6.32,-20.22,nan],[prp:-20.97,11,4,22,2,85,119.68,12.79,7.99,6.46,-20.97,nan],[prb:nan,11,4,22,2,85,119.68,12.79,7.99,6.46,-20.97,nan],[prp:-20.97,11,4,22,3,85,119.68,12.86,7.92,6.46,-20.97,nan],[prb:nan,11,4,22,3,85,119.68,12.86,7.92,6.46,-20.97,nan]</t>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-17.93,15,7,30,12,120,139.29,12.92,8.52,6.86,-17.93,nan],[prb:nan,15,7,30,12,120,139.29,12.92,8.52,6.86,-17.93,nan],[prp:-18.48,15,7,30,13,120,139.29,13.01,8.43,6.86,-18.48,nan],[prb:nan,15,7,30,13,120,139.29,13.01,8.43,6.86,-18.48,nan],[prp:-20.97,15,7,30,14,120,139.29,12.89,8.55,6.73,-20.97,nan],[prb:nan,15,7,30,14,120,139.29,12.89,8.55,6.73,-20.97,nan],[prp:-20.97,15,7,30,15,120,139.29,12.82,8.62,6.73,-20.97,nan],[prb:nan,15,7,30,15,120,139.29,12.82,8.62,6.73,-20.97,nan]</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -2122,10 +2134,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C27" t="n">
-        <v>63865158140021</v>
+        <v>63865158140020</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2133,7 +2145,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>63865158090032</v>
+        <v>63865158090033</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2141,14 +2153,18 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>63865158370018</v>
+        <v>63865158370017</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>DEV032309</t>
@@ -2166,7 +2182,11 @@
           <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-20.41,7,4,14,0,53,109.98,12.86,7.55,6.73,-20.41,nan],[prb:nan,7,4,14,0,53,109.98,12.86,7.55,6.73,-20.41,nan],[prp:-19.47,7,4,14,1,53,109.98,12.7,7.71,6.6,-19.47,nan],[prb:nan,7,4,14,1,53,109.98,12.7,7.71,6.6,-19.47,nan],[prp:-22.68,7,4,14,2,53,109.98,12.92,7.49,6.6,-22.68,nan],[prb:nan,7,4,14,2,53,109.98,12.92,7.49,6.6,-22.68,nan],[prp:-21.87,7,4,14,3,53,109.98,12.89,7.52,6.6,-21.87,nan],[prb:nan,7,4,14,3,53,109.98,12.89,7.52,6.6,-21.87,nan],[prp:-19.91,11,4,22,0,85,119.68,12.76,8.02,6.46,-19.91,nan],[prb:nan,11,4,22,0,85,119.68,12.76,8.02,6.46,-19.91,nan],[prp:-20.22,11,4,22,1,85,119.68,12.76,8.02,6.32,-20.22,nan],[prb:nan,11,4,22,1,85,119.68,12.76,8.02,6.32,-20.22,nan],[prp:-20.97,11,4,22,2,85,119.68,12.79,7.99,6.46,-20.97,nan],[prb:nan,11,4,22,2,85,119.68,12.79,7.99,6.46,-20.97,nan],[prp:-20.97,11,4,22,3,85,119.68,12.86,7.92,6.46,-20.97,nan],[prb:nan,11,4,22,3,85,119.68,12.86,7.92,6.46,-20.97,nan]</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
@@ -2180,16 +2200,44 @@
       <c r="Z27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>18</v>
+      </c>
+      <c r="C28" t="n">
+        <v>63865158140021</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>63865158090032</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>63865158370018</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
@@ -2199,14 +2247,10 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>post_prbs_test_asic_reset-create_mst_devices_chipset-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>mst_devices_Linkx-MST Linkx device presence</t>
-        </is>
-      </c>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
@@ -2220,53 +2264,17 @@
       <c r="Z28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>19</v>
-      </c>
-      <c r="C29" t="n">
-        <v>63865158140022</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>63865158090037</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>63865158370014</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>DEV032309</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>MT2640600GZP</t>
-        </is>
-      </c>
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
@@ -2275,12 +2283,12 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+          <t>post_prbs_test_asic_reset-create_mst_devices_chipset-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,12,6,24,8,95,119.32,12.89,7.88,6.6,-20.09,nan],[prp:-20.09,12,6,24,8,95,119.32,12.89,7.88,6.6,-20.09,nan],[prb:nan,12,6,24,9,95,119.32,12.89,7.88,6.46,-19.75,nan],[prp:-19.75,12,6,24,9,95,119.32,12.89,7.88,6.46,-19.75,nan],[prb:nan,12,6,24,10,95,119.32,12.82,7.95,6.46,-22.68,nan],[prp:-22.68,12,6,24,10,95,119.32,12.82,7.95,6.46,-22.68,nan],[prb:nan,12,6,24,11,95,119.32,12.73,8.04,6.46,-22.68,nan],[prp:-22.68,12,6,24,11,95,119.32,12.73,8.04,6.46,-22.68,nan],[prb:nan,14,5,28,4,110,139.47,12.7,8.74,6.73,-2.79,nan],[prb:nan,14,5,28,5,110,139.47,12.61,8.83,6.73,-2.33,nan],[prb:nan,14,5,28,6,110,139.47,12.67,8.77,6.73,-2.66,nan],[prb:nan,14,5,28,7,110,139.47,12.76,8.68,6.73,-18.57,nan],[prp:-18.57,14,5,28,7,110,139.47,12.76,8.68,6.73,-18.57,nan],[prb:nan,5,1,9,4,34,144.37,13.18,8.41,6.86,-21.87,nan],[prp:-21.87,5,1,9,4,34,144.37,13.18,8.41,6.86,-21.87,nan],[prb:nan,5,1,9,5,34,144.37,13.01,8.58,6.73,-21.87,nan],[prp:-21.87,5,1,9,5,34,144.37,13.01,8.58,6.73,-21.87,nan],[prb:nan,5,1,9,6,34,144.37,13.15,8.44,6.73,-22.68,nan],[prp:-22.68,5,1,9,6,34,144.37,13.15,8.44,6.73,-22.68,nan],[prb:nan,5,1,9,7,34,144.37,13.23,8.36,6.99,-22.08,nan],[prp:-22.08,5,1,9,7,34,144.37,13.23,8.36,6.99,-22.08,nan],[prp:-5.2,2,1,3,6,10,129.27,12.76,8.35,6.6,-5.2,8e-10]</t>
+          <t>mst_devices_Linkx-MST Linkx device presence</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
@@ -2302,10 +2310,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C30" t="n">
-        <v>63865158140023</v>
+        <v>63865158140022</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2313,7 +2321,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>63865158090031</v>
+        <v>63865158090037</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2321,16 +2329,44 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>63865158370009</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+        <v>63865158370014</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>MT2640600GZP</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,12,6,24,8,95,119.32,12.89,7.88,6.6,-20.09,nan],[prp:-20.09,12,6,24,8,95,119.32,12.89,7.88,6.6,-20.09,nan],[prb:nan,12,6,24,9,95,119.32,12.89,7.88,6.46,-19.75,nan],[prp:-19.75,12,6,24,9,95,119.32,12.89,7.88,6.46,-19.75,nan],[prb:nan,12,6,24,10,95,119.32,12.82,7.95,6.46,-22.68,nan],[prp:-22.68,12,6,24,10,95,119.32,12.82,7.95,6.46,-22.68,nan],[prb:nan,12,6,24,11,95,119.32,12.73,8.04,6.46,-22.68,nan],[prp:-22.68,12,6,24,11,95,119.32,12.73,8.04,6.46,-22.68,nan],[prb:nan,14,5,28,4,110,139.47,12.7,8.74,6.73,-2.79,nan],[prb:nan,14,5,28,5,110,139.47,12.61,8.83,6.73,-2.33,nan],[prb:nan,14,5,28,6,110,139.47,12.67,8.77,6.73,-2.66,nan],[prb:nan,14,5,28,7,110,139.47,12.76,8.68,6.73,-18.57,nan],[prp:-18.57,14,5,28,7,110,139.47,12.76,8.68,6.73,-18.57,nan],[prb:nan,5,1,9,4,34,144.37,13.18,8.41,6.86,-21.87,nan],[prp:-21.87,5,1,9,4,34,144.37,13.18,8.41,6.86,-21.87,nan],[prb:nan,5,1,9,5,34,144.37,13.01,8.58,6.73,-21.87,nan],[prp:-21.87,5,1,9,5,34,144.37,13.01,8.58,6.73,-21.87,nan],[prb:nan,5,1,9,6,34,144.37,13.15,8.44,6.73,-22.68,nan],[prp:-22.68,5,1,9,6,34,144.37,13.15,8.44,6.73,-22.68,nan],[prb:nan,5,1,9,7,34,144.37,13.23,8.36,6.99,-22.08,nan],[prp:-22.08,5,1,9,7,34,144.37,13.23,8.36,6.99,-22.08,nan],[prp:-5.2,2,1,3,6,10,129.27,12.76,8.35,6.6,-5.2,8e-10]</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
@@ -2350,10 +2386,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C31" t="n">
-        <v>63865158140025</v>
+        <v>63865158140023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2361,7 +2397,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>63865158090022</v>
+        <v>63865158090031</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2369,7 +2405,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>63865158370010</v>
+        <v>63865158370009</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -2398,10 +2434,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C32" t="n">
-        <v>63865158140024</v>
+        <v>63865158140025</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2409,7 +2445,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>63865158090023</v>
+        <v>63865158090022</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2417,7 +2453,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>63865158370016</v>
+        <v>63865158370010</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -2446,10 +2482,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C33" t="n">
-        <v>63865158140026</v>
+        <v>63865158140024</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2457,7 +2493,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>63865158090029</v>
+        <v>63865158090023</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2465,32 +2501,16 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>63865158370044</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
+        <v>63865158370016</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-21.87,7,1,13,4,50,119.6,12.89,7.89,6.6,-21.87,nan],[prb:nan,7,1,13,4,50,119.6,12.89,7.89,6.6,-21.87,nan],[prp:-22.37,7,1,13,5,50,119.6,12.82,7.96,6.46,-22.37,nan],[prb:nan,7,1,13,5,50,119.6,12.82,7.96,6.46,-22.37,nan],[prp:-18.15,7,1,13,6,50,119.6,12.79,7.99,6.46,-18.15,nan],[prb:nan,7,1,13,6,50,119.6,12.79,7.99,6.46,-18.15,nan],[prp:-18.15,7,1,13,7,50,119.6,12.89,7.89,6.46,-18.15,nan],[prb:nan,7,1,13,7,50,119.6,12.89,7.89,6.46,-18.15,nan],[prp:-20.09,7,3,13,12,52,124.17,12.82,8.12,6.32,-20.09,nan],[prb:nan,7,3,13,12,52,124.17,12.82,8.12,6.32,-20.09,nan],[prp:-20.09,7,3,13,13,52,124.17,12.86,8.08,6.46,-20.09,nan],[prb:nan,7,3,13,13,52,124.17,12.86,8.08,6.46,-20.09,nan],[prp:-22.37,7,3,13,14,52,124.17,12.79,8.15,6.46,-22.37,nan],[prb:nan,7,3,13,14,52,124.17,12.79,8.15,6.46,-22.37,nan],[prp:-22.37,7,3,13,15,52,124.17,12.73,8.21,6.46,-22.37,nan],[prb:nan,7,3,13,15,52,124.17,12.73,8.21,6.46,-22.37,nan],[prb:nan,4,6,8,8,31,149.44,12.76,8.98,6.6,-2.13,nan],[prp:-20.76,4,6,8,9,31,149.44,12.82,8.92,6.73,-20.76,nan],[prb:nan,4,6,8,9,31,149.44,12.82,8.92,6.73,-20.76,nan],[prp:-21.61,4,6,8,10,31,149.44,12.98,8.76,6.86,-21.61,nan],[prb:nan,4,6,8,10,31,149.44,12.98,8.76,6.86,-21.61,nan],[prp:-22.08,4,6,8,11,31,149.44,12.89,8.85,6.73,-22.08,nan],[prb:nan,4,6,8,11,31,149.44,12.89,8.85,6.73,-22.08,nan],[prp:-20.22,4,7,8,12,32,144.48,12.86,8.74,6.73,-20.22,nan],[prb:nan,4,7,8,12,32,144.48,12.86,8.74,6.73,-20.22,nan],[prp:-20.22,4,7,8,13,32,144.48,13.01,8.59,6.99,-20.22,nan],[prb:nan,4,7,8,13,32,144.48,13.01,8.59,6.99,-20.22,nan],[prp:-21.19,4,7,8,14,32,144.48,12.89,8.71,6.73,-21.19,nan],[prb:nan,4,7,8,14,32,144.48,12.89,8.71,6.73,-21.19,nan],[prp:-21.37,4,7,8,15,32,144.48,12.86,8.74,6.6,-21.37,nan],[prb:nan,4,7,8,15,32,144.48,12.86,8.74,6.6,-21.37,nan],[prp:-20.76,4,3,7,12,28,131.33,13.04,8.14,6.6,-20.76,nan],[prb:nan,4,3,7,12,28,131.33,13.04,8.14,6.6,-20.76,nan],[prb:nan,4,3,7,13,28,131.33,13.15,8.03,6.73,-2.97,nan],[prb:nan,4,3,7,14,28,131.33,12.95,8.23,6.6,-2.7,nan],[prb:nan,4,3,7,15,28,131.33,12.98,8.2,6.6,-2.39,nan],[prp:-21.61,3,6,6,8,23,124.67,12.89,8.07,6.6,-21.61,nan],[prb:nan,3,6,6,8,23,124.67,12.89,8.07,6.6,-21.61,nan],[prb:nan,3,6,6,9,23,124.67,12.98,7.98,6.73,-2.18,nan],[prb:nan,3,6,6,10,23,124.67,12.89,8.07,6.73,-2.41,nan],[prb:nan,3,6,6,11,23,124.67,12.86,8.1,6.73,-1.99,nan],[prb:nan,3,7,6,12,24,134.46,12.86,8.43,6.73,-2.66,nan],[prb:nan,3,7,6,13,24,134.46,12.89,8.4,6.73,-2.79,nan],[prb:nan,3,7,6,14,24,134.46,12.86,8.43,6.73,-2.81,nan],[prp:-22.92,3,7,6,15,24,134.46,12.79,8.5,6.6,-22.92,nan],[prb:nan,3,7,6,15,24,134.46,12.79,8.5,6.6,-22.92,nan],[prb:nan,3,4,6,0,21,129.87,12.82,8.32,6.73,-2.69,nan],[prb:nan,3,4,6,1,21,129.87,12.61,8.53,6.46,-2.88,nan],[prp:-20.22,3,4,6,2,21,129.87,12.79,8.35,6.6,-20.22,nan],[prb:nan,3,4,6,2,21,129.87,12.79,8.35,6.6,-20.22,nan],[prb:nan,3,4,6,3,21,129.87,12.82,8.32,6.6,-2.5,nan]</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
@@ -2510,10 +2530,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C34" t="n">
-        <v>63865158140028</v>
+        <v>63865158140026</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2521,7 +2541,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>63865158090021</v>
+        <v>63865158090029</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2529,16 +2549,32 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>63865158370024</v>
-      </c>
-      <c r="H34" t="inlineStr"/>
+        <v>63865158370044</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-21.87,7,1,13,4,50,119.6,12.89,7.89,6.6,-21.87,nan],[prb:nan,7,1,13,4,50,119.6,12.89,7.89,6.6,-21.87,nan],[prp:-22.37,7,1,13,5,50,119.6,12.82,7.96,6.46,-22.37,nan],[prb:nan,7,1,13,5,50,119.6,12.82,7.96,6.46,-22.37,nan],[prp:-18.15,7,1,13,6,50,119.6,12.79,7.99,6.46,-18.15,nan],[prb:nan,7,1,13,6,50,119.6,12.79,7.99,6.46,-18.15,nan],[prp:-18.15,7,1,13,7,50,119.6,12.89,7.89,6.46,-18.15,nan],[prb:nan,7,1,13,7,50,119.6,12.89,7.89,6.46,-18.15,nan],[prp:-20.09,7,3,13,12,52,124.17,12.82,8.12,6.32,-20.09,nan],[prb:nan,7,3,13,12,52,124.17,12.82,8.12,6.32,-20.09,nan],[prp:-20.09,7,3,13,13,52,124.17,12.86,8.08,6.46,-20.09,nan],[prb:nan,7,3,13,13,52,124.17,12.86,8.08,6.46,-20.09,nan],[prp:-22.37,7,3,13,14,52,124.17,12.79,8.15,6.46,-22.37,nan],[prb:nan,7,3,13,14,52,124.17,12.79,8.15,6.46,-22.37,nan],[prp:-22.37,7,3,13,15,52,124.17,12.73,8.21,6.46,-22.37,nan],[prb:nan,7,3,13,15,52,124.17,12.73,8.21,6.46,-22.37,nan],[prb:nan,4,6,8,8,31,149.44,12.76,8.98,6.6,-2.13,nan],[prp:-20.76,4,6,8,9,31,149.44,12.82,8.92,6.73,-20.76,nan],[prb:nan,4,6,8,9,31,149.44,12.82,8.92,6.73,-20.76,nan],[prp:-21.61,4,6,8,10,31,149.44,12.98,8.76,6.86,-21.61,nan],[prb:nan,4,6,8,10,31,149.44,12.98,8.76,6.86,-21.61,nan],[prp:-22.08,4,6,8,11,31,149.44,12.89,8.85,6.73,-22.08,nan],[prb:nan,4,6,8,11,31,149.44,12.89,8.85,6.73,-22.08,nan],[prp:-20.22,4,7,8,12,32,144.48,12.86,8.74,6.73,-20.22,nan],[prb:nan,4,7,8,12,32,144.48,12.86,8.74,6.73,-20.22,nan],[prp:-20.22,4,7,8,13,32,144.48,13.01,8.59,6.99,-20.22,nan],[prb:nan,4,7,8,13,32,144.48,13.01,8.59,6.99,-20.22,nan],[prp:-21.19,4,7,8,14,32,144.48,12.89,8.71,6.73,-21.19,nan],[prb:nan,4,7,8,14,32,144.48,12.89,8.71,6.73,-21.19,nan],[prp:-21.37,4,7,8,15,32,144.48,12.86,8.74,6.6,-21.37,nan],[prb:nan,4,7,8,15,32,144.48,12.86,8.74,6.6,-21.37,nan],[prp:-20.76,4,3,7,12,28,131.33,13.04,8.14,6.6,-20.76,nan],[prb:nan,4,3,7,12,28,131.33,13.04,8.14,6.6,-20.76,nan],[prb:nan,4,3,7,13,28,131.33,13.15,8.03,6.73,-2.97,nan],[prb:nan,4,3,7,14,28,131.33,12.95,8.23,6.6,-2.7,nan],[prb:nan,4,3,7,15,28,131.33,12.98,8.2,6.6,-2.39,nan],[prp:-21.61,3,6,6,8,23,124.67,12.89,8.07,6.6,-21.61,nan],[prb:nan,3,6,6,8,23,124.67,12.89,8.07,6.6,-21.61,nan],[prb:nan,3,6,6,9,23,124.67,12.98,7.98,6.73,-2.18,nan],[prb:nan,3,6,6,10,23,124.67,12.89,8.07,6.73,-2.41,nan],[prb:nan,3,6,6,11,23,124.67,12.86,8.1,6.73,-1.99,nan],[prb:nan,3,7,6,12,24,134.46,12.86,8.43,6.73,-2.66,nan],[prb:nan,3,7,6,13,24,134.46,12.89,8.4,6.73,-2.79,nan],[prb:nan,3,7,6,14,24,134.46,12.86,8.43,6.73,-2.81,nan],[prp:-22.92,3,7,6,15,24,134.46,12.79,8.5,6.6,-22.92,nan],[prb:nan,3,7,6,15,24,134.46,12.79,8.5,6.6,-22.92,nan],[prb:nan,3,4,6,0,21,129.87,12.82,8.32,6.73,-2.69,nan],[prb:nan,3,4,6,1,21,129.87,12.61,8.53,6.46,-2.88,nan],[prp:-20.22,3,4,6,2,21,129.87,12.79,8.35,6.6,-20.22,nan],[prb:nan,3,4,6,2,21,129.87,12.79,8.35,6.6,-20.22,nan],[prb:nan,3,4,6,3,21,129.87,12.82,8.32,6.6,-2.5,nan]</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
@@ -2558,10 +2594,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C35" t="n">
-        <v>63865158140029</v>
+        <v>63865158140028</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2569,7 +2605,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>63865158090038</v>
+        <v>63865158090021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2577,7 +2613,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>63865158370025</v>
+        <v>63865158370024</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
@@ -2606,10 +2642,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C36" t="n">
-        <v>63865158140030</v>
+        <v>63865158140029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2617,7 +2653,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>63865158090042</v>
+        <v>63865158090038</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2625,40 +2661,16 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>63865158370054</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>DEV032309</t>
-        </is>
-      </c>
+        <v>63865158370025</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,8,0,15,0,57,150,12.79,8.97,6.6,-22.08,nan],[prp:-22.08,8,0,15,0,57,150,12.79,8.97,6.6,-22.08,nan],[prb:nan,8,0,15,1,57,150,12.73,9.03,6.6,-22.08,nan],[prp:-22.08,8,0,15,1,57,150,12.73,9.03,6.6,-22.08,nan],[prb:nan,8,0,15,2,57,150,12.82,8.94,6.73,-21.61,nan],[prp:-21.61,8,0,15,2,57,150,12.82,8.94,6.73,-21.61,nan],[prb:nan,8,0,15,3,57,150,12.86,8.9,6.86,-21.87,nan],[prp:-21.87,8,0,15,3,57,150,12.86,8.9,6.86,-21.87,nan],[prb:nan,6,7,12,12,48,129.64,12.86,8.27,6.73,-19.91,nan],[prp:-19.91,6,7,12,12,48,129.64,12.86,8.27,6.73,-19.91,nan],[prb:nan,6,7,12,13,48,129.64,12.95,8.18,6.73,-20.41,nan],[prp:-20.41,6,7,12,13,48,129.64,12.95,8.18,6.73,-20.41,nan],[prb:nan,6,7,12,14,48,129.64,12.89,8.24,6.6,-23.28,nan],[prp:-23.28,6,7,12,14,48,129.64,12.89,8.24,6.6,-23.28,nan],[prb:nan,6,7,12,15,48,129.64,12.76,8.37,6.6,-22.37,nan],[prp:-22.37,6,7,12,15,48,129.64,12.76,8.37,6.6,-22.37,nan]</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
@@ -2678,10 +2690,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C37" t="n">
-        <v>63865158140037</v>
+        <v>63865158140030</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2689,7 +2701,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>63865158090018</v>
+        <v>63865158090042</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2697,7 +2709,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>63865158370013</v>
+        <v>63865158370054</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -2714,11 +2726,7 @@
           <t>DEV032309</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>MT2640600GZQ</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
@@ -2732,7 +2740,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-21.37,7,0,13,0,49,119.35,12.86,7.91,6.46,-21.37,nan],[prb:nan,7,0,13,0,49,119.35,12.86,7.91,6.46,-21.37,nan],[prp:-21.19,7,0,13,1,49,119.35,12.67,8.1,6.17,-21.19,nan],[prb:nan,7,0,13,1,49,119.35,12.67,8.1,6.17,-21.19,nan],[prp:-21.87,7,0,13,2,49,119.35,12.79,7.98,6.46,-21.87,nan],[prb:nan,7,0,13,2,49,119.35,12.79,7.98,6.46,-21.87,nan],[prp:-22.68,7,0,13,3,49,119.35,12.86,7.91,6.32,-22.68,nan],[prb:nan,7,0,13,3,49,119.35,12.86,7.91,6.32,-22.68,nan],[prp:-19.21,4,6,8,8,31,130.02,12.82,8.32,6.73,-19.21,nan],[prb:nan,4,6,8,8,31,130.02,12.82,8.32,6.73,-19.21,nan],[prp:-20.09,4,6,8,9,31,130.02,12.92,8.22,6.86,-20.09,nan],[prb:nan,4,6,8,9,31,130.02,12.92,8.22,6.86,-20.09,nan],[prp:-22.92,4,6,8,10,31,130.02,12.73,8.41,6.73,-22.92,nan],[prb:nan,4,6,8,10,31,130.02,12.73,8.41,6.73,-22.92,nan],[prp:-22.92,4,6,8,11,31,130.02,12.73,8.41,6.6,-22.92,nan],[prb:nan,4,6,8,11,31,130.02,12.73,8.41,6.6,-22.92,nan]</t>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,8,0,15,0,57,150,12.79,8.97,6.6,-22.08,nan],[prp:-22.08,8,0,15,0,57,150,12.79,8.97,6.6,-22.08,nan],[prb:nan,8,0,15,1,57,150,12.73,9.03,6.6,-22.08,nan],[prp:-22.08,8,0,15,1,57,150,12.73,9.03,6.6,-22.08,nan],[prb:nan,8,0,15,2,57,150,12.82,8.94,6.73,-21.61,nan],[prp:-21.61,8,0,15,2,57,150,12.82,8.94,6.73,-21.61,nan],[prb:nan,8,0,15,3,57,150,12.86,8.9,6.86,-21.87,nan],[prp:-21.87,8,0,15,3,57,150,12.86,8.9,6.86,-21.87,nan],[prb:nan,6,7,12,12,48,129.64,12.86,8.27,6.73,-19.91,nan],[prp:-19.91,6,7,12,12,48,129.64,12.86,8.27,6.73,-19.91,nan],[prb:nan,6,7,12,13,48,129.64,12.95,8.18,6.73,-20.41,nan],[prp:-20.41,6,7,12,13,48,129.64,12.95,8.18,6.73,-20.41,nan],[prb:nan,6,7,12,14,48,129.64,12.89,8.24,6.6,-23.28,nan],[prp:-23.28,6,7,12,14,48,129.64,12.89,8.24,6.6,-23.28,nan],[prb:nan,6,7,12,15,48,129.64,12.76,8.37,6.6,-22.37,nan],[prp:-22.37,6,7,12,15,48,129.64,12.76,8.37,6.6,-22.37,nan]</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
@@ -2754,10 +2762,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C38" t="n">
-        <v>63865158140032</v>
+        <v>63865158140037</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2765,7 +2773,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>63865158090013</v>
+        <v>63865158090018</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2773,16 +2781,28 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>63865158370012</v>
+        <v>63865158370013</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>MT2640600GZQ</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
@@ -2791,12 +2811,12 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>group_pb_button-group_pb_test-FAIL-MEASUREMENT;</t>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>group_pb_pushed-Verify group_pb button pushed</t>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-21.37,7,0,13,0,49,119.35,12.86,7.91,6.46,-21.37,nan],[prb:nan,7,0,13,0,49,119.35,12.86,7.91,6.46,-21.37,nan],[prp:-21.19,7,0,13,1,49,119.35,12.67,8.1,6.17,-21.19,nan],[prb:nan,7,0,13,1,49,119.35,12.67,8.1,6.17,-21.19,nan],[prp:-21.87,7,0,13,2,49,119.35,12.79,7.98,6.46,-21.87,nan],[prb:nan,7,0,13,2,49,119.35,12.79,7.98,6.46,-21.87,nan],[prp:-22.68,7,0,13,3,49,119.35,12.86,7.91,6.32,-22.68,nan],[prb:nan,7,0,13,3,49,119.35,12.86,7.91,6.32,-22.68,nan],[prp:-19.21,4,6,8,8,31,130.02,12.82,8.32,6.73,-19.21,nan],[prb:nan,4,6,8,8,31,130.02,12.82,8.32,6.73,-19.21,nan],[prp:-20.09,4,6,8,9,31,130.02,12.92,8.22,6.86,-20.09,nan],[prb:nan,4,6,8,9,31,130.02,12.92,8.22,6.86,-20.09,nan],[prp:-22.92,4,6,8,10,31,130.02,12.73,8.41,6.73,-22.92,nan],[prb:nan,4,6,8,10,31,130.02,12.73,8.41,6.73,-22.92,nan],[prp:-22.92,4,6,8,11,31,130.02,12.73,8.41,6.6,-22.92,nan],[prb:nan,4,6,8,11,31,130.02,12.73,8.41,6.6,-22.92,nan]</t>
         </is>
       </c>
       <c r="P38" t="inlineStr"/>
@@ -2812,14 +2832,38 @@
       <c r="Z38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>28</v>
+      </c>
+      <c r="C39" t="n">
+        <v>63865158140032</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>63865158090013</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>63865158370012</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
@@ -2831,12 +2875,12 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>sbc_storage_usb-passmark-FAIL-MEASUREMENT;</t>
+          <t>group_pb_button-group_pb_test-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>usb_passmark_pass-Verify usb device passed passmark</t>
+          <t>group_pb_pushed-Verify group_pb button pushed</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
@@ -2852,38 +2896,14 @@
       <c r="Z39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>29</v>
-      </c>
-      <c r="C40" t="n">
-        <v>63865158140033</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>63865158090011</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>63865158370022</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
@@ -2895,12 +2915,12 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>query_fnm_linkup-linkup_polling_fnm-FAIL-MEASUREMENT;</t>
+          <t>sbc_storage_usb-passmark-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>linkup_matrix_fnm-Failed: ['port 65/0', 'port 65/1']</t>
+          <t>usb_passmark_pass-Verify usb device passed passmark</t>
         </is>
       </c>
       <c r="P40" t="inlineStr"/>
@@ -2922,10 +2942,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C41" t="n">
-        <v>63865158140034</v>
+        <v>63865158140033</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2933,7 +2953,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>63865158090010</v>
+        <v>63865158090011</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2941,7 +2961,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>63865158370026</v>
+        <v>63865158370022</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2959,12 +2979,12 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+          <t>query_fnm_linkup-linkup_polling_fnm-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,10,5,20,4,78,149.65,12.98,8.77,6.86,-22.37,nan],[prp:-22.37,10,5,20,4,78,149.65,12.98,8.77,6.86,-22.37,nan],[prb:nan,10,5,20,5,78,149.65,13.01,8.74,6.86,-22.37,nan],[prp:-22.37,10,5,20,5,78,149.65,13.01,8.74,6.86,-22.37,nan],[prb:nan,10,5,20,6,78,149.65,13.04,8.71,6.86,-20.97,nan],[prp:-20.97,10,5,20,6,78,149.65,13.04,8.71,6.86,-20.97,nan],[prb:nan,10,5,20,7,78,149.65,13.09,8.66,6.86,-20.22,nan],[prp:-20.22,10,5,20,7,78,149.65,13.09,8.66,6.86,-20.22,nan]</t>
+          <t>linkup_matrix_fnm-Failed: ['port 65/0', 'port 65/1']</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
@@ -2986,10 +3006,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C42" t="n">
-        <v>63865158140035</v>
+        <v>63865158140034</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2997,7 +3017,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>63865158090014</v>
+        <v>63865158090010</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3005,33 +3025,33 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>63865158370053</v>
-      </c>
-      <c r="H42" t="inlineStr"/>
+        <v>63865158370026</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>AOT</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,4,6,8,8,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,9,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,10,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,11,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,7,8,12,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,13,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,14,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,15,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,4,8,0,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,1,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,2,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,3,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,5,8,4,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,5,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,6,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,7,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,16,6,32,8,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,9,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,10,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,11,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,7,32,12,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,13,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,14,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,15,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,4,32,0,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,1,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,2,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,3,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,5,32,4,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,5,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,6,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,7,126,0,31.84,-327.68,-1,-100]</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Try to test the ELS module on AOT master unit</t>
-        </is>
-      </c>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,10,5,20,4,78,149.65,12.98,8.77,6.86,-22.37,nan],[prp:-22.37,10,5,20,4,78,149.65,12.98,8.77,6.86,-22.37,nan],[prb:nan,10,5,20,5,78,149.65,13.01,8.74,6.86,-22.37,nan],[prp:-22.37,10,5,20,5,78,149.65,13.01,8.74,6.86,-22.37,nan],[prb:nan,10,5,20,6,78,149.65,13.04,8.71,6.86,-20.97,nan],[prp:-20.97,10,5,20,6,78,149.65,13.04,8.71,6.86,-20.97,nan],[prb:nan,10,5,20,7,78,149.65,13.09,8.66,6.86,-20.22,nan],[prp:-20.22,10,5,20,7,78,149.65,13.09,8.66,6.86,-20.22,nan]</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
@@ -3050,10 +3070,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C43" t="n">
-        <v>63865158140036</v>
+        <v>63865158140035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3061,7 +3081,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>63865158090017</v>
+        <v>63865158090014</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3069,7 +3089,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>63865158370037</v>
+        <v>63865158370053</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
@@ -3088,10 +3108,14 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:13.23,9,0,17,0,65,0,31.17,1.71,13.23,-100],[eocl:13.23,9,0,17,1,65,0,31.17,1.71,13.23,-100],[eocl:13.23,9,0,17,2,65,0,31.17,1.71,13.23,-100],[eocl:13.64,9,0,17,3,65,0,31.17,1.3,13.64,-100],[eocl:14.6,9,1,17,4,66,0,31.09,0.33,14.6,-100],[eocl:14.09,9,1,17,5,66,0,31.09,0.84,14.09,-100],[eocl:14.09,9,1,17,6,66,0,31.09,0.84,14.09,-100],[eocl:13.63,9,1,17,7,66,0,31.09,1.3,13.63,-100],[eocl:13.25,9,2,17,8,67,0,31.3,1.71,13.25,-100],[eocl:13.25,9,2,17,9,67,0,31.3,1.71,13.25,-100],[eocl:13.25,9,2,17,10,67,0,31.3,1.71,13.25,-100],[eocl:12.87,9,2,17,11,67,0,31.3,2.09,12.87,-100],[eocl:13.65,9,3,17,12,68,0,31.26,1.3,13.65,-100],[eocl:13.65,9,3,17,13,68,0,31.26,1.3,13.65,-100],[eocl:13.65,9,3,17,14,68,0,31.26,1.3,13.65,-100],[eocl:13.24,9,3,17,15,68,0,31.26,1.71,13.24,-100]</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr"/>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,4,6,8,8,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,9,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,10,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,11,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,7,8,12,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,13,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,14,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,15,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,4,8,0,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,1,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,2,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,3,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,5,8,4,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,5,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,6,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,7,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,16,6,32,8,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,9,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,10,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,11,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,7,32,12,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,13,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,14,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,15,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,4,32,0,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,1,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,2,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,3,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,5,32,4,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,5,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,6,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,7,126,0,31.84,-327.68,-1,-100]</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Try to test the ELS module on AOT master unit</t>
+        </is>
+      </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
@@ -3110,10 +3134,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C44" t="n">
-        <v>63865158140031</v>
+        <v>63865158140036</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3121,7 +3145,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>63865158090046</v>
+        <v>63865158090017</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3129,16 +3153,28 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>63865158370021</v>
+        <v>63865158370037</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:13.23,9,0,17,0,65,0,31.17,1.71,13.23,-100],[eocl:13.23,9,0,17,1,65,0,31.17,1.71,13.23,-100],[eocl:13.23,9,0,17,2,65,0,31.17,1.71,13.23,-100],[eocl:13.64,9,0,17,3,65,0,31.17,1.3,13.64,-100],[eocl:14.6,9,1,17,4,66,0,31.09,0.33,14.6,-100],[eocl:14.09,9,1,17,5,66,0,31.09,0.84,14.09,-100],[eocl:14.09,9,1,17,6,66,0,31.09,0.84,14.09,-100],[eocl:13.63,9,1,17,7,66,0,31.09,1.3,13.63,-100],[eocl:13.25,9,2,17,8,67,0,31.3,1.71,13.25,-100],[eocl:13.25,9,2,17,9,67,0,31.3,1.71,13.25,-100],[eocl:13.25,9,2,17,10,67,0,31.3,1.71,13.25,-100],[eocl:12.87,9,2,17,11,67,0,31.3,2.09,12.87,-100],[eocl:13.65,9,3,17,12,68,0,31.26,1.3,13.65,-100],[eocl:13.65,9,3,17,13,68,0,31.26,1.3,13.65,-100],[eocl:13.65,9,3,17,14,68,0,31.26,1.3,13.65,-100],[eocl:13.24,9,3,17,15,68,0,31.26,1.71,13.24,-100]</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
@@ -3158,10 +3194,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C45" t="n">
-        <v>63865158140038</v>
+        <v>63865158140031</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3169,7 +3205,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>63865158090012</v>
+        <v>63865158090046</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3177,7 +3213,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>63865158370027</v>
+        <v>63865158370021</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -3206,10 +3242,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C46" t="n">
-        <v>63865158140039</v>
+        <v>63865158140038</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3217,7 +3253,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>63865158090039</v>
+        <v>63865158090012</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3225,7 +3261,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>63865158370020</v>
+        <v>63865158370027</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
@@ -3254,10 +3290,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C47" t="n">
-        <v>63865158140040</v>
+        <v>63865158140039</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3265,7 +3301,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>63865158090016</v>
+        <v>63865158090039</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3273,7 +3309,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>63865158370055</v>
+        <v>63865158370020</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
@@ -3302,10 +3338,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C48" t="n">
-        <v>63865158140041</v>
+        <v>63865158140040</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3313,7 +3349,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>63865158090015</v>
+        <v>63865158090016</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3321,18 +3357,10 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>63865158370056</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+        <v>63865158370055</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
@@ -3358,10 +3386,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C49" t="n">
-        <v>63865158140042</v>
+        <v>63865158140041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3369,7 +3397,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>63865158090019</v>
+        <v>63865158090015</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3377,28 +3405,24 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>63865158370047</v>
-      </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+        <v>63865158370056</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,13,4,26,0,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,1,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,2,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,3,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,5,26,4,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,5,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,6,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,7,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,6,26,8,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,9,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,10,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,11,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,7,26,12,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,13,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,14,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,15,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,14,0,27,0,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,1,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,2,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,3,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,1,27,4,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,5,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,6,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,7,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,2,27,8,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,9,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,10,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,11,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,3,27,12,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,13,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,14,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,15,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,4,28,0,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,1,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,2,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,3,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,5,28,4,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,5,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,6,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,7,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,6,28,8,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,9,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,10,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,11,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,7,28,12,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,13,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,14,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,15,112,0,31.85,-327.68,-1,-100]</t>
-        </is>
-      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
@@ -3418,10 +3442,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C50" t="n">
-        <v>63865158140043</v>
+        <v>63865158140042</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3429,14 +3453,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>63865158090020</v>
+        <v>63865158090019</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>63865158370047</v>
+      </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
@@ -3449,15 +3475,73 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,13,4,26,0,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,1,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,2,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,3,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,5,26,4,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,5,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,6,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,7,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,6,26,8,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,9,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,10,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,11,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,7,26,12,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,13,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,14,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,15,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,14,0,27,0,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,1,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,2,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,3,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,1,27,4,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,5,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,6,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,7,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,2,27,8,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,9,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,10,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,11,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,3,27,12,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,13,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,14,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,15,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,4,28,0,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,1,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,2,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,3,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,5,28,4,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,5,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,6,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,7,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,6,28,8,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,9,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,10,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,11,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,7,28,12,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,13,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,14,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,15,112,0,31.85,-327.68,-1,-100]</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>39</v>
+      </c>
+      <c r="C51" t="n">
+        <v>63865158140043</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>63865158090020</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
           <t>power_on_with_fw-late_livefish_detection-FAIL-MEASUREMENT;</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>csm1_swb_maglan_asic_pcie-Fast_boot_asic_HBI_HW_failure_detected-Asic HBI HW failure detection for csm1_swb_maglan_asic_pcie</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t xml:space="preserve">Spectrum-6 in Flash Recovery Mode. 
 Suspect ASIC issue.
@@ -3469,61 +3553,23 @@
 </t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>NV</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>SPE</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Waiting Debug</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>40</v>
-      </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>units that will be tested in the automation</t>
-        </is>
-      </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>SPE</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Waiting Debug</t>
+        </is>
+      </c>
       <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
@@ -3537,7 +3583,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
@@ -3552,7 +3598,11 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>units that will be tested in the automation</t>
+        </is>
+      </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
@@ -3571,7 +3621,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
@@ -3605,7 +3655,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
@@ -3639,7 +3689,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
@@ -3654,11 +3704,7 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>units that will be tested in the automation</t>
-        </is>
-      </c>
+      <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
@@ -3677,27 +3723,13 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>45</v>
-      </c>
-      <c r="C56" t="n">
-        <v>63865158140044</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>63865158100002</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>63865158390004</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
@@ -3706,7 +3738,11 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>units that will be tested in the automation</t>
+        </is>
+      </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
@@ -3725,10 +3761,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C57" t="n">
-        <v>63865158140045</v>
+        <v>63865158140044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -3736,7 +3772,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>63865158090025</v>
+        <v>63865158100002</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -3744,40 +3780,16 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>63865158370045</v>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>DEV032309</t>
-        </is>
-      </c>
+        <v>63865158390004</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,2,2,3,8,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,9,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,10,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,11,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,3,3,12,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,13,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,14,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,15,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,0,3,0,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,1,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,2,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,3,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,1,3,4,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,5,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,6,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,7,10,0,31.47,-327.68,-1,-100]</t>
-        </is>
-      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -3791,21 +3803,53 @@
       <c r="Z57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>46</v>
+      </c>
+      <c r="C58" t="n">
+        <v>63865158140045</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>63865158090025</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>63865158370045</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>AOT</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -3815,7 +3859,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:11.26,12,4,24,0,93,250,32.47,3.85,11.26,-100],[eocl:11.5,12,4,24,1,93,250,32.47,3.61,11.5,-100],[eocl:11.26,12,4,24,2,93,250,32.47,3.85,11.26,-100],[eocl:11.02,12,4,24,3,93,250,32.47,4.09,11.02,-100],[eocl:11.06,12,5,24,4,94,250,32.77,4.09,11.06,-100],[eocl:11.3,12,5,24,5,94,250,32.77,3.85,11.3,-100],[eocl:11.06,12,5,24,6,94,250,32.77,4.09,11.06,-100],[eocl:11.06,12,5,24,7,94,250,32.77,4.09,11.06,-100],[eocl:11.01,12,6,24,8,95,250,32.36,4.09,11.01,-100],[eocl:11.25,12,6,24,9,95,250,32.36,3.85,11.25,-100],[eocl:11.01,12,6,24,10,95,250,32.36,4.09,11.01,-100],[eocl:11.01,12,6,24,11,95,250,32.36,4.09,11.01,-100],[eocl:11.5,12,7,24,12,96,250,32.47,3.61,11.5,-100],[eocl:11.5,12,7,24,13,96,250,32.47,3.61,11.5,-100],[eocl:11.77,12,7,24,14,96,250,32.47,3.34,11.77,-100],[eocl:11.77,12,7,24,15,96,250,32.47,3.34,11.77,-100]</t>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,2,2,3,8,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,9,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,10,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,11,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,3,3,12,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,13,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,14,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,15,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,0,3,0,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,1,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,2,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,3,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,1,3,4,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,5,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,6,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,7,10,0,31.47,-327.68,-1,-100]</t>
         </is>
       </c>
       <c r="P58" t="inlineStr"/>
@@ -3831,33 +3875,13 @@
       <c r="Z58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>47</v>
-      </c>
-      <c r="C59" t="n">
-        <v>63865158140046</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>63865158090030</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
-        <v>63865158370048</v>
-      </c>
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
@@ -3865,7 +3889,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>AOT</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -3875,7 +3899,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,4,6,8,8,31,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,6,8,9,31,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,6,8,10,31,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,6,8,11,31,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,7,8,12,32,0,31.3,-327.68,-1,-100],[eocl:-1.0,4,7,8,13,32,0,31.3,-327.68,-1,-100],[eocl:-1.0,4,7,8,14,32,0,31.3,-327.68,-1,-100],[eocl:-1.0,4,7,8,15,32,0,31.3,-327.68,-1,-100],[eocl:-1.0,4,4,8,0,29,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,4,8,1,29,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,4,8,2,29,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,4,8,3,29,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,5,8,4,30,0,31.35,-327.68,-1,-100],[eocl:-1.0,4,5,8,5,30,0,31.35,-327.68,-1,-100],[eocl:-1.0,4,5,8,6,30,0,31.35,-327.68,-1,-100],[eocl:-1.0,4,5,8,7,30,0,31.35,-327.68,-1,-100],[eocl:-1.0,1,2,1,8,3,0,31.61,-327.68,-1,-100],[eocl:-1.0,1,2,1,9,3,0,31.61,-327.68,-1,-100],[eocl:-1.0,1,2,1,10,3,0,31.61,-327.68,-1,-100],[eocl:-1.0,1,2,1,11,3,0,31.61,-327.68,-1,-100],[eocl:-1.0,1,3,1,12,4,0,31.47,-327.68,-1,-100],[eocl:-1.0,1,3,1,13,4,0,31.47,-327.68,-1,-100],[eocl:-1.0,1,3,1,14,4,0,31.47,-327.68,-1,-100],[eocl:-1.0,1,3,1,15,4,0,31.47,-327.68,-1,-100],[eocl:-1.0,1,0,1,0,1,0,31.5,-327.68,-1,-100],[eocl:-1.0,1,0,1,1,1,0,31.5,-327.68,-1,-100],[eocl:-1.0,1,0,1,2,1,0,31.5,-327.68,-1,-100],[eocl:-1.0,1,0,1,3,1,0,31.5,-327.68,-1,-100],[eocl:-1.0,1,1,1,4,2,0,31.71,-327.68,-1,-100],[eocl:-1.0,1,1,1,5,2,0,31.71,-327.68,-1,-100],[eocl:-1.0,1,1,1,6,2,0,31.71,-327.68,-1,-100],[eocl:-1.0,1,1,1,7,2,0,31.71,-327.68,-1,-100]</t>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:11.26,12,4,24,0,93,250,32.47,3.85,11.26,-100],[eocl:11.5,12,4,24,1,93,250,32.47,3.61,11.5,-100],[eocl:11.26,12,4,24,2,93,250,32.47,3.85,11.26,-100],[eocl:11.02,12,4,24,3,93,250,32.47,4.09,11.02,-100],[eocl:11.06,12,5,24,4,94,250,32.77,4.09,11.06,-100],[eocl:11.3,12,5,24,5,94,250,32.77,3.85,11.3,-100],[eocl:11.06,12,5,24,6,94,250,32.77,4.09,11.06,-100],[eocl:11.06,12,5,24,7,94,250,32.77,4.09,11.06,-100],[eocl:11.01,12,6,24,8,95,250,32.36,4.09,11.01,-100],[eocl:11.25,12,6,24,9,95,250,32.36,3.85,11.25,-100],[eocl:11.01,12,6,24,10,95,250,32.36,4.09,11.01,-100],[eocl:11.01,12,6,24,11,95,250,32.36,4.09,11.01,-100],[eocl:11.5,12,7,24,12,96,250,32.47,3.61,11.5,-100],[eocl:11.5,12,7,24,13,96,250,32.47,3.61,11.5,-100],[eocl:11.77,12,7,24,14,96,250,32.47,3.34,11.77,-100],[eocl:11.77,12,7,24,15,96,250,32.47,3.34,11.77,-100]</t>
         </is>
       </c>
       <c r="P59" t="inlineStr"/>
@@ -3897,10 +3921,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C60" t="n">
-        <v>63865158140047</v>
+        <v>63865158140046</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -3908,7 +3932,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>63865158090035</v>
+        <v>63865158090030</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3916,30 +3940,26 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>63865158370029</v>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+        <v>63865158370048</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>AOT</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,9,6,18,8,71,124.64,12.86,8.1,6.73,-18.24,nan],[prp:-18.24,9,6,18,8,71,124.64,12.86,8.1,6.73,-18.24,nan],[prb:nan,9,6,18,9,71,124.64,12.86,8.1,6.73,-18.15,nan],[prp:-18.15,9,6,18,9,71,124.64,12.86,8.1,6.73,-18.15,nan],[prb:nan,9,6,18,10,71,124.64,12.79,8.17,6.73,-19.47,nan],[prp:-19.47,9,6,18,10,71,124.64,12.79,8.17,6.73,-19.47,nan],[prb:nan,9,6,18,11,71,124.64,12.7,8.26,6.6,-19.47,nan],[prp:-19.47,9,6,18,11,71,124.64,12.7,8.26,6.6,-19.47,nan],[prb:nan,5,1,9,4,34,128.8,12.95,8.15,6.86,-22.68,nan],[prp:-22.68,5,1,9,4,34,128.8,12.95,8.15,6.86,-22.68,nan],[prb:nan,5,1,9,5,34,128.8,12.82,8.28,6.86,-21.87,nan],[prp:-21.87,5,1,9,5,34,128.8,12.82,8.28,6.86,-21.87,nan],[prb:nan,5,1,9,6,34,128.8,12.95,8.15,6.86,-22.37,nan],[prp:-22.37,5,1,9,6,34,128.8,12.95,8.15,6.86,-22.37,nan],[prb:nan,5,1,9,7,34,128.8,12.95,8.15,6.86,-22.08,nan],[prp:-22.08,5,1,9,7,34,128.8,12.95,8.15,6.86,-22.08,nan]</t>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,4,6,8,8,31,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,6,8,9,31,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,6,8,10,31,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,6,8,11,31,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,7,8,12,32,0,31.3,-327.68,-1,-100],[eocl:-1.0,4,7,8,13,32,0,31.3,-327.68,-1,-100],[eocl:-1.0,4,7,8,14,32,0,31.3,-327.68,-1,-100],[eocl:-1.0,4,7,8,15,32,0,31.3,-327.68,-1,-100],[eocl:-1.0,4,4,8,0,29,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,4,8,1,29,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,4,8,2,29,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,4,8,3,29,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,5,8,4,30,0,31.35,-327.68,-1,-100],[eocl:-1.0,4,5,8,5,30,0,31.35,-327.68,-1,-100],[eocl:-1.0,4,5,8,6,30,0,31.35,-327.68,-1,-100],[eocl:-1.0,4,5,8,7,30,0,31.35,-327.68,-1,-100],[eocl:-1.0,1,2,1,8,3,0,31.61,-327.68,-1,-100],[eocl:-1.0,1,2,1,9,3,0,31.61,-327.68,-1,-100],[eocl:-1.0,1,2,1,10,3,0,31.61,-327.68,-1,-100],[eocl:-1.0,1,2,1,11,3,0,31.61,-327.68,-1,-100],[eocl:-1.0,1,3,1,12,4,0,31.47,-327.68,-1,-100],[eocl:-1.0,1,3,1,13,4,0,31.47,-327.68,-1,-100],[eocl:-1.0,1,3,1,14,4,0,31.47,-327.68,-1,-100],[eocl:-1.0,1,3,1,15,4,0,31.47,-327.68,-1,-100],[eocl:-1.0,1,0,1,0,1,0,31.5,-327.68,-1,-100],[eocl:-1.0,1,0,1,1,1,0,31.5,-327.68,-1,-100],[eocl:-1.0,1,0,1,2,1,0,31.5,-327.68,-1,-100],[eocl:-1.0,1,0,1,3,1,0,31.5,-327.68,-1,-100],[eocl:-1.0,1,1,1,4,2,0,31.71,-327.68,-1,-100],[eocl:-1.0,1,1,1,5,2,0,31.71,-327.68,-1,-100],[eocl:-1.0,1,1,1,6,2,0,31.71,-327.68,-1,-100],[eocl:-1.0,1,1,1,7,2,0,31.71,-327.68,-1,-100]</t>
         </is>
       </c>
       <c r="P60" t="inlineStr"/>
@@ -3961,10 +3981,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C61" t="n">
-        <v>63865158140048</v>
+        <v>63865158140047</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3972,7 +3992,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>63865158090043</v>
+        <v>63865158090035</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -3980,26 +4000,30 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>63865158370043</v>
-      </c>
-      <c r="H61" t="inlineStr"/>
+        <v>63865158370029</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>AOT</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,10,0,19,0,73,0,31.02,0,-1,-100],[eocl:-1.0,10,0,19,1,73,0,31.02,0,-1,-100],[eocl:-1.0,10,0,19,2,73,0,31.02,0,-1,-100],[eocl:-1.0,10,0,19,3,73,0,31.02,0,-1,-100],[eocl:-1.0,10,1,19,4,74,0,31.07,0,-1,-100],[eocl:-1.0,10,1,19,5,74,0,31.07,0,-1,-100],[eocl:-1.0,10,1,19,6,74,0,31.07,0,-1,-100],[eocl:-1.0,10,1,19,7,74,0,31.07,0,-1,-100],[eocl:-1.0,10,2,19,8,75,0,31.46,0,-1,-100],[eocl:-1.0,10,2,19,9,75,0,31.46,0,-1,-100],[eocl:-1.0,10,2,19,10,75,0,31.46,0,-1,-100],[eocl:-1.0,10,2,19,11,75,0,31.46,0,-1,-100],[eocl:-1.0,10,3,19,12,76,0,31.59,0,-1,-100],[eocl:-1.0,10,3,19,13,76,0,31.59,0,-1,-100],[eocl:-1.0,10,3,19,14,76,0,31.59,0,-1,-100],[eocl:-1.0,10,3,19,15,76,0,31.59,0,-1,-100]</t>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,9,6,18,8,71,124.64,12.86,8.1,6.73,-18.24,nan],[prp:-18.24,9,6,18,8,71,124.64,12.86,8.1,6.73,-18.24,nan],[prb:nan,9,6,18,9,71,124.64,12.86,8.1,6.73,-18.15,nan],[prp:-18.15,9,6,18,9,71,124.64,12.86,8.1,6.73,-18.15,nan],[prb:nan,9,6,18,10,71,124.64,12.79,8.17,6.73,-19.47,nan],[prp:-19.47,9,6,18,10,71,124.64,12.79,8.17,6.73,-19.47,nan],[prb:nan,9,6,18,11,71,124.64,12.7,8.26,6.6,-19.47,nan],[prp:-19.47,9,6,18,11,71,124.64,12.7,8.26,6.6,-19.47,nan],[prb:nan,5,1,9,4,34,128.8,12.95,8.15,6.86,-22.68,nan],[prp:-22.68,5,1,9,4,34,128.8,12.95,8.15,6.86,-22.68,nan],[prb:nan,5,1,9,5,34,128.8,12.82,8.28,6.86,-21.87,nan],[prp:-21.87,5,1,9,5,34,128.8,12.82,8.28,6.86,-21.87,nan],[prb:nan,5,1,9,6,34,128.8,12.95,8.15,6.86,-22.37,nan],[prp:-22.37,5,1,9,6,34,128.8,12.95,8.15,6.86,-22.37,nan],[prb:nan,5,1,9,7,34,128.8,12.95,8.15,6.86,-22.08,nan],[prp:-22.08,5,1,9,7,34,128.8,12.95,8.15,6.86,-22.08,nan]</t>
         </is>
       </c>
       <c r="P61" t="inlineStr"/>
@@ -4021,10 +4045,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C62" t="n">
-        <v>63865158140049</v>
+        <v>63865158140048</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4032,7 +4056,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>63865158090036</v>
+        <v>63865158090043</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -4040,16 +4064,28 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>63865158370041</v>
+        <v>63865158370043</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,10,0,19,0,73,0,31.02,0,-1,-100],[eocl:-1.0,10,0,19,1,73,0,31.02,0,-1,-100],[eocl:-1.0,10,0,19,2,73,0,31.02,0,-1,-100],[eocl:-1.0,10,0,19,3,73,0,31.02,0,-1,-100],[eocl:-1.0,10,1,19,4,74,0,31.07,0,-1,-100],[eocl:-1.0,10,1,19,5,74,0,31.07,0,-1,-100],[eocl:-1.0,10,1,19,6,74,0,31.07,0,-1,-100],[eocl:-1.0,10,1,19,7,74,0,31.07,0,-1,-100],[eocl:-1.0,10,2,19,8,75,0,31.46,0,-1,-100],[eocl:-1.0,10,2,19,9,75,0,31.46,0,-1,-100],[eocl:-1.0,10,2,19,10,75,0,31.46,0,-1,-100],[eocl:-1.0,10,2,19,11,75,0,31.46,0,-1,-100],[eocl:-1.0,10,3,19,12,76,0,31.59,0,-1,-100],[eocl:-1.0,10,3,19,13,76,0,31.59,0,-1,-100],[eocl:-1.0,10,3,19,14,76,0,31.59,0,-1,-100],[eocl:-1.0,10,3,19,15,76,0,31.59,0,-1,-100]</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
@@ -4069,10 +4105,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C63" t="n">
-        <v>63865158140050</v>
+        <v>63865158140049</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4080,7 +4116,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>63865158090040</v>
+        <v>63865158090036</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -4088,7 +4124,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>63865158370050</v>
+        <v>63865158370041</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -4117,10 +4153,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C64" t="n">
-        <v>63865158140052</v>
+        <v>63865158140050</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4128,7 +4164,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>63865158090044</v>
+        <v>63865158090040</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -4136,7 +4172,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>63865158370046</v>
+        <v>63865158370050</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -4165,10 +4201,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C65" t="n">
-        <v>63865158140031</v>
+        <v>63865158140052</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4176,7 +4212,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>63865158090046</v>
+        <v>63865158090044</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -4184,7 +4220,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>63865158370049</v>
+        <v>63865158370046</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
@@ -4213,10 +4249,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C66" t="n">
-        <v>63865158140055</v>
+        <v>63865158140031</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4224,7 +4260,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>63865158090045</v>
+        <v>63865158090046</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -4232,42 +4268,17 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>63865158370023</v>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
+        <v>63865158370049</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>query_fnm_linkup-linkup_polling_fnm-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>linkup_matrix_fnm-Failed: ['port 65/0', 'port 65/1']</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>PASS FT - Fail at HS cold test GOOD RX , NO BER 
-30-SEP : cookbook flow (LPBK remating / cleaning / crossing, Windu cross) -&gt; still fail replace CSM</t>
-        </is>
-      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
@@ -4286,10 +4297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C67" t="n">
-        <v>63865158140051</v>
+        <v>63865158140055</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4297,7 +4308,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>63865158090049</v>
+        <v>63865158090045</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -4305,17 +4316,42 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>63865158370039</v>
-      </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
+        <v>63865158370023</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>query_fnm_linkup-linkup_polling_fnm-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>linkup_matrix_fnm-Failed: ['port 65/0', 'port 65/1']</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>PASS FT - Fail at HS cold test GOOD RX , NO BER 
+30-SEP : cookbook flow (LPBK remating / cleaning / crossing, Windu cross) -&gt; still fail replace CSM</t>
+        </is>
+      </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
@@ -4334,10 +4370,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C68" t="n">
-        <v>63865158140056</v>
+        <v>63865158140051</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4345,10 +4381,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>63865158090047</v>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
+        <v>63865158090049</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>63865158370039</v>
+      </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
@@ -4376,10 +4418,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C69" t="n">
-        <v>63865158140057</v>
+        <v>63865158140056</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4387,16 +4429,10 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>63865158090051</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G69" t="n">
-        <v>63865158370038</v>
-      </c>
+        <v>63865158090047</v>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
@@ -4424,15 +4460,27 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C70" t="n">
-        <v>63865158140062</v>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
+        <v>63865158140057</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>63865158090051</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>63865158370038</v>
+      </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
@@ -4460,10 +4508,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C71" t="n">
-        <v>63865158140060</v>
+        <v>63865158140062</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
@@ -4496,27 +4544,15 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C72" t="n">
-        <v>63865158140061</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>63865158090050</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G72" t="n">
-        <v>63865158370040</v>
-      </c>
+        <v>63865158140060</v>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
@@ -4544,15 +4580,27 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C73" t="n">
-        <v>63865158140058</v>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
+        <v>63865158140061</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>63865158090050</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>63865158370040</v>
+      </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
@@ -4580,10 +4628,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C74" t="n">
-        <v>63865158140059</v>
+        <v>63865158140058</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
@@ -4609,6 +4657,42 @@
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="inlineStr"/>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>62</v>
+      </c>
+      <c r="C75" t="n">
+        <v>63865158140059</v>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr"/>
+      <c r="X75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/TS3_mapping.xlsx
+++ b/TS3_mapping.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+          <t>fuse_mismatch_group1-read_fuse_missmatch-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>

--- a/TS3_mapping.xlsx
+++ b/TS3_mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z75"/>
+  <dimension ref="A1:Z79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,8 +599,16 @@
           <t>DEV032313</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>MT2640600H05</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>AOT</t>
@@ -740,7 +748,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>On-going</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -820,9 +828,21 @@
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
@@ -860,9 +880,21 @@
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>SPE</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Waiting Debug</t>
+        </is>
+      </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
@@ -940,9 +972,21 @@
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
@@ -1073,9 +1117,21 @@
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>SPE</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
@@ -1113,9 +1169,21 @@
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>SPE</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Waiting Debug</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
@@ -1237,10 +1305,14 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>DEV032309</t>
@@ -1262,9 +1334,21 @@
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>SPE</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
@@ -1342,9 +1426,21 @@
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
@@ -1422,9 +1518,21 @@
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
@@ -1458,9 +1566,21 @@
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>SPE</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
@@ -1498,9 +1618,21 @@
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>SPE</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Waiting Debug</t>
+        </is>
+      </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
@@ -1617,17 +1749,29 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>DEV032309</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>MT2640600GZE</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>AOT</t>
@@ -1703,9 +1847,21 @@
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
@@ -1740,24 +1896,64 @@
       <c r="G20" t="n">
         <v>63865158370028</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>DEV032309</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>MT2640600GZB</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:11.28,11,4,22,0,85,250,32.6,3.85,11.28,-100],[eocl:11.28,11,4,22,1,85,250,32.6,3.85,11.28,-100],[eocl:11.28,11,4,22,2,85,250,32.6,3.85,11.28,-100],[eocl:11.04,11,4,22,3,85,250,32.6,4.09,11.04,-100],[eocl:11.04,11,5,22,5,86,250,32.57,4.09,11.04,-100],[eocl:11.52,11,6,22,8,87,250,32.6,3.61,11.52,-100],[eocl:11.28,11,6,22,9,87,250,32.6,3.85,11.28,-100],[eocl:11.28,11,6,22,10,87,250,32.6,3.85,11.28,-100],[eocl:11.52,11,6,22,11,87,250,32.6,3.61,11.52,-100],[eocl:11.3,11,7,22,12,88,250,32.77,3.85,11.3,-100],[eocl:11.06,11,7,22,14,88,250,32.77,4.09,11.06,-100],[eocl:11.3,11,7,22,15,88,250,32.77,3.85,11.3,-100]</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
@@ -1792,15 +1988,31 @@
       <c r="G21" t="n">
         <v>63865158370019</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>DEV032309</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>MT2640600H00</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
           <t>AOT</t>
@@ -1819,9 +2031,21 @@
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Joy</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
@@ -1829,51 +2053,51 @@
       <c r="Z21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>13</v>
-      </c>
-      <c r="C22" t="n">
-        <v>63865158140015</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>63865158090024</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>63865158370015</v>
-      </c>
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>DEV032309</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>laser_tuning-create_mst_devices_chipset-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>mst_devices_Linkx-MST Linkx device presence</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Joy</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
@@ -1887,10 +2111,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C23" t="n">
-        <v>63865158140014</v>
+        <v>63865158140015</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1898,7 +2122,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>63865158090026</v>
+        <v>63865158090024</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1906,39 +2130,49 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>63865158370052</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+        <v>63865158370015</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>DEV032309</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>MT2640600GZF</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>AOT</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+          <t>power_on-burn_os_if_needed_and_boot_os-ERROR-OutOfBandException;</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:14.08,7,3,13,12,52,0,31.06,0.84,14.08,-100],[eocl:13.62,7,3,13,13,52,0,31.06,1.3,13.62,-100],[eocl:13.62,7,3,13,14,52,0,31.06,1.3,13.62,-100],[eocl:13.21,7,3,13,15,52,0,31.06,1.71,13.21,-100]</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>FBK stand alone IL still abnormal
-Need to replace an W-FBK
-Replaced FBK then pass</t>
-        </is>
-      </c>
+          <t>Exceed timeout on command ControlKeys.USER_COMMAND without receiving expected-reply: (ONIE: Rescue Mode ...)|(Access granted)|(Start PXE over)|(ONIE: OS Install Mode ...)|(Secure Boot Violation)|(GNU GRUB)</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
@@ -1948,7 +2182,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Joy</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -1969,33 +2203,91 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" t="n">
-        <v>63865158140013</v>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+        <v>63865158140014</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>63865158090026</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>63865158370052</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>DEV032309</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>MT2640600GZ5</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:14.08,7,3,13,12,52,0,31.06,0.84,14.08,-100],[eocl:13.62,7,3,13,13,52,0,31.06,1.3,13.62,-100],[eocl:13.62,7,3,13,14,52,0,31.06,1.3,13.62,-100],[eocl:13.21,7,3,13,15,52,0,31.06,1.71,13.21,-100]</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>FBK stand alone IL still abnormal
+Need to replace an W-FBK
+Replaced FBK then pass</t>
+        </is>
+      </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
@@ -2009,10 +2301,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C25" t="n">
-        <v>63865158140019</v>
+        <v>63865158140013</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2020,7 +2312,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>63865158090034</v>
+        <v>63865158090052</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2028,7 +2320,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>63865158370042</v>
+        <v>63865158370035</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -2045,23 +2337,29 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>AOT</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>power_on-validate_power_converter_dma_data-ERROR-Exception;</t>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>csm1_asic_brd__pdb_node_controller': 'write_i2c_block' function failed: device=/dev/mst/192.168.10.20:23108,@dev@mst@dev-i2c-6, i2c_addr=0x60, addr_width=1, reg_addr=0xc7, size=2</t>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:13.07,10,4,20,0,77,250,32.81,2.09,13.07,-100],[eocl:13.07,10,4,20,1,77,250,32.81,2.09,13.07,-100],[eocl:12.72,10,4,20,2,77,250,32.81,2.44,12.72,-100],[eocl:13.07,10,4,20,3,77,250,32.81,2.09,13.07,-100],[eocl:12.33,10,5,20,4,78,250,32.32,2.76,12.33,-100],[eocl:12.33,10,5,20,5,78,250,32.32,2.76,12.33,-100],[eocl:12.33,10,5,20,6,78,250,32.32,2.76,12.33,-100],[eocl:12.02,10,5,20,7,78,250,32.32,3.07,12.02,-100],[eocl:12.93,10,6,20,8,79,0,31.79,2.09,12.93,-100],[eocl:12.93,10,6,20,9,79,0,31.79,2.09,12.93,-100],[eocl:12.93,10,6,20,10,79,0,31.79,2.09,12.93,-100],[eocl:12.93,10,6,20,11,79,0,31.79,2.09,12.93,-100],[eocl:13.0,10,7,20,12,80,250,32.29,2.09,13,-100],[eocl:12.65,10,7,20,13,80,250,32.29,2.44,12.65,-100],[eocl:12.65,10,7,20,14,80,250,32.29,2.44,12.65,-100],[eocl:13.0,10,7,20,15,80,250,32.29,2.09,13,-100],[eocl:12.87,11,4,22,0,85,0,31.36,2.09,12.87,-100],[eocl:12.87,11,4,22,1,85,0,31.36,2.09,12.87,-100],[eocl:12.87,11,4,22,2,85,0,31.36,2.09,12.87,-100],[eocl:12.87,11,4,22,3,85,0,31.36,2.09,12.87,-100],[eocl:13.65,11,5,22,4,86,0,31.24,1.3,13.65,-100],[eocl:13.65,11,5,22,5,86,0,31.24,1.3,13.65,-100],[eocl:13.65,11,5,22,6,86,0,31.24,1.3,13.65,-100],[eocl:13.24,11,5,22,7,86,0,31.24,1.71,13.24,-100],[eocl:14.61,11,6,22,8,87,0,31.16,0.33,14.61,-100],[eocl:14.61,11,6,22,9,87,0,31.16,0.33,14.61,-100],[eocl:14.61,11,6,22,10,87,0,31.16,0.33,14.61,-100],[eocl:14.61,11,6,22,11,87,0,31.16,0.33,14.61,-100],[eocl:14.09,11,7,22,12,88,0,31.11,0.84,14.09,-100],[eocl:14.6,11,7,22,13,88,0,31.11,0.33,14.6,-100],[eocl:14.6,11,7,22,14,88,0,31.11,0.33,14.6,-100],[eocl:14.6,11,7,22,15,88,0,31.11,0.33,14.6,-100],[eocl:11.09,12,6,24,10,95,240,32.95,4.09,11.09,-100],[eocl:-1.0,3,6,6,8,23,0,31.05,0,-1,-100],[eocl:-1.0,3,6,6,9,23,0,31.05,0,-1,-100],[eocl:-1.0,3,6,6,10,23,0,31.05,0,-1,-100],[eocl:-1.0,3,6,6,11,23,0,31.05,-327.68,-1,-100],[eocl:-1.0,3,7,6,12,24,0,32,0,-1,-100],[eocl:-1.0,3,7,6,13,24,0,32,0,-1,-100],[eocl:-1.0,3,7,6,14,24,0,32,-327.68,-1,-100],[eocl:-1.0,3,7,6,15,24,0,32,0,-1,-100],[eocl:-1.0,3,4,6,0,21,0,31.48,-327.68,-1,-100],[eocl:-1.0,3,4,6,1,21,0,31.48,-327.68,-1,-100],[eocl:-1.0,3,4,6,2,21,0,31.48,-327.68,-1,-100],[eocl:-1.0,3,4,6,3,21,0,31.48,0,-1,-100],[eocl:-1.0,3,5,6,4,22,0,31.18,-327.68,-1,-100],[eocl:-1.0,3,5,6,5,22,0,31.18,0,-1,-100],[eocl:-1.0,3,5,6,6,22,0,31.18,-327.68,-1,-100],[eocl:-1.0,3,5,6,7,22,0,31.18,0,-1,-100]</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tried master PDB then pass. Replacing with new PDB to retest.
-29-SEP: Passed with new PDB - &gt; retets on PDB station </t>
+          <t>ELS1 OE1 Channel loss margin
+ELS2 OE3 no ELS input power
+ELS3 OE6 Channel loss margin
+ELS12 OE24 no ELS input power
+Remating D36 of OE1
+Remating ELS2
+Remating D36 of OE6
+Remating D36 of OE24</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr"/>
@@ -2073,7 +2371,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>Joy</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -2088,39 +2386,96 @@
       <c r="Z25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>63865158140019</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>63865158090034</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>63865158370042</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>MT2640600GZ7</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>AOT</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+          <t>power_on-validate_power_converter_dma_data-ERROR-Exception;</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-17.93,15,7,30,12,120,139.29,12.92,8.52,6.86,-17.93,nan],[prb:nan,15,7,30,12,120,139.29,12.92,8.52,6.86,-17.93,nan],[prp:-18.48,15,7,30,13,120,139.29,13.01,8.43,6.86,-18.48,nan],[prb:nan,15,7,30,13,120,139.29,13.01,8.43,6.86,-18.48,nan],[prp:-20.97,15,7,30,14,120,139.29,12.89,8.55,6.73,-20.97,nan],[prb:nan,15,7,30,14,120,139.29,12.89,8.55,6.73,-20.97,nan],[prp:-20.97,15,7,30,15,120,139.29,12.82,8.62,6.73,-20.97,nan],[prb:nan,15,7,30,15,120,139.29,12.82,8.62,6.73,-20.97,nan]</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr"/>
+          <t>csm1_asic_brd__pdb_node_controller': 'write_i2c_block' function failed: device=/dev/mst/192.168.10.20:23108,@dev@mst@dev-i2c-6, i2c_addr=0x60, addr_width=1, reg_addr=0xc7, size=2</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tried master PDB then pass. Replacing with new PDB to retest.
+29-SEP: Passed with new PDB - &gt; retets on PDB station </t>
+        </is>
+      </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Joy</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>On-going</t>
+        </is>
+      </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
@@ -2128,48 +2483,16 @@
       <c r="Z26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>17</v>
-      </c>
-      <c r="C27" t="n">
-        <v>63865158140020</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>63865158090033</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>63865158370017</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>DEV032309</t>
-        </is>
-      </c>
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
@@ -2184,15 +2507,27 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-20.41,7,4,14,0,53,109.98,12.86,7.55,6.73,-20.41,nan],[prb:nan,7,4,14,0,53,109.98,12.86,7.55,6.73,-20.41,nan],[prp:-19.47,7,4,14,1,53,109.98,12.7,7.71,6.6,-19.47,nan],[prb:nan,7,4,14,1,53,109.98,12.7,7.71,6.6,-19.47,nan],[prp:-22.68,7,4,14,2,53,109.98,12.92,7.49,6.6,-22.68,nan],[prb:nan,7,4,14,2,53,109.98,12.92,7.49,6.6,-22.68,nan],[prp:-21.87,7,4,14,3,53,109.98,12.89,7.52,6.6,-21.87,nan],[prb:nan,7,4,14,3,53,109.98,12.89,7.52,6.6,-21.87,nan],[prp:-19.91,11,4,22,0,85,119.68,12.76,8.02,6.46,-19.91,nan],[prb:nan,11,4,22,0,85,119.68,12.76,8.02,6.46,-19.91,nan],[prp:-20.22,11,4,22,1,85,119.68,12.76,8.02,6.32,-20.22,nan],[prb:nan,11,4,22,1,85,119.68,12.76,8.02,6.32,-20.22,nan],[prp:-20.97,11,4,22,2,85,119.68,12.79,7.99,6.46,-20.97,nan],[prb:nan,11,4,22,2,85,119.68,12.79,7.99,6.46,-20.97,nan],[prp:-20.97,11,4,22,3,85,119.68,12.86,7.92,6.46,-20.97,nan],[prb:nan,11,4,22,3,85,119.68,12.86,7.92,6.46,-20.97,nan]</t>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-17.93,15,7,30,12,120,139.29,12.92,8.52,6.86,-17.93,nan],[prb:nan,15,7,30,12,120,139.29,12.92,8.52,6.86,-17.93,nan],[prp:-18.48,15,7,30,13,120,139.29,13.01,8.43,6.86,-18.48,nan],[prb:nan,15,7,30,13,120,139.29,13.01,8.43,6.86,-18.48,nan],[prp:-20.97,15,7,30,14,120,139.29,12.89,8.55,6.73,-20.97,nan],[prb:nan,15,7,30,14,120,139.29,12.89,8.55,6.73,-20.97,nan],[prp:-20.97,15,7,30,15,120,139.29,12.82,8.62,6.73,-20.97,nan],[prb:nan,15,7,30,15,120,139.29,12.82,8.62,6.73,-20.97,nan]</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
@@ -2206,10 +2541,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C28" t="n">
-        <v>63865158140021</v>
+        <v>63865158140020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2217,7 +2552,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>63865158090032</v>
+        <v>63865158090033</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2225,21 +2560,33 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>63865158370018</v>
+        <v>63865158370017</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>DEV032309</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>MT2640600GZN</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
           <t>FT</t>
@@ -2250,13 +2597,29 @@
           <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-20.41,7,4,14,0,53,109.98,12.86,7.55,6.73,-20.41,nan],[prb:nan,7,4,14,0,53,109.98,12.86,7.55,6.73,-20.41,nan],[prp:-19.47,7,4,14,1,53,109.98,12.7,7.71,6.6,-19.47,nan],[prb:nan,7,4,14,1,53,109.98,12.7,7.71,6.6,-19.47,nan],[prp:-22.68,7,4,14,2,53,109.98,12.92,7.49,6.6,-22.68,nan],[prb:nan,7,4,14,2,53,109.98,12.92,7.49,6.6,-22.68,nan],[prp:-21.87,7,4,14,3,53,109.98,12.89,7.52,6.6,-21.87,nan],[prb:nan,7,4,14,3,53,109.98,12.89,7.52,6.6,-21.87,nan],[prp:-19.91,11,4,22,0,85,119.68,12.76,8.02,6.46,-19.91,nan],[prb:nan,11,4,22,0,85,119.68,12.76,8.02,6.46,-19.91,nan],[prp:-20.22,11,4,22,1,85,119.68,12.76,8.02,6.32,-20.22,nan],[prb:nan,11,4,22,1,85,119.68,12.76,8.02,6.32,-20.22,nan],[prp:-20.97,11,4,22,2,85,119.68,12.79,7.99,6.46,-20.97,nan],[prb:nan,11,4,22,2,85,119.68,12.79,7.99,6.46,-20.97,nan],[prp:-20.97,11,4,22,3,85,119.68,12.86,7.92,6.46,-20.97,nan],[prb:nan,11,4,22,3,85,119.68,12.86,7.92,6.46,-20.97,nan]</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
@@ -2264,18 +2627,58 @@
       <c r="Z28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>18</v>
+      </c>
+      <c r="C29" t="n">
+        <v>63865158140021</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>63865158090032</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>63865158370018</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>MT2640600GZL</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
           <t>FT</t>
@@ -2283,20 +2686,28 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>post_prbs_test_asic_reset-create_mst_devices_chipset-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>mst_devices_Linkx-MST Linkx device presence</t>
-        </is>
-      </c>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
@@ -2304,53 +2715,17 @@
       <c r="Z29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>19</v>
-      </c>
-      <c r="C30" t="n">
-        <v>63865158140022</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>63865158090037</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>63865158370014</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>DEV032309</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>MT2640600GZP</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
@@ -2359,20 +2734,32 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+          <t>post_prbs_test_asic_reset-create_mst_devices_chipset-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,12,6,24,8,95,119.32,12.89,7.88,6.6,-20.09,nan],[prp:-20.09,12,6,24,8,95,119.32,12.89,7.88,6.6,-20.09,nan],[prb:nan,12,6,24,9,95,119.32,12.89,7.88,6.46,-19.75,nan],[prp:-19.75,12,6,24,9,95,119.32,12.89,7.88,6.46,-19.75,nan],[prb:nan,12,6,24,10,95,119.32,12.82,7.95,6.46,-22.68,nan],[prp:-22.68,12,6,24,10,95,119.32,12.82,7.95,6.46,-22.68,nan],[prb:nan,12,6,24,11,95,119.32,12.73,8.04,6.46,-22.68,nan],[prp:-22.68,12,6,24,11,95,119.32,12.73,8.04,6.46,-22.68,nan],[prb:nan,14,5,28,4,110,139.47,12.7,8.74,6.73,-2.79,nan],[prb:nan,14,5,28,5,110,139.47,12.61,8.83,6.73,-2.33,nan],[prb:nan,14,5,28,6,110,139.47,12.67,8.77,6.73,-2.66,nan],[prb:nan,14,5,28,7,110,139.47,12.76,8.68,6.73,-18.57,nan],[prp:-18.57,14,5,28,7,110,139.47,12.76,8.68,6.73,-18.57,nan],[prb:nan,5,1,9,4,34,144.37,13.18,8.41,6.86,-21.87,nan],[prp:-21.87,5,1,9,4,34,144.37,13.18,8.41,6.86,-21.87,nan],[prb:nan,5,1,9,5,34,144.37,13.01,8.58,6.73,-21.87,nan],[prp:-21.87,5,1,9,5,34,144.37,13.01,8.58,6.73,-21.87,nan],[prb:nan,5,1,9,6,34,144.37,13.15,8.44,6.73,-22.68,nan],[prp:-22.68,5,1,9,6,34,144.37,13.15,8.44,6.73,-22.68,nan],[prb:nan,5,1,9,7,34,144.37,13.23,8.36,6.99,-22.08,nan],[prp:-22.08,5,1,9,7,34,144.37,13.23,8.36,6.99,-22.08,nan],[prp:-5.2,2,1,3,6,10,129.27,12.76,8.35,6.6,-5.2,8e-10]</t>
+          <t>mst_devices_Linkx-MST Linkx device presence</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
@@ -2386,10 +2773,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C31" t="n">
-        <v>63865158140023</v>
+        <v>63865158140022</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2397,7 +2784,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>63865158090031</v>
+        <v>63865158090037</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2405,22 +2792,66 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>63865158370009</v>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+        <v>63865158370014</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>MT2640600GZP</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,12,6,24,8,95,119.32,12.89,7.88,6.6,-20.09,nan],[prp:-20.09,12,6,24,8,95,119.32,12.89,7.88,6.6,-20.09,nan],[prb:nan,12,6,24,9,95,119.32,12.89,7.88,6.46,-19.75,nan],[prp:-19.75,12,6,24,9,95,119.32,12.89,7.88,6.46,-19.75,nan],[prb:nan,12,6,24,10,95,119.32,12.82,7.95,6.46,-22.68,nan],[prp:-22.68,12,6,24,10,95,119.32,12.82,7.95,6.46,-22.68,nan],[prb:nan,12,6,24,11,95,119.32,12.73,8.04,6.46,-22.68,nan],[prp:-22.68,12,6,24,11,95,119.32,12.73,8.04,6.46,-22.68,nan],[prb:nan,14,5,28,4,110,139.47,12.7,8.74,6.73,-2.79,nan],[prb:nan,14,5,28,5,110,139.47,12.61,8.83,6.73,-2.33,nan],[prb:nan,14,5,28,6,110,139.47,12.67,8.77,6.73,-2.66,nan],[prb:nan,14,5,28,7,110,139.47,12.76,8.68,6.73,-18.57,nan],[prp:-18.57,14,5,28,7,110,139.47,12.76,8.68,6.73,-18.57,nan],[prb:nan,5,1,9,4,34,144.37,13.18,8.41,6.86,-21.87,nan],[prp:-21.87,5,1,9,4,34,144.37,13.18,8.41,6.86,-21.87,nan],[prb:nan,5,1,9,5,34,144.37,13.01,8.58,6.73,-21.87,nan],[prp:-21.87,5,1,9,5,34,144.37,13.01,8.58,6.73,-21.87,nan],[prb:nan,5,1,9,6,34,144.37,13.15,8.44,6.73,-22.68,nan],[prp:-22.68,5,1,9,6,34,144.37,13.15,8.44,6.73,-22.68,nan],[prb:nan,5,1,9,7,34,144.37,13.23,8.36,6.99,-22.08,nan],[prp:-22.08,5,1,9,7,34,144.37,13.23,8.36,6.99,-22.08,nan],[prp:-5.2,2,1,3,6,10,129.27,12.76,8.35,6.6,-5.2,8e-10]</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
@@ -2428,47 +2859,51 @@
       <c r="Z31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>21</v>
-      </c>
-      <c r="C32" t="n">
-        <v>63865158140025</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>63865158090022</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>63865158370010</v>
-      </c>
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>CUST</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>fuse_mismatch_group1-read_fuse_missmatch-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>csm1_swb_maglan_asic_pcie_mng.yu_boot.fuse_ctrl.redundency_missmatch_cause-crspace_reg_read:mng.yu_boot.fuse_ctrl.redundency_missmatch_cause</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>SPE</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Waiting Debug</t>
+        </is>
+      </c>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
@@ -2482,10 +2917,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C33" t="n">
-        <v>63865158140024</v>
+        <v>63865158140023</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2493,7 +2928,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>63865158090023</v>
+        <v>63865158090031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2501,12 +2936,28 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>63865158370016</v>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+        <v>63865158370009</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>MT2640600H04</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
@@ -2530,10 +2981,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C34" t="n">
-        <v>63865158140026</v>
+        <v>63865158140025</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2541,7 +2992,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>63865158090029</v>
+        <v>63865158090022</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2549,32 +3000,32 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>63865158370044</v>
+        <v>63865158370010</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>MT2640600H03</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-21.87,7,1,13,4,50,119.6,12.89,7.89,6.6,-21.87,nan],[prb:nan,7,1,13,4,50,119.6,12.89,7.89,6.6,-21.87,nan],[prp:-22.37,7,1,13,5,50,119.6,12.82,7.96,6.46,-22.37,nan],[prb:nan,7,1,13,5,50,119.6,12.82,7.96,6.46,-22.37,nan],[prp:-18.15,7,1,13,6,50,119.6,12.79,7.99,6.46,-18.15,nan],[prb:nan,7,1,13,6,50,119.6,12.79,7.99,6.46,-18.15,nan],[prp:-18.15,7,1,13,7,50,119.6,12.89,7.89,6.46,-18.15,nan],[prb:nan,7,1,13,7,50,119.6,12.89,7.89,6.46,-18.15,nan],[prp:-20.09,7,3,13,12,52,124.17,12.82,8.12,6.32,-20.09,nan],[prb:nan,7,3,13,12,52,124.17,12.82,8.12,6.32,-20.09,nan],[prp:-20.09,7,3,13,13,52,124.17,12.86,8.08,6.46,-20.09,nan],[prb:nan,7,3,13,13,52,124.17,12.86,8.08,6.46,-20.09,nan],[prp:-22.37,7,3,13,14,52,124.17,12.79,8.15,6.46,-22.37,nan],[prb:nan,7,3,13,14,52,124.17,12.79,8.15,6.46,-22.37,nan],[prp:-22.37,7,3,13,15,52,124.17,12.73,8.21,6.46,-22.37,nan],[prb:nan,7,3,13,15,52,124.17,12.73,8.21,6.46,-22.37,nan],[prb:nan,4,6,8,8,31,149.44,12.76,8.98,6.6,-2.13,nan],[prp:-20.76,4,6,8,9,31,149.44,12.82,8.92,6.73,-20.76,nan],[prb:nan,4,6,8,9,31,149.44,12.82,8.92,6.73,-20.76,nan],[prp:-21.61,4,6,8,10,31,149.44,12.98,8.76,6.86,-21.61,nan],[prb:nan,4,6,8,10,31,149.44,12.98,8.76,6.86,-21.61,nan],[prp:-22.08,4,6,8,11,31,149.44,12.89,8.85,6.73,-22.08,nan],[prb:nan,4,6,8,11,31,149.44,12.89,8.85,6.73,-22.08,nan],[prp:-20.22,4,7,8,12,32,144.48,12.86,8.74,6.73,-20.22,nan],[prb:nan,4,7,8,12,32,144.48,12.86,8.74,6.73,-20.22,nan],[prp:-20.22,4,7,8,13,32,144.48,13.01,8.59,6.99,-20.22,nan],[prb:nan,4,7,8,13,32,144.48,13.01,8.59,6.99,-20.22,nan],[prp:-21.19,4,7,8,14,32,144.48,12.89,8.71,6.73,-21.19,nan],[prb:nan,4,7,8,14,32,144.48,12.89,8.71,6.73,-21.19,nan],[prp:-21.37,4,7,8,15,32,144.48,12.86,8.74,6.6,-21.37,nan],[prb:nan,4,7,8,15,32,144.48,12.86,8.74,6.6,-21.37,nan],[prp:-20.76,4,3,7,12,28,131.33,13.04,8.14,6.6,-20.76,nan],[prb:nan,4,3,7,12,28,131.33,13.04,8.14,6.6,-20.76,nan],[prb:nan,4,3,7,13,28,131.33,13.15,8.03,6.73,-2.97,nan],[prb:nan,4,3,7,14,28,131.33,12.95,8.23,6.6,-2.7,nan],[prb:nan,4,3,7,15,28,131.33,12.98,8.2,6.6,-2.39,nan],[prp:-21.61,3,6,6,8,23,124.67,12.89,8.07,6.6,-21.61,nan],[prb:nan,3,6,6,8,23,124.67,12.89,8.07,6.6,-21.61,nan],[prb:nan,3,6,6,9,23,124.67,12.98,7.98,6.73,-2.18,nan],[prb:nan,3,6,6,10,23,124.67,12.89,8.07,6.73,-2.41,nan],[prb:nan,3,6,6,11,23,124.67,12.86,8.1,6.73,-1.99,nan],[prb:nan,3,7,6,12,24,134.46,12.86,8.43,6.73,-2.66,nan],[prb:nan,3,7,6,13,24,134.46,12.89,8.4,6.73,-2.79,nan],[prb:nan,3,7,6,14,24,134.46,12.86,8.43,6.73,-2.81,nan],[prp:-22.92,3,7,6,15,24,134.46,12.79,8.5,6.6,-22.92,nan],[prb:nan,3,7,6,15,24,134.46,12.79,8.5,6.6,-22.92,nan],[prb:nan,3,4,6,0,21,129.87,12.82,8.32,6.73,-2.69,nan],[prb:nan,3,4,6,1,21,129.87,12.61,8.53,6.46,-2.88,nan],[prp:-20.22,3,4,6,2,21,129.87,12.79,8.35,6.6,-20.22,nan],[prb:nan,3,4,6,2,21,129.87,12.79,8.35,6.6,-20.22,nan],[prb:nan,3,4,6,3,21,129.87,12.82,8.32,6.6,-2.5,nan]</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
@@ -2594,10 +3045,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C35" t="n">
-        <v>63865158140028</v>
+        <v>63865158140024</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2605,7 +3056,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>63865158090021</v>
+        <v>63865158090023</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2613,11 +3064,23 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>63865158370024</v>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+        <v>63865158370016</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
@@ -2642,10 +3105,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C36" t="n">
-        <v>63865158140029</v>
+        <v>63865158140026</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2653,7 +3116,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>63865158090038</v>
+        <v>63865158090029</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2661,22 +3124,66 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>63865158370025</v>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+        <v>63865158370044</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>MT2640600GZG</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-21.87,7,1,13,4,50,119.6,12.89,7.89,6.6,-21.87,nan],[prb:nan,7,1,13,4,50,119.6,12.89,7.89,6.6,-21.87,nan],[prp:-22.37,7,1,13,5,50,119.6,12.82,7.96,6.46,-22.37,nan],[prb:nan,7,1,13,5,50,119.6,12.82,7.96,6.46,-22.37,nan],[prp:-18.15,7,1,13,6,50,119.6,12.79,7.99,6.46,-18.15,nan],[prb:nan,7,1,13,6,50,119.6,12.79,7.99,6.46,-18.15,nan],[prp:-18.15,7,1,13,7,50,119.6,12.89,7.89,6.46,-18.15,nan],[prb:nan,7,1,13,7,50,119.6,12.89,7.89,6.46,-18.15,nan],[prp:-20.09,7,3,13,12,52,124.17,12.82,8.12,6.32,-20.09,nan],[prb:nan,7,3,13,12,52,124.17,12.82,8.12,6.32,-20.09,nan],[prp:-20.09,7,3,13,13,52,124.17,12.86,8.08,6.46,-20.09,nan],[prb:nan,7,3,13,13,52,124.17,12.86,8.08,6.46,-20.09,nan],[prp:-22.37,7,3,13,14,52,124.17,12.79,8.15,6.46,-22.37,nan],[prb:nan,7,3,13,14,52,124.17,12.79,8.15,6.46,-22.37,nan],[prp:-22.37,7,3,13,15,52,124.17,12.73,8.21,6.46,-22.37,nan],[prb:nan,7,3,13,15,52,124.17,12.73,8.21,6.46,-22.37,nan],[prb:nan,4,6,8,8,31,149.44,12.76,8.98,6.6,-2.13,nan],[prp:-20.76,4,6,8,9,31,149.44,12.82,8.92,6.73,-20.76,nan],[prb:nan,4,6,8,9,31,149.44,12.82,8.92,6.73,-20.76,nan],[prp:-21.61,4,6,8,10,31,149.44,12.98,8.76,6.86,-21.61,nan],[prb:nan,4,6,8,10,31,149.44,12.98,8.76,6.86,-21.61,nan],[prp:-22.08,4,6,8,11,31,149.44,12.89,8.85,6.73,-22.08,nan],[prb:nan,4,6,8,11,31,149.44,12.89,8.85,6.73,-22.08,nan],[prp:-20.22,4,7,8,12,32,144.48,12.86,8.74,6.73,-20.22,nan],[prb:nan,4,7,8,12,32,144.48,12.86,8.74,6.73,-20.22,nan],[prp:-20.22,4,7,8,13,32,144.48,13.01,8.59,6.99,-20.22,nan],[prb:nan,4,7,8,13,32,144.48,13.01,8.59,6.99,-20.22,nan],[prp:-21.19,4,7,8,14,32,144.48,12.89,8.71,6.73,-21.19,nan],[prb:nan,4,7,8,14,32,144.48,12.89,8.71,6.73,-21.19,nan],[prp:-21.37,4,7,8,15,32,144.48,12.86,8.74,6.6,-21.37,nan],[prb:nan,4,7,8,15,32,144.48,12.86,8.74,6.6,-21.37,nan],[prp:-20.76,4,3,7,12,28,131.33,13.04,8.14,6.6,-20.76,nan],[prb:nan,4,3,7,12,28,131.33,13.04,8.14,6.6,-20.76,nan],[prb:nan,4,3,7,13,28,131.33,13.15,8.03,6.73,-2.97,nan],[prb:nan,4,3,7,14,28,131.33,12.95,8.23,6.6,-2.7,nan],[prb:nan,4,3,7,15,28,131.33,12.98,8.2,6.6,-2.39,nan],[prp:-21.61,3,6,6,8,23,124.67,12.89,8.07,6.6,-21.61,nan],[prb:nan,3,6,6,8,23,124.67,12.89,8.07,6.6,-21.61,nan],[prb:nan,3,6,6,9,23,124.67,12.98,7.98,6.73,-2.18,nan],[prb:nan,3,6,6,10,23,124.67,12.89,8.07,6.73,-2.41,nan],[prb:nan,3,6,6,11,23,124.67,12.86,8.1,6.73,-1.99,nan],[prb:nan,3,7,6,12,24,134.46,12.86,8.43,6.73,-2.66,nan],[prb:nan,3,7,6,13,24,134.46,12.89,8.4,6.73,-2.79,nan],[prb:nan,3,7,6,14,24,134.46,12.86,8.43,6.73,-2.81,nan],[prp:-22.92,3,7,6,15,24,134.46,12.79,8.5,6.6,-22.92,nan],[prb:nan,3,7,6,15,24,134.46,12.79,8.5,6.6,-22.92,nan],[prb:nan,3,4,6,0,21,129.87,12.82,8.32,6.73,-2.69,nan],[prb:nan,3,4,6,1,21,129.87,12.61,8.53,6.46,-2.88,nan],[prp:-20.22,3,4,6,2,21,129.87,12.79,8.35,6.6,-20.22,nan],[prb:nan,3,4,6,2,21,129.87,12.79,8.35,6.6,-20.22,nan],[prb:nan,3,4,6,3,21,129.87,12.82,8.32,6.6,-2.5,nan]</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
@@ -2690,10 +3197,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C37" t="n">
-        <v>63865158140030</v>
+        <v>63865158140028</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2701,7 +3208,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>63865158090042</v>
+        <v>63865158090021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2709,7 +3216,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>63865158370054</v>
+        <v>63865158370024</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -2728,21 +3235,9 @@
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,8,0,15,0,57,150,12.79,8.97,6.6,-22.08,nan],[prp:-22.08,8,0,15,0,57,150,12.79,8.97,6.6,-22.08,nan],[prb:nan,8,0,15,1,57,150,12.73,9.03,6.6,-22.08,nan],[prp:-22.08,8,0,15,1,57,150,12.73,9.03,6.6,-22.08,nan],[prb:nan,8,0,15,2,57,150,12.82,8.94,6.73,-21.61,nan],[prp:-21.61,8,0,15,2,57,150,12.82,8.94,6.73,-21.61,nan],[prb:nan,8,0,15,3,57,150,12.86,8.9,6.86,-21.87,nan],[prp:-21.87,8,0,15,3,57,150,12.86,8.9,6.86,-21.87,nan],[prb:nan,6,7,12,12,48,129.64,12.86,8.27,6.73,-19.91,nan],[prp:-19.91,6,7,12,12,48,129.64,12.86,8.27,6.73,-19.91,nan],[prb:nan,6,7,12,13,48,129.64,12.95,8.18,6.73,-20.41,nan],[prp:-20.41,6,7,12,13,48,129.64,12.95,8.18,6.73,-20.41,nan],[prb:nan,6,7,12,14,48,129.64,12.89,8.24,6.6,-23.28,nan],[prp:-23.28,6,7,12,14,48,129.64,12.89,8.24,6.6,-23.28,nan],[prb:nan,6,7,12,15,48,129.64,12.76,8.37,6.6,-22.37,nan],[prp:-22.37,6,7,12,15,48,129.64,12.76,8.37,6.6,-22.37,nan]</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
@@ -2762,10 +3257,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C38" t="n">
-        <v>63865158140037</v>
+        <v>63865158140029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2773,7 +3268,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>63865158090018</v>
+        <v>63865158090038</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2781,7 +3276,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>63865158370013</v>
+        <v>63865158370025</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2798,27 +3293,11 @@
           <t>DEV032309</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>MT2640600GZQ</t>
-        </is>
-      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-21.37,7,0,13,0,49,119.35,12.86,7.91,6.46,-21.37,nan],[prb:nan,7,0,13,0,49,119.35,12.86,7.91,6.46,-21.37,nan],[prp:-21.19,7,0,13,1,49,119.35,12.67,8.1,6.17,-21.19,nan],[prb:nan,7,0,13,1,49,119.35,12.67,8.1,6.17,-21.19,nan],[prp:-21.87,7,0,13,2,49,119.35,12.79,7.98,6.46,-21.87,nan],[prb:nan,7,0,13,2,49,119.35,12.79,7.98,6.46,-21.87,nan],[prp:-22.68,7,0,13,3,49,119.35,12.86,7.91,6.32,-22.68,nan],[prb:nan,7,0,13,3,49,119.35,12.86,7.91,6.32,-22.68,nan],[prp:-19.21,4,6,8,8,31,130.02,12.82,8.32,6.73,-19.21,nan],[prb:nan,4,6,8,8,31,130.02,12.82,8.32,6.73,-19.21,nan],[prp:-20.09,4,6,8,9,31,130.02,12.92,8.22,6.86,-20.09,nan],[prb:nan,4,6,8,9,31,130.02,12.92,8.22,6.86,-20.09,nan],[prp:-22.92,4,6,8,10,31,130.02,12.73,8.41,6.73,-22.92,nan],[prb:nan,4,6,8,10,31,130.02,12.73,8.41,6.73,-22.92,nan],[prp:-22.92,4,6,8,11,31,130.02,12.73,8.41,6.6,-22.92,nan],[prb:nan,4,6,8,11,31,130.02,12.73,8.41,6.6,-22.92,nan]</t>
-        </is>
-      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
@@ -2838,10 +3317,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C39" t="n">
-        <v>63865158140032</v>
+        <v>63865158140030</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2849,7 +3328,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>63865158090013</v>
+        <v>63865158090042</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2857,17 +3336,33 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>63865158370012</v>
+        <v>63865158370054</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>MT2640600GZU</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
           <t>FT</t>
@@ -2875,20 +3370,32 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>group_pb_button-group_pb_test-FAIL-MEASUREMENT;</t>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>group_pb_pushed-Verify group_pb button pushed</t>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,8,0,15,0,57,150,12.79,8.97,6.6,-22.08,nan],[prp:-22.08,8,0,15,0,57,150,12.79,8.97,6.6,-22.08,nan],[prb:nan,8,0,15,1,57,150,12.73,9.03,6.6,-22.08,nan],[prp:-22.08,8,0,15,1,57,150,12.73,9.03,6.6,-22.08,nan],[prb:nan,8,0,15,2,57,150,12.82,8.94,6.73,-21.61,nan],[prp:-21.61,8,0,15,2,57,150,12.82,8.94,6.73,-21.61,nan],[prb:nan,8,0,15,3,57,150,12.86,8.9,6.86,-21.87,nan],[prp:-21.87,8,0,15,3,57,150,12.86,8.9,6.86,-21.87,nan],[prb:nan,6,7,12,12,48,129.64,12.86,8.27,6.73,-19.91,nan],[prp:-19.91,6,7,12,12,48,129.64,12.86,8.27,6.73,-19.91,nan],[prb:nan,6,7,12,13,48,129.64,12.95,8.18,6.73,-20.41,nan],[prp:-20.41,6,7,12,13,48,129.64,12.95,8.18,6.73,-20.41,nan],[prb:nan,6,7,12,14,48,129.64,12.89,8.24,6.6,-23.28,nan],[prp:-23.28,6,7,12,14,48,129.64,12.89,8.24,6.6,-23.28,nan],[prb:nan,6,7,12,15,48,129.64,12.76,8.37,6.6,-22.37,nan],[prp:-22.37,6,7,12,15,48,129.64,12.76,8.37,6.6,-22.37,nan]</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
@@ -2896,18 +3403,58 @@
       <c r="Z39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>27</v>
+      </c>
+      <c r="C40" t="n">
+        <v>63865158140037</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>63865158090018</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>63865158370013</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>MT2640600GZQ</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
           <t>FT</t>
@@ -2915,20 +3462,32 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>sbc_storage_usb-passmark-FAIL-MEASUREMENT;</t>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>usb_passmark_pass-Verify usb device passed passmark</t>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-21.37,7,0,13,0,49,119.35,12.86,7.91,6.46,-21.37,nan],[prb:nan,7,0,13,0,49,119.35,12.86,7.91,6.46,-21.37,nan],[prp:-21.19,7,0,13,1,49,119.35,12.67,8.1,6.17,-21.19,nan],[prb:nan,7,0,13,1,49,119.35,12.67,8.1,6.17,-21.19,nan],[prp:-21.87,7,0,13,2,49,119.35,12.79,7.98,6.46,-21.87,nan],[prb:nan,7,0,13,2,49,119.35,12.79,7.98,6.46,-21.87,nan],[prp:-22.68,7,0,13,3,49,119.35,12.86,7.91,6.32,-22.68,nan],[prb:nan,7,0,13,3,49,119.35,12.86,7.91,6.32,-22.68,nan],[prp:-19.21,4,6,8,8,31,130.02,12.82,8.32,6.73,-19.21,nan],[prb:nan,4,6,8,8,31,130.02,12.82,8.32,6.73,-19.21,nan],[prp:-20.09,4,6,8,9,31,130.02,12.92,8.22,6.86,-20.09,nan],[prb:nan,4,6,8,9,31,130.02,12.92,8.22,6.86,-20.09,nan],[prp:-22.92,4,6,8,10,31,130.02,12.73,8.41,6.73,-22.92,nan],[prb:nan,4,6,8,10,31,130.02,12.73,8.41,6.73,-22.92,nan],[prp:-22.92,4,6,8,11,31,130.02,12.73,8.41,6.6,-22.92,nan],[prb:nan,4,6,8,11,31,130.02,12.73,8.41,6.6,-22.92,nan]</t>
         </is>
       </c>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
@@ -2936,63 +3495,51 @@
       <c r="Z40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>29</v>
-      </c>
-      <c r="C41" t="n">
-        <v>63865158140033</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>63865158090011</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>63865158370022</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>CUST</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>query_fnm_linkup-linkup_polling_fnm-FAIL-MEASUREMENT;</t>
+          <t>fuse_mismatch_group1-read_fuse_missmatch-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>linkup_matrix_fnm-Failed: ['port 65/0', 'port 65/1']</t>
+          <t>csm1_swb_maglan_asic_pcie_mng.yu_boot.fuse_ctrl.redundency_missmatch_cause-crspace_reg_read:mng.yu_boot.fuse_ctrl.redundency_missmatch_cause</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>SPE</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Waiting Debug</t>
+        </is>
+      </c>
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
@@ -3006,10 +3553,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C42" t="n">
-        <v>63865158140034</v>
+        <v>63865158140032</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3017,7 +3564,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>63865158090010</v>
+        <v>63865158090013</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3025,15 +3572,23 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>63865158370026</v>
+        <v>63865158370012</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
@@ -3043,20 +3598,32 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+          <t>group_pb_button-group_pb_test-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,10,5,20,4,78,149.65,12.98,8.77,6.86,-22.37,nan],[prp:-22.37,10,5,20,4,78,149.65,12.98,8.77,6.86,-22.37,nan],[prb:nan,10,5,20,5,78,149.65,13.01,8.74,6.86,-22.37,nan],[prp:-22.37,10,5,20,5,78,149.65,13.01,8.74,6.86,-22.37,nan],[prb:nan,10,5,20,6,78,149.65,13.04,8.71,6.86,-20.97,nan],[prp:-20.97,10,5,20,6,78,149.65,13.04,8.71,6.86,-20.97,nan],[prb:nan,10,5,20,7,78,149.65,13.09,8.66,6.86,-20.22,nan],[prp:-20.22,10,5,20,7,78,149.65,13.09,8.66,6.86,-20.22,nan]</t>
+          <t>group_pb_pushed-Verify group_pb button pushed</t>
         </is>
       </c>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Joy</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
@@ -3064,33 +3631,13 @@
       <c r="Z42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>31</v>
-      </c>
-      <c r="C43" t="n">
-        <v>63865158140035</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>63865158090014</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>63865158370053</v>
-      </c>
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
@@ -3098,29 +3645,37 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>AOT</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+          <t>sbc_storage_usb-passmark-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,4,6,8,8,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,9,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,10,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,11,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,7,8,12,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,13,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,14,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,15,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,4,8,0,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,1,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,2,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,3,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,5,8,4,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,5,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,6,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,7,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,16,6,32,8,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,9,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,10,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,11,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,7,32,12,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,13,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,14,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,15,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,4,32,0,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,1,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,2,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,3,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,5,32,4,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,5,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,6,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,7,126,0,31.84,-327.68,-1,-100]</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Try to test the ELS module on AOT master unit</t>
-        </is>
-      </c>
+          <t>usb_passmark_pass-Verify usb device passed passmark</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Joy</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
@@ -3128,33 +3683,13 @@
       <c r="Z43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>32</v>
-      </c>
-      <c r="C44" t="n">
-        <v>63865158140036</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>63865158090017</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G44" t="n">
-        <v>63865158370037</v>
-      </c>
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
@@ -3162,25 +3697,33 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>AOT</t>
+          <t>HS Cold</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:13.23,9,0,17,0,65,0,31.17,1.71,13.23,-100],[eocl:13.23,9,0,17,1,65,0,31.17,1.71,13.23,-100],[eocl:13.23,9,0,17,2,65,0,31.17,1.71,13.23,-100],[eocl:13.64,9,0,17,3,65,0,31.17,1.3,13.64,-100],[eocl:14.6,9,1,17,4,66,0,31.09,0.33,14.6,-100],[eocl:14.09,9,1,17,5,66,0,31.09,0.84,14.09,-100],[eocl:14.09,9,1,17,6,66,0,31.09,0.84,14.09,-100],[eocl:13.63,9,1,17,7,66,0,31.09,1.3,13.63,-100],[eocl:13.25,9,2,17,8,67,0,31.3,1.71,13.25,-100],[eocl:13.25,9,2,17,9,67,0,31.3,1.71,13.25,-100],[eocl:13.25,9,2,17,10,67,0,31.3,1.71,13.25,-100],[eocl:12.87,9,2,17,11,67,0,31.3,2.09,12.87,-100],[eocl:13.65,9,3,17,12,68,0,31.26,1.3,13.65,-100],[eocl:13.65,9,3,17,13,68,0,31.26,1.3,13.65,-100],[eocl:13.65,9,3,17,14,68,0,31.26,1.3,13.65,-100],[eocl:13.24,9,3,17,15,68,0,31.26,1.71,13.24,-100]</t>
-        </is>
-      </c>
+          <t>HS_COLD high speed fail MMC79 rx power margin fail</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>SPE</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Waiting Debug</t>
+        </is>
+      </c>
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
@@ -3194,10 +3737,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C45" t="n">
-        <v>63865158140031</v>
+        <v>63865158140033</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3205,7 +3748,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>63865158090046</v>
+        <v>63865158090011</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3213,22 +3756,66 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>63865158370021</v>
-      </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
+        <v>63865158370022</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>MT2640600GZV</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>query_fnm_linkup-linkup_polling_fnm-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>linkup_matrix_fnm-Failed: ['port 65/0', 'port 65/1']</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Joy</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
@@ -3242,10 +3829,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C46" t="n">
-        <v>63865158140038</v>
+        <v>63865158140034</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3253,7 +3840,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>63865158090012</v>
+        <v>63865158090010</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3261,22 +3848,66 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>63865158370027</v>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
+        <v>63865158370026</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>MT2640600GZ2</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,10,5,20,4,78,149.65,12.98,8.77,6.86,-22.37,nan],[prp:-22.37,10,5,20,4,78,149.65,12.98,8.77,6.86,-22.37,nan],[prb:nan,10,5,20,5,78,149.65,13.01,8.74,6.86,-22.37,nan],[prp:-22.37,10,5,20,5,78,149.65,13.01,8.74,6.86,-22.37,nan],[prb:nan,10,5,20,6,78,149.65,13.04,8.71,6.86,-20.97,nan],[prp:-20.97,10,5,20,6,78,149.65,13.04,8.71,6.86,-20.97,nan],[prb:nan,10,5,20,7,78,149.65,13.09,8.66,6.86,-20.22,nan],[prp:-20.22,10,5,20,7,78,149.65,13.09,8.66,6.86,-20.22,nan]</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
@@ -3290,10 +3921,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C47" t="n">
-        <v>63865158140039</v>
+        <v>63865158140035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3301,7 +3932,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>63865158090039</v>
+        <v>63865158090014</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3309,22 +3940,70 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>63865158370020</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
+        <v>63865158370053</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>MT2640600GZ3</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,4,6,8,8,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,9,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,10,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,6,8,11,31,0,31.54,-327.68,-1,-100],[eocl:-1.0,4,7,8,12,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,13,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,14,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,7,8,15,32,0,31.67,-327.68,-1,-100],[eocl:-1.0,4,4,8,0,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,1,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,2,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,4,8,3,29,0,31.57,-327.68,-1,-100],[eocl:-1.0,4,5,8,4,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,5,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,6,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,4,5,8,7,30,0,31.86,-327.68,-1,-100],[eocl:-1.0,16,6,32,8,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,9,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,10,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,6,32,11,127,0,31.3,-327.68,-1,-100],[eocl:-1.0,16,7,32,12,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,13,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,14,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,7,32,15,128,0,31.45,-327.68,-1,-100],[eocl:-1.0,16,4,32,0,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,1,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,2,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,4,32,3,125,0,31.21,-327.68,-1,-100],[eocl:-1.0,16,5,32,4,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,5,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,6,126,0,31.84,-327.68,-1,-100],[eocl:-1.0,16,5,32,7,126,0,31.84,-327.68,-1,-100]</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Try to test the ELS module on AOT master unit</t>
+        </is>
+      </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
@@ -3338,10 +4017,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C48" t="n">
-        <v>63865158140040</v>
+        <v>63865158140036</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3349,7 +4028,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>63865158090016</v>
+        <v>63865158090017</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3357,22 +4036,66 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>63865158370055</v>
-      </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
+        <v>63865158370037</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>MT2640600GZY</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:13.23,9,0,17,0,65,0,31.17,1.71,13.23,-100],[eocl:13.23,9,0,17,1,65,0,31.17,1.71,13.23,-100],[eocl:13.23,9,0,17,2,65,0,31.17,1.71,13.23,-100],[eocl:13.64,9,0,17,3,65,0,31.17,1.3,13.64,-100],[eocl:14.6,9,1,17,4,66,0,31.09,0.33,14.6,-100],[eocl:14.09,9,1,17,5,66,0,31.09,0.84,14.09,-100],[eocl:14.09,9,1,17,6,66,0,31.09,0.84,14.09,-100],[eocl:13.63,9,1,17,7,66,0,31.09,1.3,13.63,-100],[eocl:13.25,9,2,17,8,67,0,31.3,1.71,13.25,-100],[eocl:13.25,9,2,17,9,67,0,31.3,1.71,13.25,-100],[eocl:13.25,9,2,17,10,67,0,31.3,1.71,13.25,-100],[eocl:12.87,9,2,17,11,67,0,31.3,2.09,12.87,-100],[eocl:13.65,9,3,17,12,68,0,31.26,1.3,13.65,-100],[eocl:13.65,9,3,17,13,68,0,31.26,1.3,13.65,-100],[eocl:13.65,9,3,17,14,68,0,31.26,1.3,13.65,-100],[eocl:13.24,9,3,17,15,68,0,31.26,1.71,13.24,-100]</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
@@ -3386,10 +4109,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C49" t="n">
-        <v>63865158140041</v>
+        <v>63865158140031</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3397,7 +4120,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>63865158090015</v>
+        <v>63865158090046</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3405,7 +4128,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>63865158370056</v>
+        <v>63865158370021</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -3417,9 +4140,21 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>MT2640600GZH</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
@@ -3428,7 +4163,11 @@
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr"/>
@@ -3442,10 +4181,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C50" t="n">
-        <v>63865158140042</v>
+        <v>63865158140038</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3453,7 +4192,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>63865158090019</v>
+        <v>63865158090012</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3461,34 +4200,46 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>63865158370047</v>
-      </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,13,4,26,0,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,1,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,2,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,3,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,5,26,4,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,5,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,6,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,7,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,6,26,8,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,9,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,10,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,11,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,7,26,12,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,13,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,14,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,15,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,14,0,27,0,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,1,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,2,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,3,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,1,27,4,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,5,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,6,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,7,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,2,27,8,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,9,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,10,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,11,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,3,27,12,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,13,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,14,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,15,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,4,28,0,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,1,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,2,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,3,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,5,28,4,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,5,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,6,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,7,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,6,28,8,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,9,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,10,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,11,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,7,28,12,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,13,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,14,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,15,112,0,31.85,-327.68,-1,-100]</t>
-        </is>
-      </c>
+        <v>63865158370027</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>MT2640600GZK</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
@@ -3502,10 +4253,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C51" t="n">
-        <v>63865158140043</v>
+        <v>63865158140039</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3513,44 +4264,45 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>63865158090020</v>
+        <v>63865158090039</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>63865158370020</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>AOT</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>power_on_with_fw-late_livefish_detection-FAIL-MEASUREMENT;</t>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>csm1_swb_maglan_asic_pcie-Fast_boot_asic_HBI_HW_failure_detected-Asic HBI HW failure detection for csm1_swb_maglan_asic_pcie</t>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,6,5,12,4,46,139.29,12.86,8.58,6.73,-20.76,nan],[prp:-20.76,6,5,12,4,46,139.29,12.86,8.58,6.73,-20.76,nan],[prb:nan,6,5,12,5,46,139.29,12.98,8.46,6.73,-20.97,nan],[prp:-20.97,6,5,12,5,46,139.29,12.98,8.46,6.73,-20.97,nan],[prb:nan,6,5,12,6,46,139.29,13.01,8.43,6.86,-18.7,nan],[prp:-18.7,6,5,12,6,46,139.29,13.01,8.43,6.86,-18.7,nan],[prb:nan,6,5,12,7,46,139.29,12.86,8.58,6.6,-18.7,nan],[prp:-18.7,6,5,12,7,46,139.29,12.86,8.58,6.6,-18.7,nan],[prb:4e-4,15,1,29,4,114,144.7,12.95,8.65,6.73,-2.03,4e-4],[prb:4e-4,15,1,29,5,114,144.7,12.73,8.87,6.46,-2.51,4e-4],[prb:4e-4,15,1,29,6,114,144.7,12.98,8.62,6.99,-2.41,4e-4],[prb:4e-4,15,1,29,7,114,144.7,13.04,8.56,6.86,-1.67,4e-4]</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spectrum-6 in Flash Recovery Mode. 
-Suspect ASIC issue.
-NV : share details 
-JE130526T0960963100707
-E6B171_9_2_8
-01 OCT: ULT E6B171_9_2_8 passed FT on rev_2B.
-It passed HBI HS test, without failures (FT1 and FT2).
-</t>
+          <t>ELS15 OE29 mmc114 partner raw ber 4e-4
+Swap ELS15 &amp; 16 Windu
+PFT Fail ELS15 OE29 mmc114 partner raw ber 4e-4</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr"/>
@@ -3583,31 +4335,71 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>40</v>
-      </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="C52" t="n">
+        <v>63865158140040</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>63865158090016</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>63865158370055</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>units that will be tested in the automation</t>
+          <t>High speed fail; MMC128 no BER
+Swap ELS16/9
+Still High speed fail; MMC128 no BER</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>SPE</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Waiting Debug</t>
+        </is>
+      </c>
       <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
@@ -3621,15 +4413,37 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>41</v>
-      </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+        <v>37</v>
+      </c>
+      <c r="C53" t="n">
+        <v>63865158140041</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>63865158090015</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>63865158370056</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
@@ -3655,27 +4469,85 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>42</v>
-      </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="C54" t="n">
+        <v>63865158140042</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>63865158090019</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>63865158370047</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>MT2640600GZX</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,13,4,26,0,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,1,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,2,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,4,26,3,101,0,31.09,-327.68,-1,-100],[eocl:-1.0,13,5,26,4,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,5,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,6,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,5,26,7,102,0,31.58,-327.68,-1,-100],[eocl:-1.0,13,6,26,8,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,9,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,10,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,6,26,11,103,0,31.13,-327.68,-1,-100],[eocl:-1.0,13,7,26,12,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,13,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,14,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,13,7,26,15,104,0,31.65,-327.68,-1,-100],[eocl:-1.0,14,0,27,0,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,1,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,2,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,0,27,3,105,0,31.46,-327.68,-1,-100],[eocl:-1.0,14,1,27,4,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,5,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,6,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,1,27,7,106,0,31.55,-327.68,-1,-100],[eocl:-1.0,14,2,27,8,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,9,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,10,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,2,27,11,107,0,31.69,-327.68,-1,-100],[eocl:-1.0,14,3,27,12,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,13,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,14,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,3,27,15,108,0,31.45,-327.68,-1,-100],[eocl:-1.0,14,4,28,0,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,1,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,2,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,4,28,3,109,0,31.11,-327.68,-1,-100],[eocl:-1.0,14,5,28,4,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,5,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,6,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,5,28,7,110,0,30.86,-327.68,-1,-100],[eocl:-1.0,14,6,28,8,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,9,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,10,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,6,28,11,111,0,31.61,-327.68,-1,-100],[eocl:-1.0,14,7,28,12,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,13,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,14,112,0,31.85,-327.68,-1,-100],[eocl:-1.0,14,7,28,15,112,0,31.85,-327.68,-1,-100]</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr"/>
@@ -3689,27 +4561,74 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>43</v>
-      </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="C55" t="n">
+        <v>63865158140043</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>63865158090020</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>power_on_with_fw-late_livefish_detection-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>csm1_swb_maglan_asic_pcie-Fast_boot_asic_HBI_HW_failure_detected-Asic HBI HW failure detection for csm1_swb_maglan_asic_pcie</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spectrum-6 in Flash Recovery Mode. 
+Suspect ASIC issue.
+NV : share details 
+JE130526T0960963100707
+E6B171_9_2_8
+01 OCT: ULT E6B171_9_2_8 passed FT on rev_2B.
+It passed HBI HS test, without failures (FT1 and FT2).
+</t>
+        </is>
+      </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>SPE</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Waiting Debug</t>
+        </is>
+      </c>
       <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
@@ -3723,10 +4642,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>44</v>
-      </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="C56" t="n">
+        <v>63865158150001</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
@@ -3761,27 +4686,19 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C57" t="n">
-        <v>63865158140044</v>
+        <v>63865158150002</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E57" t="n">
-        <v>63865158100002</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
-        <v>63865158390004</v>
-      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
@@ -3809,59 +4726,27 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C58" t="n">
-        <v>63865158140045</v>
+        <v>63865158150003</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E58" t="n">
-        <v>63865158090025</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>63865158370045</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>DEV032309</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,2,2,3,8,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,9,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,10,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,11,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,3,3,12,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,13,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,14,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,15,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,0,3,0,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,1,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,2,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,3,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,1,3,4,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,5,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,6,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,7,10,0,31.47,-327.68,-1,-100]</t>
-        </is>
-      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
@@ -3875,10 +4760,22 @@
       <c r="Z58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>43</v>
+      </c>
+      <c r="C59" t="n">
+        <v>63865158150004</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
@@ -3887,21 +4784,9 @@
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:11.26,12,4,24,0,93,250,32.47,3.85,11.26,-100],[eocl:11.5,12,4,24,1,93,250,32.47,3.61,11.5,-100],[eocl:11.26,12,4,24,2,93,250,32.47,3.85,11.26,-100],[eocl:11.02,12,4,24,3,93,250,32.47,4.09,11.02,-100],[eocl:11.06,12,5,24,4,94,250,32.77,4.09,11.06,-100],[eocl:11.3,12,5,24,5,94,250,32.77,3.85,11.3,-100],[eocl:11.06,12,5,24,6,94,250,32.77,4.09,11.06,-100],[eocl:11.06,12,5,24,7,94,250,32.77,4.09,11.06,-100],[eocl:11.01,12,6,24,8,95,250,32.36,4.09,11.01,-100],[eocl:11.25,12,6,24,9,95,250,32.36,3.85,11.25,-100],[eocl:11.01,12,6,24,10,95,250,32.36,4.09,11.01,-100],[eocl:11.01,12,6,24,11,95,250,32.36,4.09,11.01,-100],[eocl:11.5,12,7,24,12,96,250,32.47,3.61,11.5,-100],[eocl:11.5,12,7,24,13,96,250,32.47,3.61,11.5,-100],[eocl:11.77,12,7,24,14,96,250,32.47,3.34,11.77,-100],[eocl:11.77,12,7,24,15,96,250,32.47,3.34,11.77,-100]</t>
-        </is>
-      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
@@ -3921,48 +4806,32 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C60" t="n">
-        <v>63865158140046</v>
+        <v>63865158150005</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E60" t="n">
-        <v>63865158090030</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
-        <v>63865158370048</v>
-      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>AOT</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,4,6,8,8,31,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,6,8,9,31,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,6,8,10,31,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,6,8,11,31,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,7,8,12,32,0,31.3,-327.68,-1,-100],[eocl:-1.0,4,7,8,13,32,0,31.3,-327.68,-1,-100],[eocl:-1.0,4,7,8,14,32,0,31.3,-327.68,-1,-100],[eocl:-1.0,4,7,8,15,32,0,31.3,-327.68,-1,-100],[eocl:-1.0,4,4,8,0,29,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,4,8,1,29,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,4,8,2,29,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,4,8,3,29,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,5,8,4,30,0,31.35,-327.68,-1,-100],[eocl:-1.0,4,5,8,5,30,0,31.35,-327.68,-1,-100],[eocl:-1.0,4,5,8,6,30,0,31.35,-327.68,-1,-100],[eocl:-1.0,4,5,8,7,30,0,31.35,-327.68,-1,-100],[eocl:-1.0,1,2,1,8,3,0,31.61,-327.68,-1,-100],[eocl:-1.0,1,2,1,9,3,0,31.61,-327.68,-1,-100],[eocl:-1.0,1,2,1,10,3,0,31.61,-327.68,-1,-100],[eocl:-1.0,1,2,1,11,3,0,31.61,-327.68,-1,-100],[eocl:-1.0,1,3,1,12,4,0,31.47,-327.68,-1,-100],[eocl:-1.0,1,3,1,13,4,0,31.47,-327.68,-1,-100],[eocl:-1.0,1,3,1,14,4,0,31.47,-327.68,-1,-100],[eocl:-1.0,1,3,1,15,4,0,31.47,-327.68,-1,-100],[eocl:-1.0,1,0,1,0,1,0,31.5,-327.68,-1,-100],[eocl:-1.0,1,0,1,1,1,0,31.5,-327.68,-1,-100],[eocl:-1.0,1,0,1,2,1,0,31.5,-327.68,-1,-100],[eocl:-1.0,1,0,1,3,1,0,31.5,-327.68,-1,-100],[eocl:-1.0,1,1,1,4,2,0,31.71,-327.68,-1,-100],[eocl:-1.0,1,1,1,5,2,0,31.71,-327.68,-1,-100],[eocl:-1.0,1,1,1,6,2,0,31.71,-327.68,-1,-100],[eocl:-1.0,1,1,1,7,2,0,31.71,-327.68,-1,-100]</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>units that will be tested in the automation</t>
+        </is>
+      </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
@@ -3981,10 +4850,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C61" t="n">
-        <v>63865158140047</v>
+        <v>63865158140044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3992,7 +4861,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>63865158090035</v>
+        <v>63865158100002</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4000,11 +4869,11 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>63865158370029</v>
+        <v>63865158390004</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -4018,20 +4887,39 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+          <t>post_prbs_test_asic_reset-create_mst_devices_chipset-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,9,6,18,8,71,124.64,12.86,8.1,6.73,-18.24,nan],[prp:-18.24,9,6,18,8,71,124.64,12.86,8.1,6.73,-18.24,nan],[prb:nan,9,6,18,9,71,124.64,12.86,8.1,6.73,-18.15,nan],[prp:-18.15,9,6,18,9,71,124.64,12.86,8.1,6.73,-18.15,nan],[prb:nan,9,6,18,10,71,124.64,12.79,8.17,6.73,-19.47,nan],[prp:-19.47,9,6,18,10,71,124.64,12.79,8.17,6.73,-19.47,nan],[prb:nan,9,6,18,11,71,124.64,12.7,8.26,6.6,-19.47,nan],[prp:-19.47,9,6,18,11,71,124.64,12.7,8.26,6.6,-19.47,nan],[prb:nan,5,1,9,4,34,128.8,12.95,8.15,6.86,-22.68,nan],[prp:-22.68,5,1,9,4,34,128.8,12.95,8.15,6.86,-22.68,nan],[prb:nan,5,1,9,5,34,128.8,12.82,8.28,6.86,-21.87,nan],[prp:-21.87,5,1,9,5,34,128.8,12.82,8.28,6.86,-21.87,nan],[prb:nan,5,1,9,6,34,128.8,12.95,8.15,6.86,-22.37,nan],[prp:-22.37,5,1,9,6,34,128.8,12.95,8.15,6.86,-22.37,nan],[prb:nan,5,1,9,7,34,128.8,12.95,8.15,6.86,-22.08,nan],[prp:-22.08,5,1,9,7,34,128.8,12.95,8.15,6.86,-22.08,nan]</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr"/>
+          <t>mst_devices_Linkx-MST Linkx device presence</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Same issue as before
+Swap ELS9/12 and retest FT(D)
+Pass post_prbs_test_asic_reset-create_mst_devices_chipset-FAIL-MEASUREMENT
+-&gt; Run -cof mode check pass without high speed</t>
+        </is>
+      </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>SPE</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Waiting Debug</t>
+        </is>
+      </c>
       <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
@@ -4045,10 +4933,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C62" t="n">
-        <v>63865158140048</v>
+        <v>63865158140045</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4056,7 +4944,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>63865158090043</v>
+        <v>63865158090025</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -4064,13 +4952,33 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>63865158370043</v>
-      </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
+        <v>63865158370045</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>MT2640600GZM</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr">
         <is>
           <t>AOT</t>
@@ -4083,15 +4991,27 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,10,0,19,0,73,0,31.02,0,-1,-100],[eocl:-1.0,10,0,19,1,73,0,31.02,0,-1,-100],[eocl:-1.0,10,0,19,2,73,0,31.02,0,-1,-100],[eocl:-1.0,10,0,19,3,73,0,31.02,0,-1,-100],[eocl:-1.0,10,1,19,4,74,0,31.07,0,-1,-100],[eocl:-1.0,10,1,19,5,74,0,31.07,0,-1,-100],[eocl:-1.0,10,1,19,6,74,0,31.07,0,-1,-100],[eocl:-1.0,10,1,19,7,74,0,31.07,0,-1,-100],[eocl:-1.0,10,2,19,8,75,0,31.46,0,-1,-100],[eocl:-1.0,10,2,19,9,75,0,31.46,0,-1,-100],[eocl:-1.0,10,2,19,10,75,0,31.46,0,-1,-100],[eocl:-1.0,10,2,19,11,75,0,31.46,0,-1,-100],[eocl:-1.0,10,3,19,12,76,0,31.59,0,-1,-100],[eocl:-1.0,10,3,19,13,76,0,31.59,0,-1,-100],[eocl:-1.0,10,3,19,14,76,0,31.59,0,-1,-100],[eocl:-1.0,10,3,19,15,76,0,31.59,0,-1,-100]</t>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,2,2,3,8,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,9,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,10,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,2,3,11,11,0,31.57,-327.68,-1,-100],[eocl:-1.0,2,3,3,12,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,13,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,14,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,3,3,15,12,0,31.56,-327.68,-1,-100],[eocl:-1.0,2,0,3,0,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,1,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,2,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,0,3,3,9,0,30.85,-327.68,-1,-100],[eocl:-1.0,2,1,3,4,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,5,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,6,10,0,31.47,-327.68,-1,-100],[eocl:-1.0,2,1,3,7,10,0,31.47,-327.68,-1,-100]</t>
         </is>
       </c>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
@@ -4099,47 +5019,51 @@
       <c r="Z62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>TS3</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>50</v>
-      </c>
-      <c r="C63" t="n">
-        <v>63865158140049</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>63865158090036</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G63" t="n">
-        <v>63865158370041</v>
-      </c>
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:11.26,12,4,24,0,93,250,32.47,3.85,11.26,-100],[eocl:11.5,12,4,24,1,93,250,32.47,3.61,11.5,-100],[eocl:11.26,12,4,24,2,93,250,32.47,3.85,11.26,-100],[eocl:11.02,12,4,24,3,93,250,32.47,4.09,11.02,-100],[eocl:11.06,12,5,24,4,94,250,32.77,4.09,11.06,-100],[eocl:11.3,12,5,24,5,94,250,32.77,3.85,11.3,-100],[eocl:11.06,12,5,24,6,94,250,32.77,4.09,11.06,-100],[eocl:11.06,12,5,24,7,94,250,32.77,4.09,11.06,-100],[eocl:11.01,12,6,24,8,95,250,32.36,4.09,11.01,-100],[eocl:11.25,12,6,24,9,95,250,32.36,3.85,11.25,-100],[eocl:11.01,12,6,24,10,95,250,32.36,4.09,11.01,-100],[eocl:11.01,12,6,24,11,95,250,32.36,4.09,11.01,-100],[eocl:11.5,12,7,24,12,96,250,32.47,3.61,11.5,-100],[eocl:11.5,12,7,24,13,96,250,32.47,3.61,11.5,-100],[eocl:11.77,12,7,24,14,96,250,32.47,3.34,11.77,-100],[eocl:11.77,12,7,24,15,96,250,32.47,3.34,11.77,-100]</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr"/>
       <c r="X63" t="inlineStr"/>
@@ -4153,10 +5077,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C64" t="n">
-        <v>63865158140050</v>
+        <v>63865158140046</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4164,7 +5088,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>63865158090040</v>
+        <v>63865158090030</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -4172,22 +5096,66 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>63865158370050</v>
-      </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
+        <v>63865158370048</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>MT2640600GZM</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,4,6,8,8,31,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,6,8,9,31,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,6,8,10,31,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,6,8,11,31,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,7,8,12,32,0,31.3,-327.68,-1,-100],[eocl:-1.0,4,7,8,13,32,0,31.3,-327.68,-1,-100],[eocl:-1.0,4,7,8,14,32,0,31.3,-327.68,-1,-100],[eocl:-1.0,4,7,8,15,32,0,31.3,-327.68,-1,-100],[eocl:-1.0,4,4,8,0,29,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,4,8,1,29,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,4,8,2,29,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,4,8,3,29,0,31.59,-327.68,-1,-100],[eocl:-1.0,4,5,8,4,30,0,31.35,-327.68,-1,-100],[eocl:-1.0,4,5,8,5,30,0,31.35,-327.68,-1,-100],[eocl:-1.0,4,5,8,6,30,0,31.35,-327.68,-1,-100],[eocl:-1.0,4,5,8,7,30,0,31.35,-327.68,-1,-100],[eocl:-1.0,1,2,1,8,3,0,31.61,-327.68,-1,-100],[eocl:-1.0,1,2,1,9,3,0,31.61,-327.68,-1,-100],[eocl:-1.0,1,2,1,10,3,0,31.61,-327.68,-1,-100],[eocl:-1.0,1,2,1,11,3,0,31.61,-327.68,-1,-100],[eocl:-1.0,1,3,1,12,4,0,31.47,-327.68,-1,-100],[eocl:-1.0,1,3,1,13,4,0,31.47,-327.68,-1,-100],[eocl:-1.0,1,3,1,14,4,0,31.47,-327.68,-1,-100],[eocl:-1.0,1,3,1,15,4,0,31.47,-327.68,-1,-100],[eocl:-1.0,1,0,1,0,1,0,31.5,-327.68,-1,-100],[eocl:-1.0,1,0,1,1,1,0,31.5,-327.68,-1,-100],[eocl:-1.0,1,0,1,2,1,0,31.5,-327.68,-1,-100],[eocl:-1.0,1,0,1,3,1,0,31.5,-327.68,-1,-100],[eocl:-1.0,1,1,1,4,2,0,31.71,-327.68,-1,-100],[eocl:-1.0,1,1,1,5,2,0,31.71,-327.68,-1,-100],[eocl:-1.0,1,1,1,6,2,0,31.71,-327.68,-1,-100],[eocl:-1.0,1,1,1,7,2,0,31.71,-327.68,-1,-100]</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr"/>
       <c r="X64" t="inlineStr"/>
@@ -4201,10 +5169,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C65" t="n">
-        <v>63865158140052</v>
+        <v>63865158140047</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4212,7 +5180,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>63865158090044</v>
+        <v>63865158090035</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -4220,22 +5188,66 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>63865158370046</v>
-      </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
+        <v>63865158370029</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>MT2640600GZZ</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,9,6,18,8,71,124.64,12.86,8.1,6.73,-18.24,nan],[prp:-18.24,9,6,18,8,71,124.64,12.86,8.1,6.73,-18.24,nan],[prb:nan,9,6,18,9,71,124.64,12.86,8.1,6.73,-18.15,nan],[prp:-18.15,9,6,18,9,71,124.64,12.86,8.1,6.73,-18.15,nan],[prb:nan,9,6,18,10,71,124.64,12.79,8.17,6.73,-19.47,nan],[prp:-19.47,9,6,18,10,71,124.64,12.79,8.17,6.73,-19.47,nan],[prb:nan,9,6,18,11,71,124.64,12.7,8.26,6.6,-19.47,nan],[prp:-19.47,9,6,18,11,71,124.64,12.7,8.26,6.6,-19.47,nan],[prb:nan,5,1,9,4,34,128.8,12.95,8.15,6.86,-22.68,nan],[prp:-22.68,5,1,9,4,34,128.8,12.95,8.15,6.86,-22.68,nan],[prb:nan,5,1,9,5,34,128.8,12.82,8.28,6.86,-21.87,nan],[prp:-21.87,5,1,9,5,34,128.8,12.82,8.28,6.86,-21.87,nan],[prb:nan,5,1,9,6,34,128.8,12.95,8.15,6.86,-22.37,nan],[prp:-22.37,5,1,9,6,34,128.8,12.95,8.15,6.86,-22.37,nan],[prb:nan,5,1,9,7,34,128.8,12.95,8.15,6.86,-22.08,nan],[prp:-22.08,5,1,9,7,34,128.8,12.95,8.15,6.86,-22.08,nan]</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V65" t="inlineStr"/>
       <c r="W65" t="inlineStr"/>
       <c r="X65" t="inlineStr"/>
@@ -4249,10 +5261,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C66" t="n">
-        <v>63865158140031</v>
+        <v>63865158140048</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4260,7 +5272,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>63865158090046</v>
+        <v>63865158090043</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -4268,22 +5280,66 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>63865158370049</v>
-      </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
+        <v>63865158370043</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>MT2640600GZD</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:-1.0,10,0,19,0,73,0,31.02,0,-1,-100],[eocl:-1.0,10,0,19,1,73,0,31.02,0,-1,-100],[eocl:-1.0,10,0,19,2,73,0,31.02,0,-1,-100],[eocl:-1.0,10,0,19,3,73,0,31.02,0,-1,-100],[eocl:-1.0,10,1,19,4,74,0,31.07,0,-1,-100],[eocl:-1.0,10,1,19,5,74,0,31.07,0,-1,-100],[eocl:-1.0,10,1,19,6,74,0,31.07,0,-1,-100],[eocl:-1.0,10,1,19,7,74,0,31.07,0,-1,-100],[eocl:-1.0,10,2,19,8,75,0,31.46,0,-1,-100],[eocl:-1.0,10,2,19,9,75,0,31.46,0,-1,-100],[eocl:-1.0,10,2,19,10,75,0,31.46,0,-1,-100],[eocl:-1.0,10,2,19,11,75,0,31.46,0,-1,-100],[eocl:-1.0,10,3,19,12,76,0,31.59,0,-1,-100],[eocl:-1.0,10,3,19,13,76,0,31.59,0,-1,-100],[eocl:-1.0,10,3,19,14,76,0,31.59,0,-1,-100],[eocl:-1.0,10,3,19,15,76,0,31.59,0,-1,-100]</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V66" t="inlineStr"/>
       <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr"/>
@@ -4297,10 +5353,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C67" t="n">
-        <v>63865158140055</v>
+        <v>63865158140049</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4308,7 +5364,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>63865158090045</v>
+        <v>63865158090036</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -4316,7 +5372,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>63865158370023</v>
+        <v>63865158370041</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -4325,12 +5381,24 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>MT2640600GZ4</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr">
         <is>
           <t>FT</t>
@@ -4338,25 +5406,32 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>query_fnm_linkup-linkup_polling_fnm-FAIL-MEASUREMENT;</t>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>linkup_matrix_fnm-Failed: ['port 65/0', 'port 65/1']</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>PASS FT - Fail at HS cold test GOOD RX , NO BER 
-30-SEP : cookbook flow (LPBK remating / cleaning / crossing, Windu cross) -&gt; still fail replace CSM</t>
-        </is>
-      </c>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-21.61,8,6,16,8,63,130.1,12.92,8.22,6.73,-21.61,nan],[prb:nan,8,6,16,8,63,130.1,12.92,8.22,6.73,-21.61,nan],[prp:-21.37,8,6,16,9,63,130.1,13.04,8.1,6.99,-21.37,nan],[prb:nan,8,6,16,9,63,130.1,13.04,8.1,6.99,-21.37,nan],[prp:-21.61,8,6,16,10,63,130.1,12.79,8.35,6.73,-21.61,nan],[prb:nan,8,6,16,10,63,130.1,12.79,8.35,6.73,-21.61,nan],[prp:-21.61,8,6,16,11,63,130.1,12.67,8.47,6.6,-21.61,nan],[prb:nan,8,6,16,11,63,130.1,12.67,8.47,6.6,-21.61,nan],[prp:-19.75,11,5,22,4,86,139.16,13.01,8.43,6.86,-19.75,nan],[prb:nan,11,5,22,4,86,139.16,13.01,8.43,6.86,-19.75,nan],[prp:-19.91,11,5,22,5,86,139.16,13.07,8.37,6.99,-19.91,nan],[prb:nan,11,5,22,5,86,139.16,13.07,8.37,6.99,-19.91,nan],[prp:-22.92,11,5,22,6,86,139.16,13.18,8.26,6.99,-22.92,nan],[prb:nan,11,5,22,6,86,139.16,13.18,8.26,6.99,-22.92,nan],[prp:-22.08,11,5,22,7,86,139.16,13.18,8.26,7.23,-22.08,nan],[prb:nan,11,5,22,7,86,139.16,13.18,8.26,7.23,-22.08,nan]</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr"/>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V67" t="inlineStr"/>
       <c r="W67" t="inlineStr"/>
       <c r="X67" t="inlineStr"/>
@@ -4370,10 +5445,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C68" t="n">
-        <v>63865158140051</v>
+        <v>63865158140050</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4381,7 +5456,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>63865158090049</v>
+        <v>63865158090040</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -4389,22 +5464,66 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>63865158370039</v>
-      </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
+        <v>63865158370050</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>MT2640600H01</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:nan,13,6,26,8,103,129.12,12.98,8.13,6.6,-20.76,nan],[prp:-20.76,13,6,26,8,103,129.12,12.98,8.13,6.6,-20.76,nan],[prb:nan,13,6,26,9,103,129.12,12.98,8.13,6.6,-20.6,nan],[prp:-20.6,13,6,26,9,103,129.12,12.98,8.13,6.6,-20.6,nan],[prb:nan,13,6,26,10,103,129.12,12.98,8.13,6.6,-21.87,nan],[prp:-21.87,13,6,26,10,103,129.12,12.98,8.13,6.6,-21.87,nan],[prb:nan,13,6,26,11,103,129.12,12.86,8.25,6.46,-21.87,nan],[prp:-21.87,13,6,26,11,103,129.12,12.86,8.25,6.46,-21.87,nan]</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr"/>
-      <c r="U68" t="inlineStr"/>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V68" t="inlineStr"/>
       <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr"/>
@@ -4418,10 +5537,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C69" t="n">
-        <v>63865158140056</v>
+        <v>63865158140052</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4429,24 +5548,74 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>63865158090047</v>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
+        <v>63865158090044</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>63865158370046</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>MT2640600GZC</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>laser_tuning-create_mst_devices_chipset-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>mst_devices_Linkx-MST Linkx device presence</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr"/>
-      <c r="U69" t="inlineStr"/>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Joy</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V69" t="inlineStr"/>
       <c r="W69" t="inlineStr"/>
       <c r="X69" t="inlineStr"/>
@@ -4460,10 +5629,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C70" t="n">
-        <v>63865158140057</v>
+        <v>63865158140031</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4471,7 +5640,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>63865158090051</v>
+        <v>63865158090046</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -4479,22 +5648,66 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>63865158370038</v>
-      </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
+        <v>63865158370049</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>MT2640600GZ8</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>stress-run_stress-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>cpo_collect_stress_integrated_iter_0-[meas,S,an,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prb:2e-08,6,csm1_swb_maglan_asic_pcie,5,6,10,8,39,174.22,13.73,8.68,7.68,-1.07,2e-08],[prb:2e-08,6,csm1_swb_maglan_asic_pcie,5,6,10,9,39,174.22,13.88,8.53,7.88,0.26,2e-08],[prb:2e-08,6,csm1_swb_maglan_asic_pcie,5,6,10,10,39,174.22,13.81,8.6,7.78,-0.46,2e-08],[prb:2e-08,6,csm1_swb_maglan_asic_pcie,5,6,10,11,39,174.22,13.76,8.65,7.78,-0.94,2e-08],[prb:8e-08,7,csm1_swb_maglan_asic_pcie,5,6,10,8,39,173.94,13.81,8.59,7.78,-0.91,8e-08],[prb:8e-08,7,csm1_swb_maglan_asic_pcie,5,6,10,9,39,173.94,13.93,8.47,7.98,0.42,8e-08],[prb:8e-08,7,csm1_swb_maglan_asic_pcie,5,6,10,10,39,173.94,13.88,8.52,7.88,-0.25,8e-08],[prb:8e-08,7,csm1_swb_maglan_asic_pcie,5,6,10,11,39,173.94,13.81,8.59,7.78,-0.74,8e-08],[prb:2e-07,8,csm1_swb_maglan_asic_pcie,5,6,10,8,39,174.22,13.85,8.56,7.88,-0.77,2e-07],[prb:2e-07,8,csm1_swb_maglan_asic_pcie,5,6,10,9,39,174.22,13.98,8.43,7.98,0.57,2e-07],[prb:2e-07,8,csm1_swb_maglan_asic_pcie,5,6,10,10,39,174.22,13.9,8.51,7.88,-0.14,2e-07],[prb:2e-07,8,csm1_swb_maglan_asic_pcie,5,6,10,11,39,174.22,13.85,8.56,7.88,-0.56,2e-07],[prb:5e-07,9,csm1_swb_maglan_asic_pcie,5,6,10,8,39,173.94,13.88,8.52,7.88,-0.69,5e-07],[prb:5e-07,9,csm1_swb_maglan_asic_pcie,5,6,10,9,39,173.94,14.02,8.38,7.98,0.64,5e-07],[prb:5e-07,9,csm1_swb_maglan_asic_pcie,5,6,10,10,39,173.94,13.95,8.45,7.88,-0.06,5e-07],[prb:5e-07,9,csm1_swb_maglan_asic_pcie,5,6,10,11,39,173.94,13.9,8.5,7.88,-0.45,5e-07]</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr"/>
-      <c r="U70" t="inlineStr"/>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>FXV</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
       <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr"/>
@@ -4508,24 +5721,61 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C71" t="n">
-        <v>63865158140062</v>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
+        <v>63865158140055</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>63865158090045</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>63865158370023</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>query_fnm_linkup-linkup_polling_fnm-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>linkup_matrix_fnm-Failed: ['port 65/0', 'port 65/1']</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>PASS FT - Fail at HS cold test GOOD RX , NO BER 
+30-SEP : cookbook flow (LPBK remating / cleaning / crossing, Windu cross) -&gt; still fail replace CSM</t>
+        </is>
+      </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr"/>
@@ -4544,23 +5794,51 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C72" t="n">
-        <v>63865158140060</v>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+        <v>63865158140051</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>63865158090049</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>63865158370039</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>cpo_collect_restricted-[meas,ei,li,oil,oli,fc,ops,opm,eip,eocl,tp],[eocl:11.22,15,6,30,9,119,250,32.12,3.85,11.22,-100],[eocl:11.46,15,6,30,10,119,250,32.12,3.61,11.46,-100],[eocl:11.46,15,6,30,11,119,250,32.12,3.61,11.46,-100],[eocl:11.24,15,7,30,12,120,250,32.32,3.85,11.24,-100],[eocl:11.48,15,7,30,13,120,250,32.32,3.61,11.48,-100],[eocl:11.24,15,7,30,14,120,250,32.32,3.85,11.24,-100],[eocl:11.24,15,7,30,15,120,250,32.32,3.85,11.24,-100],[eocl:11.22,15,4,30,0,117,250,32.15,3.85,11.22,-100],[eocl:11.46,15,4,30,1,117,250,32.15,3.61,11.46,-100],[eocl:11.46,15,4,30,2,117,250,32.15,3.61,11.46,-100],[eocl:11.77,15,5,30,4,118,250,32.4,3.34,11.77,-100],[eocl:11.77,15,5,30,5,118,250,32.4,3.34,11.77,-100],[eocl:11.77,15,5,30,6,118,250,32.4,3.34,11.77,-100],[eocl:11.5,15,5,30,7,118,250,32.4,3.61,11.5,-100]</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
@@ -4580,10 +5858,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C73" t="n">
-        <v>63865158140061</v>
+        <v>63865158140056</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -4591,7 +5869,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>63865158090050</v>
+        <v>63865158090047</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -4599,17 +5877,34 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>63865158370040</v>
-      </c>
-      <c r="H73" t="inlineStr"/>
+        <v>63865158370036</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
       <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Fiber check OE6 no ELS input power
+Found Sagitta power low and remating D36</t>
+        </is>
+      </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr"/>
@@ -4628,23 +5923,51 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C74" t="n">
-        <v>63865158140058</v>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+        <v>63865158140057</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>63865158090051</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>63865158370038</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>stress-run_stress-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>cpo_collect_stress_integrated_iter_0-[meas,S,an,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[eocl:11.01,1,csm1_swb_maglan_asic_pcie,13,6,26,11,103,214.28,12.3,11.01,6.17,-2.91,5e-13],[eocl:11.09,2,csm1_swb_maglan_asic_pcie,8,5,16,4,62,229.05,12.51,11.09,6.32,-3.14,3e-12],[eocl:11.09,2,csm1_swb_maglan_asic_pcie,8,5,16,5,62,229.05,12.51,11.09,6.46,-3,3e-12],[eocl:11.01,2,csm1_swb_maglan_asic_pcie,13,6,26,11,103,214.28,12.3,11.01,6.17,-2.92,5e-13],[eocl:11.15,3,csm1_swb_maglan_asic_pcie,8,5,16,4,62,228.7,12.44,11.15,6.32,-3.21,4e-12],[eocl:11.11,3,csm1_swb_maglan_asic_pcie,8,5,16,5,62,228.7,12.48,11.11,6.32,-3.04,4e-12],[eocl:11.01,3,csm1_swb_maglan_asic_pcie,13,6,26,11,103,214.28,12.3,11.01,6.17,-2.93,6e-13],[eocl:11.17,4,csm1_swb_maglan_asic_pcie,8,5,16,4,62,229.41,12.44,11.17,6.32,-3.23,4e-12],[eocl:11.17,4,csm1_swb_maglan_asic_pcie,8,5,16,5,62,229.41,12.44,11.17,6.32,-3.08,4e-12],[eocl:11.04,4,csm1_swb_maglan_asic_pcie,8,5,16,6,62,229.41,12.57,11.04,6.46,-2.29,4e-12],[eocl:11.01,4,csm1_swb_maglan_asic_pcie,13,6,26,11,103,214.28,12.3,11.01,6.17,-2.94,5e-13],[eocl:11.16,5,csm1_swb_maglan_asic_pcie,8,5,16,4,62,229.05,12.44,11.16,6.32,-3.23,4e-12],[eocl:11.16,5,csm1_swb_maglan_asic_pcie,8,5,16,5,62,229.05,12.44,11.16,6.32,-3.09,4e-12],[eocl:11.03,5,csm1_swb_maglan_asic_pcie,8,5,16,6,62,229.05,12.57,11.03,6.46,-2.29,4e-12],[eocl:11.04,5,csm1_swb_maglan_asic_pcie,13,6,26,11,103,214.28,12.27,11.04,6.17,-2.97,5e-13],[eocl:11.17,6,csm1_swb_maglan_asic_pcie,8,5,16,4,62,229.41,12.44,11.17,6.32,-3.22,4e-12],[eocl:11.13,6,csm1_swb_maglan_asic_pcie,8,5,16,5,62,229.41,12.48,11.13,6.32,-3.07,4e-12],[eocl:11.04,6,csm1_swb_maglan_asic_pcie,8,5,16,6,62,229.41,12.57,11.04,6.32,-2.29,4e-12],[eocl:11.03,6,csm1_swb_maglan_asic_pcie,13,6,26,11,103,214.03,12.27,11.03,6.17,-2.98,5e-13],[eocl:11.13,7,csm1_swb_maglan_asic_pcie,8,5,16,4,62,229.41,12.48,11.13,6.32,-3.2,4e-12],[eocl:11.13,7,csm1_swb_maglan_asic_pcie,8,5,16,5,62,229.41,12.48,11.13,6.32,-3.04,4e-12],[eocl:11.07,7,csm1_swb_maglan_asic_pcie,13,6,26,11,103,214.03,12.23,11.07,6.17,-3.04,5e-13],[eocl:11.09,8,csm1_swb_maglan_asic_pcie,8,5,16,4,62,229.05,12.51,11.09,6.32,-3.2,4e-12],[eocl:11.09,8,csm1_swb_maglan_asic_pcie,8,5,16,5,62,229.05,12.51,11.09,6.32,-3.03,4e-12],[eocl:11.07,8,csm1_swb_maglan_asic_pcie,13,6,26,11,103,214.03,12.23,11.07,6.17,-3.01,5e-13],[eocl:11.07,9,csm1_swb_maglan_asic_pcie,8,5,16,4,62,229.41,12.54,11.07,6.46,-3.15,4e-12],[eocl:11.1,9,csm1_swb_maglan_asic_pcie,8,5,16,5,62,229.41,12.51,11.1,6.32,-3.01,4e-12],[eocl:11.07,9,csm1_swb_maglan_asic_pcie,13,6,26,11,103,214.03,12.23,11.07,6.17,-3.03,5e-13]</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
@@ -4664,14 +5987,24 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C75" t="n">
-        <v>63865158140059</v>
-      </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
+        <v>63865158140062</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>63865158090048</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -4693,6 +6026,178 @@
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="inlineStr"/>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>59</v>
+      </c>
+      <c r="C76" t="n">
+        <v>63865158140060</v>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr"/>
+      <c r="X76" t="inlineStr"/>
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>60</v>
+      </c>
+      <c r="C77" t="n">
+        <v>63865158140061</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>63865158090050</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>63865158370040</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>high_speed_eth_linkup-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>cpo_collect_linkup-[meas,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[prp:-23.28,4,3,7,12,28,164.11,12.98,9.17,6.73,-23.28,nan],[prb:nan,4,3,7,12,28,164.11,12.98,9.17,6.73,-23.28,nan],[prp:-23.28,4,3,7,13,28,164.11,13.01,9.14,6.86,-23.28,nan],[prb:nan,4,3,7,13,28,164.11,13.01,9.14,6.86,-23.28,nan],[prp:-19.32,4,3,7,14,28,164.11,12.92,9.23,6.99,-19.32,nan],[prb:nan,4,3,7,14,28,164.11,12.92,9.23,6.99,-19.32,nan],[prp:-19.21,4,3,7,15,28,164.11,12.76,9.39,6.73,-19.21,nan],[prb:nan,4,3,7,15,28,164.11,12.76,9.39,6.73,-19.21,nan],[prp:-20.09,2,3,3,12,12,119.22,12.79,7.97,6.73,-20.09,nan],[prb:nan,2,3,3,12,12,119.22,12.79,7.97,6.73,-20.09,nan],[prp:-21.37,2,3,3,13,12,119.22,13.07,7.69,6.86,-21.37,nan],[prb:nan,2,3,3,13,12,119.22,13.07,7.69,6.86,-21.37,nan],[prp:-21.19,2,3,3,14,12,119.22,12.82,7.94,6.73,-21.19,nan],[prb:nan,2,3,3,14,12,119.22,12.82,7.94,6.73,-21.19,nan],[prp:-21.37,2,3,3,15,12,119.22,12.67,8.09,6.6,-21.37,nan],[prb:nan,2,3,3,15,12,119.22,12.67,8.09,6.6,-21.37,nan],[prp:-19.91,1,3,1,12,4,114.73,12.64,7.96,6.32,-19.91,nan],[prb:nan,1,3,1,12,4,114.73,12.64,7.96,6.32,-19.91,nan],[prp:-19.75,1,3,1,13,4,114.73,12.76,7.84,6.46,-19.75,nan],[prb:nan,1,3,1,13,4,114.73,12.76,7.84,6.46,-19.75,nan],[prp:-21.87,1,3,1,14,4,114.73,12.79,7.81,6.46,-21.87,nan],[prb:nan,1,3,1,14,4,114.73,12.79,7.81,6.46,-21.87,nan],[prp:-21.61,1,3,1,15,4,114.73,12.7,7.9,6.46,-21.61,nan],[prb:nan,1,3,1,15,4,114.73,12.7,7.9,6.46,-21.61,nan]</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr"/>
+      <c r="X77" t="inlineStr"/>
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>61</v>
+      </c>
+      <c r="C78" t="n">
+        <v>63865158140058</v>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr"/>
+      <c r="X78" t="inlineStr"/>
+      <c r="Y78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>TS3</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>62</v>
+      </c>
+      <c r="C79" t="n">
+        <v>63865158140059</v>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/TS3_mapping.xlsx
+++ b/TS3_mapping.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1327,10 +1327,14 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>fuse_mismatch_group1-read_fuse_missmatch-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
+          <t>post_prbs_test_asic_reset-create_mst_devices_chipset-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>mst_devices_Linkx-MST Linkx device presence</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
@@ -2324,10 +2328,14 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>DEV032309</t>
@@ -2958,7 +2966,11 @@
           <t>MT2640600H04</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
@@ -3022,7 +3034,11 @@
           <t>MT2640600H03</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
@@ -3081,8 +3097,16 @@
           <t>DEV032309</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>MT2640600GZA</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
@@ -3233,7 +3257,11 @@
           <t>DEV032309</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>MT2640600GZ6</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -3293,8 +3321,16 @@
           <t>DEV032309</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>MT2640600GZ9</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -4873,10 +4909,14 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
@@ -5749,7 +5789,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="J71" t="inlineStr"/>
@@ -5820,7 +5860,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
@@ -5881,10 +5925,14 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>

--- a/TS3_mapping.xlsx
+++ b/TS3_mapping.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/TS3_mapping.xlsx
+++ b/TS3_mapping.xlsx
@@ -1501,7 +1501,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3262,7 +3262,11 @@
           <t>MT2640600GZ6</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>

--- a/TS3_mapping.xlsx
+++ b/TS3_mapping.xlsx
@@ -3746,7 +3746,11 @@
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>moved to Omer for material fuse 33</t>
+        </is>
+      </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
@@ -4642,14 +4646,14 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spectrum-6 in Flash Recovery Mode. 
+          <t>Spectrum-6 in Flash Recovery Mode. 
 Suspect ASIC issue.
 NV : share details 
 JE130526T0960963100707
 E6B171_9_2_8
 01 OCT: ULT E6B171_9_2_8 passed FT on rev_2B.
 It passed HBI HS test, without failures (FT1 and FT2).
-</t>
+moved to Omer for material fuse 33</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr"/>

--- a/TS3_mapping.xlsx
+++ b/TS3_mapping.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4696,7 +4696,9 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>63865158110005</v>
+      </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
@@ -4740,7 +4742,9 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="n">
+        <v>63865158110004</v>
+      </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
@@ -4780,7 +4784,9 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="n">
+        <v>63865158110002</v>
+      </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
@@ -4820,7 +4826,9 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="n">
+        <v>63865158110001</v>
+      </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
@@ -4860,7 +4868,9 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="n">
+        <v>63865158110003</v>
+      </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
@@ -4925,9 +4935,21 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>DEV032313</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>MT2641601RDL</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr">
         <is>
           <t>FT</t>
@@ -5800,9 +5822,21 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>MT2641601RC2</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr">
         <is>
           <t>FT</t>
@@ -5873,9 +5907,21 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>MT2641601RC0</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
           <t>FT</t>
@@ -5941,9 +5987,21 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>MT2641601RC1</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="M73" t="inlineStr">
         <is>
           <t>FT</t>
@@ -6005,10 +6063,26 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>MT2641601RAF</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr">
         <is>
           <t>FT</t>
@@ -6061,7 +6135,9 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="n">
+        <v>63865158370031</v>
+      </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
@@ -6094,10 +6170,22 @@
       <c r="C76" t="n">
         <v>63865158140060</v>
       </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>63865158090053</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>63865158370030</v>
+      </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
@@ -6151,10 +6239,26 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>DEV032309</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>MT2641601RAE</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="M77" t="inlineStr">
         <is>
           <t>FT</t>

--- a/TS3_mapping.xlsx
+++ b/TS3_mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z79"/>
+  <dimension ref="A1:Z82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6140,7 +6140,11 @@
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>DEV032648</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
@@ -6188,8 +6192,16 @@
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>DEV032648</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>MT26426019XQ</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
@@ -6358,6 +6370,140 @@
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="inlineStr"/>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>FUSE33</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>64165164520003</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>64165164500001</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>64165164390002</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>FUSE33</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>64165164520002</v>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>FUSE33</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>64165164520001</v>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr"/>
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/TS3_mapping.xlsx
+++ b/TS3_mapping.xlsx
@@ -6440,12 +6440,24 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>64165164520002</v>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
+        <v>64165164520001</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>64165164500002</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>64165164390004</v>
+      </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
@@ -6478,13 +6490,29 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>64165164520001</v>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+        <v>64165164520002</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>64165164500003</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>64165164390003</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
